--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AY118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809087</v>
+        <v>129809109</v>
       </c>
       <c r="B2" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495710</v>
+        <v>495738</v>
       </c>
       <c r="R2" t="n">
-        <v>7039992</v>
+        <v>7040008</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +766,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809089</v>
+        <v>129809157</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>82916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495476</v>
+        <v>495620</v>
       </c>
       <c r="R3" t="n">
-        <v>7040074</v>
+        <v>7040063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809109</v>
+        <v>129809578</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,41 +905,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -924,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495738</v>
+        <v>495701</v>
       </c>
       <c r="R4" t="n">
-        <v>7040008</v>
+        <v>7040014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +976,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,28 +985,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809157</v>
+        <v>129809087</v>
       </c>
       <c r="B5" t="n">
-        <v>82916</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495620</v>
+        <v>495710</v>
       </c>
       <c r="R5" t="n">
-        <v>7040063</v>
+        <v>7039992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,53 +1126,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809611</v>
+        <v>129809089</v>
       </c>
       <c r="B6" t="n">
-        <v>100963</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495627</v>
+        <v>495476</v>
       </c>
       <c r="R6" t="n">
-        <v>7039995</v>
+        <v>7040074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,45 +1199,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809578</v>
+        <v>129809603</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,30 +1234,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1246,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495701</v>
+        <v>495504</v>
       </c>
       <c r="R7" t="n">
-        <v>7040014</v>
+        <v>7040017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1301,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,22 +1321,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1339,7 +1354,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809603</v>
+        <v>129809595</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1377,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495504</v>
+        <v>495548</v>
       </c>
       <c r="R8" t="n">
-        <v>7040017</v>
+        <v>7039913</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,11 +1428,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,37 +1480,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129809595</v>
+        <v>129809611</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>100963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495548</v>
+        <v>495627</v>
       </c>
       <c r="R9" t="n">
-        <v>7039913</v>
+        <v>7039995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,6 +1561,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1559,26 +1579,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809115</v>
+        <v>129809107</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495682</v>
+        <v>495592</v>
       </c>
       <c r="R10" t="n">
-        <v>7040065</v>
+        <v>7040205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,11 +1667,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1795,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129809107</v>
+        <v>129809146</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>91589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495592</v>
+        <v>495659</v>
       </c>
       <c r="R12" t="n">
-        <v>7040205</v>
+        <v>7039854</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809146</v>
+        <v>129809599</v>
       </c>
       <c r="B13" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,34 +1898,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495659</v>
+        <v>495719</v>
       </c>
       <c r="R13" t="n">
-        <v>7039854</v>
+        <v>7040059</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,69 +1963,107 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809082</v>
+        <v>129809573</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495470</v>
+        <v>495496</v>
       </c>
       <c r="R14" t="n">
-        <v>7039843</v>
+        <v>7040079</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2100,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På bark av en levande sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,55 +2109,85 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129809599</v>
+        <v>129809583</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>80222</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2129,10 +2195,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495719</v>
+        <v>495575</v>
       </c>
       <c r="R15" t="n">
-        <v>7040059</v>
+        <v>7039971</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,7 +2235,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>På barken av en död sälglåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,27 +2250,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2222,52 +2288,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129809573</v>
+        <v>129809115</v>
       </c>
       <c r="B16" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495496</v>
+        <v>495682</v>
       </c>
       <c r="R16" t="n">
-        <v>7040079</v>
+        <v>7040065</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2363,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,96 +2372,63 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129809583</v>
+        <v>129809082</v>
       </c>
       <c r="B17" t="n">
-        <v>80222</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495575</v>
+        <v>495470</v>
       </c>
       <c r="R17" t="n">
-        <v>7039971</v>
+        <v>7039843</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,7 +2465,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På barken av en död sälglåga.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,44 +2474,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129809152</v>
+        <v>129809144</v>
       </c>
       <c r="B21" t="n">
-        <v>91613</v>
+        <v>78094</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,19 +2825,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2845,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495696</v>
+        <v>495584</v>
       </c>
       <c r="R21" t="n">
-        <v>7040090</v>
+        <v>7040207</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2907,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809114</v>
+        <v>129809602</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2918,34 +2922,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495559</v>
+        <v>495479</v>
       </c>
       <c r="R22" t="n">
-        <v>7039895</v>
+        <v>7039967</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,29 +2987,50 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3106,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809144</v>
+        <v>129809596</v>
       </c>
       <c r="B24" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,34 +3145,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495584</v>
+        <v>495570</v>
       </c>
       <c r="R24" t="n">
-        <v>7040207</v>
+        <v>7039935</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,28 +3216,54 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129809602</v>
+        <v>129809152</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,37 +3271,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495479</v>
+        <v>495696</v>
       </c>
       <c r="R25" t="n">
-        <v>7039967</v>
+        <v>7040090</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,54 +3335,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129809596</v>
+        <v>129809114</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,37 +3364,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495570</v>
+        <v>495559</v>
       </c>
       <c r="R26" t="n">
-        <v>7039935</v>
+        <v>7039895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,60 +3426,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129809131</v>
+        <v>129809147</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>91589</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495455</v>
+        <v>495722</v>
       </c>
       <c r="R27" t="n">
-        <v>7040119</v>
+        <v>7040115</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,11 +3526,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3557,10 +3552,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129809147</v>
+        <v>129809096</v>
       </c>
       <c r="B28" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3568,21 +3563,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3592,10 +3587,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495722</v>
+        <v>495570</v>
       </c>
       <c r="R28" t="n">
-        <v>7040115</v>
+        <v>7040065</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3654,10 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129809096</v>
+        <v>129809131</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,21 +3660,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3689,10 +3684,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495570</v>
+        <v>495455</v>
       </c>
       <c r="R29" t="n">
-        <v>7040065</v>
+        <v>7040119</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3725,6 +3720,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129809141</v>
+        <v>129809105</v>
       </c>
       <c r="B31" t="n">
-        <v>80222</v>
+        <v>91557</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,21 +3864,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495483</v>
+        <v>495461</v>
       </c>
       <c r="R31" t="n">
-        <v>7040081</v>
+        <v>7039930</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3950,34 +3950,30 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809105</v>
+        <v>129809094</v>
       </c>
       <c r="B32" t="n">
-        <v>91557</v>
+        <v>91613</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3985,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495461</v>
+        <v>495459</v>
       </c>
       <c r="R32" t="n">
-        <v>7039930</v>
+        <v>7039862</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,6 +4025,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4047,45 +4044,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809126</v>
+        <v>129809572</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495467</v>
+        <v>495579</v>
       </c>
       <c r="R33" t="n">
-        <v>7040110</v>
+        <v>7039969</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4122,7 +4126,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På barken av en sälglåga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4131,79 +4135,89 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809137</v>
+        <v>129809141</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>80222</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495739</v>
+        <v>495483</v>
       </c>
       <c r="R34" t="n">
-        <v>7040024</v>
+        <v>7040081</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4262,10 +4276,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129809094</v>
+        <v>129809567</v>
       </c>
       <c r="B35" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4273,30 +4287,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495459</v>
+        <v>495594</v>
       </c>
       <c r="R35" t="n">
-        <v>7039862</v>
+        <v>7039971</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4331,35 +4357,64 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129809567</v>
+        <v>129809137</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,16 +4422,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4384,12 +4439,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4399,10 +4462,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495594</v>
+        <v>495739</v>
       </c>
       <c r="R36" t="n">
-        <v>7039971</v>
+        <v>7040024</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,11 +4500,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4450,93 +4508,61 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129809572</v>
+        <v>129809126</v>
       </c>
       <c r="B37" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495579</v>
+        <v>495467</v>
       </c>
       <c r="R37" t="n">
-        <v>7039969</v>
+        <v>7040110</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4573,7 +4599,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På barken av en sälglåga.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4582,54 +4608,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129809561</v>
+        <v>129809111</v>
       </c>
       <c r="B38" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,41 +4637,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495774</v>
+        <v>495558</v>
       </c>
       <c r="R38" t="n">
-        <v>7040061</v>
+        <v>7039811</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,7 +4701,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I en upplyft granlåga.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4717,54 +4710,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129809604</v>
+        <v>129809138</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,37 +4739,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495501</v>
+        <v>495613</v>
       </c>
       <c r="R39" t="n">
-        <v>7040069</v>
+        <v>7039922</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4843,44 +4807,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4984,32 +4922,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809111</v>
+        <v>129809140</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>92046</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5019,10 +4957,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495558</v>
+        <v>495671</v>
       </c>
       <c r="R41" t="n">
-        <v>7039811</v>
+        <v>7039845</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5055,11 +4993,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5086,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809138</v>
+        <v>129809561</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>91593</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5097,34 +5030,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495613</v>
+        <v>495774</v>
       </c>
       <c r="R42" t="n">
-        <v>7039922</v>
+        <v>7040061</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5159,56 +5099,87 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129809140</v>
+        <v>129809084</v>
       </c>
       <c r="B43" t="n">
-        <v>92046</v>
+        <v>80215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5218,10 +5189,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495671</v>
+        <v>495651</v>
       </c>
       <c r="R43" t="n">
-        <v>7039845</v>
+        <v>7039928</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5280,45 +5251,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129809084</v>
+        <v>129809604</v>
       </c>
       <c r="B44" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495651</v>
+        <v>495501</v>
       </c>
       <c r="R44" t="n">
-        <v>7039928</v>
+        <v>7040069</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5359,18 +5333,44 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129809154</v>
+        <v>129809605</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5503,16 +5503,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495635</v>
+        <v>495546</v>
       </c>
       <c r="R46" t="n">
-        <v>7039937</v>
+        <v>7040104</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5553,28 +5556,54 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129809079</v>
+        <v>129809154</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5582,21 +5611,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5606,10 +5635,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495550</v>
+        <v>495635</v>
       </c>
       <c r="R47" t="n">
-        <v>7039807</v>
+        <v>7039937</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5642,11 +5671,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5673,10 +5697,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809080</v>
+        <v>129809592</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5684,34 +5708,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495554</v>
+        <v>495516</v>
       </c>
       <c r="R48" t="n">
-        <v>7039840</v>
+        <v>7039796</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5775,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5757,28 +5784,54 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129809605</v>
+        <v>129809079</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5786,37 +5839,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495546</v>
+        <v>495550</v>
       </c>
       <c r="R49" t="n">
-        <v>7040104</v>
+        <v>7039807</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,60 +5901,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129809592</v>
+        <v>129809080</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5912,37 +5941,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495516</v>
+        <v>495554</v>
       </c>
       <c r="R50" t="n">
-        <v>7039796</v>
+        <v>7039840</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5979,7 +6005,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,54 +6014,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809103</v>
+        <v>129809142</v>
       </c>
       <c r="B51" t="n">
-        <v>83050</v>
+        <v>78094</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495680</v>
+        <v>495682</v>
       </c>
       <c r="R51" t="n">
-        <v>7039973</v>
+        <v>7039932</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6129,45 +6129,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809142</v>
+        <v>129809584</v>
       </c>
       <c r="B52" t="n">
-        <v>78094</v>
+        <v>80222</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495682</v>
+        <v>495504</v>
       </c>
       <c r="R52" t="n">
-        <v>7039932</v>
+        <v>7040027</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,65 +6209,92 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På barken av en smal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129809584</v>
+        <v>129809606</v>
       </c>
       <c r="B53" t="n">
-        <v>80222</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6268,10 +6302,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495504</v>
+        <v>495603</v>
       </c>
       <c r="R53" t="n">
-        <v>7040027</v>
+        <v>7040220</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6306,11 +6340,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På barken av en smal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6328,22 +6357,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6361,10 +6390,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809606</v>
+        <v>129809103</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6372,37 +6401,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495603</v>
+        <v>495680</v>
       </c>
       <c r="R54" t="n">
-        <v>7040220</v>
+        <v>7039973</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6443,44 +6469,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6622,10 +6622,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129809078</v>
+        <v>129809155</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6633,21 +6633,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495653</v>
+        <v>495737</v>
       </c>
       <c r="R56" t="n">
-        <v>7039924</v>
+        <v>7040098</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6693,11 +6693,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6724,10 +6719,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129809155</v>
+        <v>129809078</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6735,21 +6730,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6759,10 +6754,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495737</v>
+        <v>495653</v>
       </c>
       <c r="R57" t="n">
-        <v>7040098</v>
+        <v>7039924</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6795,6 +6790,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6923,10 +6923,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129809133</v>
+        <v>129809563</v>
       </c>
       <c r="B59" t="n">
-        <v>80215</v>
+        <v>92311</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,34 +6934,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495563</v>
+        <v>495549</v>
       </c>
       <c r="R59" t="n">
-        <v>7039894</v>
+        <v>7039804</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6996,34 +7003,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I en knäckt gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809143</v>
+        <v>129809153</v>
       </c>
       <c r="B60" t="n">
-        <v>78094</v>
+        <v>91613</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7031,23 +7064,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7055,10 +7084,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495700</v>
+        <v>495507</v>
       </c>
       <c r="R60" t="n">
-        <v>7040007</v>
+        <v>7040063</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7117,32 +7146,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809156</v>
+        <v>129809133</v>
       </c>
       <c r="B61" t="n">
-        <v>82916</v>
+        <v>80215</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7152,10 +7181,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495664</v>
+        <v>495563</v>
       </c>
       <c r="R61" t="n">
-        <v>7040037</v>
+        <v>7039894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7311,10 +7340,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809153</v>
+        <v>129809562</v>
       </c>
       <c r="B63" t="n">
-        <v>91613</v>
+        <v>91593</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7322,30 +7351,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495507</v>
+        <v>495606</v>
       </c>
       <c r="R63" t="n">
-        <v>7040063</v>
+        <v>7040134</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7380,77 +7420,100 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129809610</v>
+        <v>129809156</v>
       </c>
       <c r="B64" t="n">
-        <v>100963</v>
+        <v>82916</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495622</v>
+        <v>495664</v>
       </c>
       <c r="R64" t="n">
-        <v>7039966</v>
+        <v>7040037</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7491,34 +7554,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129809563</v>
+        <v>129809610</v>
       </c>
       <c r="B65" t="n">
-        <v>92311</v>
+        <v>100963</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7526,30 +7583,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7557,10 +7615,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495549</v>
+        <v>495622</v>
       </c>
       <c r="R65" t="n">
-        <v>7039804</v>
+        <v>7039966</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7595,11 +7653,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>I en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7613,21 +7666,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7645,10 +7683,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129809562</v>
+        <v>129809143</v>
       </c>
       <c r="B66" t="n">
-        <v>91593</v>
+        <v>78094</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7656,41 +7694,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495606</v>
+        <v>495700</v>
       </c>
       <c r="R66" t="n">
-        <v>7040134</v>
+        <v>7040007</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7725,65 +7756,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129809099</v>
+        <v>129809158</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>83042</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,21 +7791,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495626</v>
+        <v>495531</v>
       </c>
       <c r="R67" t="n">
-        <v>7040099</v>
+        <v>7040125</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809158</v>
+        <v>129809098</v>
       </c>
       <c r="B68" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7888,21 +7888,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495531</v>
+        <v>495709</v>
       </c>
       <c r="R68" t="n">
-        <v>7040125</v>
+        <v>7040119</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7974,10 +7974,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809127</v>
+        <v>129809099</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7985,21 +7985,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495608</v>
+        <v>495626</v>
       </c>
       <c r="R69" t="n">
-        <v>7040209</v>
+        <v>7040099</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8045,11 +8045,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8178,10 +8173,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809098</v>
+        <v>129809127</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8189,21 +8184,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8213,10 +8208,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495709</v>
+        <v>495608</v>
       </c>
       <c r="R71" t="n">
-        <v>7040119</v>
+        <v>7040209</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8249,6 +8244,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809104</v>
+        <v>129809585</v>
       </c>
       <c r="B73" t="n">
-        <v>83050</v>
+        <v>91589</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,34 +8383,41 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495595</v>
+        <v>495645</v>
       </c>
       <c r="R73" t="n">
-        <v>7040220</v>
+        <v>7039861</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8451,28 +8458,54 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809130</v>
+        <v>129809568</v>
       </c>
       <c r="B74" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8480,34 +8513,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495569</v>
+        <v>495618</v>
       </c>
       <c r="R74" t="n">
-        <v>7039991</v>
+        <v>7040130</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8544,7 +8585,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8555,26 +8596,51 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809101</v>
+        <v>129809122</v>
       </c>
       <c r="B75" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8582,21 +8648,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8606,10 +8672,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495682</v>
+        <v>495433</v>
       </c>
       <c r="R75" t="n">
-        <v>7039933</v>
+        <v>7039995</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8642,6 +8708,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8668,10 +8739,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809122</v>
+        <v>129809601</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8679,34 +8750,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495433</v>
+        <v>495583</v>
       </c>
       <c r="R76" t="n">
-        <v>7039995</v>
+        <v>7039969</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8741,39 +8815,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809601</v>
+        <v>129809104</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8781,37 +8876,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495583</v>
+        <v>495595</v>
       </c>
       <c r="R77" t="n">
-        <v>7039969</v>
+        <v>7040220</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8852,54 +8944,28 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809585</v>
+        <v>129809607</v>
       </c>
       <c r="B78" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8907,28 +8973,28 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8938,10 +9004,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495645</v>
+        <v>495591</v>
       </c>
       <c r="R78" t="n">
-        <v>7039861</v>
+        <v>7040221</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8976,6 +9042,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Med apothecier på gran.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9003,12 +9074,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9026,7 +9097,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129809607</v>
+        <v>129809600</v>
       </c>
       <c r="B79" t="n">
         <v>79081</v>
@@ -9056,11 +9127,7 @@
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9068,10 +9135,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>495591</v>
+        <v>495604</v>
       </c>
       <c r="R79" t="n">
-        <v>7040221</v>
+        <v>7040032</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9108,7 +9175,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Med apothecier på gran.</t>
+          <t>På gran i äldre  granskog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9161,10 +9228,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809600</v>
+        <v>129809101</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,37 +9239,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495604</v>
+        <v>495682</v>
       </c>
       <c r="R80" t="n">
-        <v>7040032</v>
+        <v>7039933</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9237,55 +9301,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På gran i äldre  granskog.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9427,10 +9460,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129809568</v>
+        <v>129809130</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9438,42 +9471,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>495618</v>
+        <v>495569</v>
       </c>
       <c r="R82" t="n">
-        <v>7040130</v>
+        <v>7039991</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9510,7 +9535,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9521,41 +9546,16 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9659,32 +9659,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129809145</v>
+        <v>129809125</v>
       </c>
       <c r="B84" t="n">
-        <v>80146</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>495535</v>
+        <v>495461</v>
       </c>
       <c r="R84" t="n">
-        <v>7040131</v>
+        <v>7040125</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9730,6 +9730,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9756,10 +9761,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129809125</v>
+        <v>129809574</v>
       </c>
       <c r="B85" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9767,16 +9772,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9785,16 +9790,24 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>495461</v>
+        <v>495509</v>
       </c>
       <c r="R85" t="n">
-        <v>7040125</v>
+        <v>7040092</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9831,7 +9844,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9842,69 +9855,86 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129809574</v>
+        <v>129809145</v>
       </c>
       <c r="B86" t="n">
-        <v>57733</v>
+        <v>80146</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>495509</v>
+        <v>495535</v>
       </c>
       <c r="R86" t="n">
-        <v>7040092</v>
+        <v>7040131</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9939,11 +9969,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9952,73 +9977,48 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129809081</v>
+        <v>129809135</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>495568</v>
+        <v>495536</v>
       </c>
       <c r="R87" t="n">
-        <v>7040032</v>
+        <v>7040124</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10064,11 +10064,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10095,45 +10090,52 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129809135</v>
+        <v>129809580</v>
       </c>
       <c r="B88" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>495536</v>
+        <v>495517</v>
       </c>
       <c r="R88" t="n">
-        <v>7040124</v>
+        <v>7040108</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10168,34 +10170,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På barken av en upplyft död nedfallen sälg.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129809148</v>
+        <v>129809081</v>
       </c>
       <c r="B89" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10203,21 +10236,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10227,10 +10260,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>495742</v>
+        <v>495568</v>
       </c>
       <c r="R89" t="n">
-        <v>7040116</v>
+        <v>7040032</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10263,6 +10296,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10289,10 +10327,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129809580</v>
+        <v>129809148</v>
       </c>
       <c r="B90" t="n">
-        <v>80186</v>
+        <v>91589</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10300,41 +10338,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>495517</v>
+        <v>495742</v>
       </c>
       <c r="R90" t="n">
-        <v>7040108</v>
+        <v>7040116</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10369,65 +10400,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På barken av en upplyft död nedfallen sälg.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129809095</v>
+        <v>129809587</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10435,34 +10435,41 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>495614</v>
+        <v>495597</v>
       </c>
       <c r="R91" t="n">
-        <v>7039909</v>
+        <v>7040221</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10497,34 +10504,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>I en stående levande gran.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129809587</v>
+        <v>129809608</v>
       </c>
       <c r="B92" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10532,30 +10570,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10563,10 +10597,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>495597</v>
+        <v>495581</v>
       </c>
       <c r="R92" t="n">
-        <v>7040221</v>
+        <v>7040226</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10601,11 +10635,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>I en stående levande gran.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10633,12 +10662,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10656,7 +10685,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129809608</v>
+        <v>129809597</v>
       </c>
       <c r="B93" t="n">
         <v>79081</v>
@@ -10694,10 +10723,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>495581</v>
+        <v>495598</v>
       </c>
       <c r="R93" t="n">
-        <v>7040226</v>
+        <v>7039942</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10782,7 +10811,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129809597</v>
+        <v>129809095</v>
       </c>
       <c r="B94" t="n">
         <v>79081</v>
@@ -10811,19 +10840,16 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>495598</v>
+        <v>495614</v>
       </c>
       <c r="R94" t="n">
-        <v>7039942</v>
+        <v>7039909</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10864,44 +10890,18 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11034,10 +11034,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129809593</v>
+        <v>129809093</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11045,37 +11045,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>495530</v>
+        <v>495655</v>
       </c>
       <c r="R96" t="n">
-        <v>7039833</v>
+        <v>7040108</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11116,54 +11109,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129809093</v>
+        <v>129809593</v>
       </c>
       <c r="B97" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11171,30 +11138,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>495655</v>
+        <v>495530</v>
       </c>
       <c r="R97" t="n">
-        <v>7040108</v>
+        <v>7039833</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11235,18 +11209,44 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129809116</v>
+        <v>129809594</v>
       </c>
       <c r="B102" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11691,34 +11691,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>495435</v>
+        <v>495544</v>
       </c>
       <c r="R102" t="n">
-        <v>7039823</v>
+        <v>7039898</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11755,7 +11758,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11764,25 +11767,51 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129809594</v>
+        <v>129809598</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -11820,10 +11849,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495544</v>
+        <v>495684</v>
       </c>
       <c r="R103" t="n">
-        <v>7039898</v>
+        <v>7040002</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11856,11 +11885,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11913,10 +11937,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129809598</v>
+        <v>129809116</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11924,37 +11948,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>495684</v>
+        <v>495435</v>
       </c>
       <c r="R104" t="n">
-        <v>7040002</v>
+        <v>7039823</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11989,89 +12010,68 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129809586</v>
+        <v>129809581</v>
       </c>
       <c r="B105" t="n">
-        <v>91589</v>
+        <v>80222</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>495477</v>
+        <v>495749</v>
       </c>
       <c r="R105" t="n">
-        <v>7039974</v>
+        <v>7040011</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Växer i en stubbe av en knäckt gran.</t>
+          <t>På bark på en smal sälg.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12141,22 +12141,22 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12174,52 +12174,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129809581</v>
+        <v>129809102</v>
       </c>
       <c r="B106" t="n">
-        <v>80222</v>
+        <v>83050</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>495749</v>
+        <v>495533</v>
       </c>
       <c r="R106" t="n">
-        <v>7040011</v>
+        <v>7039800</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12254,65 +12247,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På bark på en smal sälg.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809570</v>
+        <v>129809586</v>
       </c>
       <c r="B107" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12320,29 +12282,28 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -12352,10 +12313,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495618</v>
+        <v>495477</v>
       </c>
       <c r="R107" t="n">
-        <v>7040246</v>
+        <v>7039974</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12392,7 +12353,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Växer i en stubbe av en knäckt gran.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12401,6 +12362,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12421,12 +12383,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12444,10 +12406,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129809102</v>
+        <v>129809113</v>
       </c>
       <c r="B108" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12455,21 +12417,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12479,10 +12441,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>495533</v>
+        <v>495541</v>
       </c>
       <c r="R108" t="n">
-        <v>7039800</v>
+        <v>7039874</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12515,6 +12477,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12541,7 +12508,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129809113</v>
+        <v>129809570</v>
       </c>
       <c r="B109" t="n">
         <v>57736</v>
@@ -12570,16 +12537,24 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>495541</v>
+        <v>495618</v>
       </c>
       <c r="R109" t="n">
-        <v>7039874</v>
+        <v>7040246</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12616,7 +12591,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12627,26 +12602,51 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129809085</v>
+        <v>129809582</v>
       </c>
       <c r="B110" t="n">
-        <v>80215</v>
+        <v>80222</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12654,34 +12654,41 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>495476</v>
+        <v>495698</v>
       </c>
       <c r="R110" t="n">
-        <v>7040074</v>
+        <v>7040023</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12716,54 +12723,89 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129809151</v>
+        <v>129809085</v>
       </c>
       <c r="B111" t="n">
-        <v>91613</v>
+        <v>80215</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12771,10 +12813,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>495456</v>
+        <v>495476</v>
       </c>
       <c r="R111" t="n">
-        <v>7039928</v>
+        <v>7040074</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12833,10 +12875,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129809566</v>
+        <v>129809151</v>
       </c>
       <c r="B112" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12844,42 +12886,30 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>495633</v>
+        <v>495456</v>
       </c>
       <c r="R112" t="n">
-        <v>7040044</v>
+        <v>7039928</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12914,11 +12944,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12927,80 +12952,56 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129809582</v>
+        <v>129809566</v>
       </c>
       <c r="B113" t="n">
-        <v>80222</v>
+        <v>57736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -13010,10 +13011,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>495698</v>
+        <v>495633</v>
       </c>
       <c r="R113" t="n">
-        <v>7040023</v>
+        <v>7040044</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13050,7 +13051,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13059,7 +13060,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -13070,22 +13070,22 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13100,6 +13100,540 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129835891</v>
+      </c>
+      <c r="B114" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Gulåstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>495437</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7039821</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129835888</v>
+      </c>
+      <c r="B115" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Gulåstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>495432</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7039838</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129835887</v>
+      </c>
+      <c r="B116" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Gulåstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>495432</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7039845</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129835889</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Gulåstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>495434</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7039822</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129835890</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Gulåstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>495436</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7039822</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -675,54 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809109</v>
+        <v>129809611</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>100963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -730,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495738</v>
+        <v>495627</v>
       </c>
       <c r="R2" t="n">
-        <v>7040008</v>
+        <v>7039995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,18 +767,24 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -894,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809578</v>
+        <v>129809603</v>
       </c>
       <c r="B4" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,30 +899,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495701</v>
+        <v>495504</v>
       </c>
       <c r="R4" t="n">
-        <v>7040014</v>
+        <v>7040017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +966,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,22 +986,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1029,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809087</v>
+        <v>129809595</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,34 +1030,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495710</v>
+        <v>495548</v>
       </c>
       <c r="R5" t="n">
-        <v>7039992</v>
+        <v>7039913</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,25 +1101,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809089</v>
+        <v>129809578</v>
       </c>
       <c r="B6" t="n">
         <v>80186</v>
@@ -1155,16 +1174,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495476</v>
+        <v>495701</v>
       </c>
       <c r="R6" t="n">
-        <v>7040074</v>
+        <v>7040014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,34 +1225,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809603</v>
+        <v>129809087</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,37 +1291,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495504</v>
+        <v>495710</v>
       </c>
       <c r="R7" t="n">
-        <v>7040017</v>
+        <v>7039992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,65 +1353,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809595</v>
+        <v>129809089</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,37 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495548</v>
+        <v>495476</v>
       </c>
       <c r="R8" t="n">
-        <v>7039913</v>
+        <v>7040074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,86 +1456,72 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129809611</v>
+        <v>129809109</v>
       </c>
       <c r="B9" t="n">
-        <v>100963</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1523,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495627</v>
+        <v>495738</v>
       </c>
       <c r="R9" t="n">
-        <v>7039995</v>
+        <v>7040008</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1569,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,34 +1578,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809107</v>
+        <v>129809146</v>
       </c>
       <c r="B10" t="n">
-        <v>91593</v>
+        <v>91589</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495592</v>
+        <v>495659</v>
       </c>
       <c r="R10" t="n">
-        <v>7040205</v>
+        <v>7039854</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129809139</v>
+        <v>129809107</v>
       </c>
       <c r="B11" t="n">
-        <v>80187</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495484</v>
+        <v>495592</v>
       </c>
       <c r="R11" t="n">
-        <v>7040082</v>
+        <v>7040205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129809146</v>
+        <v>129809115</v>
       </c>
       <c r="B12" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495659</v>
+        <v>495682</v>
       </c>
       <c r="R12" t="n">
-        <v>7039854</v>
+        <v>7040065</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,6 +1861,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809599</v>
+        <v>129809082</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,37 +1903,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495719</v>
+        <v>495470</v>
       </c>
       <c r="R13" t="n">
-        <v>7040059</v>
+        <v>7039843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1967,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,85 +1976,55 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809573</v>
+        <v>129809599</v>
       </c>
       <c r="B14" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2060,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495496</v>
+        <v>495719</v>
       </c>
       <c r="R14" t="n">
-        <v>7040079</v>
+        <v>7040059</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2100,7 +2072,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,27 +2087,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2153,52 +2125,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129809583</v>
+        <v>129809139</v>
       </c>
       <c r="B15" t="n">
-        <v>80222</v>
+        <v>80187</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495575</v>
+        <v>495484</v>
       </c>
       <c r="R15" t="n">
-        <v>7039971</v>
+        <v>7040082</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,100 +2198,76 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På barken av en död sälglåga.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129809115</v>
+        <v>129809573</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495682</v>
+        <v>495496</v>
       </c>
       <c r="R16" t="n">
-        <v>7040065</v>
+        <v>7040079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2304,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På bark av en levande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,63 +2313,96 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129809082</v>
+        <v>129809583</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>80222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495470</v>
+        <v>495575</v>
       </c>
       <c r="R17" t="n">
-        <v>7039843</v>
+        <v>7039971</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2439,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På barken av en död sälglåga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,18 +2448,44 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809076</v>
+        <v>129809144</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>78094</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495663</v>
+        <v>495584</v>
       </c>
       <c r="R19" t="n">
-        <v>7040097</v>
+        <v>7040207</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809159</v>
+        <v>129809076</v>
       </c>
       <c r="B20" t="n">
-        <v>83042</v>
+        <v>91593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495530</v>
+        <v>495663</v>
       </c>
       <c r="R20" t="n">
-        <v>7040111</v>
+        <v>7040097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129809144</v>
+        <v>129809159</v>
       </c>
       <c r="B21" t="n">
-        <v>78094</v>
+        <v>83042</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495584</v>
+        <v>495530</v>
       </c>
       <c r="R21" t="n">
-        <v>7040207</v>
+        <v>7040111</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809602</v>
+        <v>129809114</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,37 +2922,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495479</v>
+        <v>495559</v>
       </c>
       <c r="R22" t="n">
-        <v>7039967</v>
+        <v>7039895</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2987,50 +2984,29 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3134,7 +3110,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809596</v>
+        <v>129809602</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3172,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495570</v>
+        <v>495479</v>
       </c>
       <c r="R24" t="n">
-        <v>7039935</v>
+        <v>7039967</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3260,10 +3236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129809152</v>
+        <v>129809596</v>
       </c>
       <c r="B25" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,30 +3247,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495696</v>
+        <v>495570</v>
       </c>
       <c r="R25" t="n">
-        <v>7040090</v>
+        <v>7039935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3335,28 +3318,54 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129809114</v>
+        <v>129809152</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3364,23 +3373,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3388,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495559</v>
+        <v>495696</v>
       </c>
       <c r="R26" t="n">
-        <v>7039895</v>
+        <v>7040090</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3424,11 +3429,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3552,10 +3552,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129809096</v>
+        <v>129809124</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495570</v>
+        <v>495478</v>
       </c>
       <c r="R28" t="n">
-        <v>7040065</v>
+        <v>7040087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,6 +3623,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129809131</v>
+        <v>129809096</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3660,21 +3665,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3684,10 +3689,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495455</v>
+        <v>495570</v>
       </c>
       <c r="R29" t="n">
-        <v>7040119</v>
+        <v>7040065</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,11 +3725,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3751,10 +3751,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129809124</v>
+        <v>129809131</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,21 +3762,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495478</v>
+        <v>495455</v>
       </c>
       <c r="R30" t="n">
-        <v>7040087</v>
+        <v>7040119</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,45 +3853,61 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129809105</v>
+        <v>129809137</v>
       </c>
       <c r="B31" t="n">
-        <v>91557</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495461</v>
+        <v>495739</v>
       </c>
       <c r="R31" t="n">
-        <v>7039930</v>
+        <v>7040024</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3950,30 +3966,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809094</v>
+        <v>129809105</v>
       </c>
       <c r="B32" t="n">
-        <v>91613</v>
+        <v>91557</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3981,10 +4001,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495459</v>
+        <v>495461</v>
       </c>
       <c r="R32" t="n">
-        <v>7039862</v>
+        <v>7039930</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4025,7 +4045,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4044,52 +4063,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809572</v>
+        <v>129809094</v>
       </c>
       <c r="B33" t="n">
-        <v>80215</v>
+        <v>91613</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495579</v>
+        <v>495459</v>
       </c>
       <c r="R33" t="n">
-        <v>7039969</v>
+        <v>7039862</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4124,11 +4132,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På barken av en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4139,85 +4142,68 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809141</v>
+        <v>129809567</v>
       </c>
       <c r="B34" t="n">
-        <v>80222</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495483</v>
+        <v>495594</v>
       </c>
       <c r="R34" t="n">
-        <v>7040081</v>
+        <v>7039971</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4252,6 +4238,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4260,23 +4251,48 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129809567</v>
+        <v>129809126</v>
       </c>
       <c r="B35" t="n">
         <v>57736</v>
@@ -4305,24 +4321,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495594</v>
+        <v>495467</v>
       </c>
       <c r="R35" t="n">
-        <v>7039971</v>
+        <v>7040110</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,7 +4367,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4370,89 +4378,55 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129809137</v>
+        <v>129809572</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>80215</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4462,10 +4436,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495739</v>
+        <v>495579</v>
       </c>
       <c r="R36" t="n">
-        <v>7040024</v>
+        <v>7039969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4500,56 +4474,87 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På barken av en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129809126</v>
+        <v>129809141</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>80222</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4559,10 +4564,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495467</v>
+        <v>495483</v>
       </c>
       <c r="R37" t="n">
-        <v>7040110</v>
+        <v>7040081</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4595,11 +4600,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4626,32 +4626,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129809111</v>
+        <v>129809084</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495558</v>
+        <v>495651</v>
       </c>
       <c r="R38" t="n">
-        <v>7039811</v>
+        <v>7039928</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4697,11 +4697,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4728,10 +4723,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129809138</v>
+        <v>129809111</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4739,16 +4734,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4763,10 +4758,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495613</v>
+        <v>495558</v>
       </c>
       <c r="R39" t="n">
-        <v>7039922</v>
+        <v>7039811</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4799,6 +4794,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4922,32 +4922,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809140</v>
+        <v>129809138</v>
       </c>
       <c r="B41" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495671</v>
+        <v>495613</v>
       </c>
       <c r="R41" t="n">
-        <v>7039845</v>
+        <v>7039922</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5019,52 +5019,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809561</v>
+        <v>129809140</v>
       </c>
       <c r="B42" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495774</v>
+        <v>495671</v>
       </c>
       <c r="R42" t="n">
-        <v>7040061</v>
+        <v>7039845</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5099,100 +5092,76 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129809084</v>
+        <v>129809561</v>
       </c>
       <c r="B43" t="n">
-        <v>80215</v>
+        <v>91593</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495651</v>
+        <v>495774</v>
       </c>
       <c r="R43" t="n">
-        <v>7039928</v>
+        <v>7040061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,24 +5196,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129809605</v>
+        <v>129809079</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,37 +5485,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495546</v>
+        <v>495550</v>
       </c>
       <c r="R46" t="n">
-        <v>7040104</v>
+        <v>7039807</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5550,60 +5547,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129809154</v>
+        <v>129809080</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5611,21 +5587,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5635,10 +5611,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495635</v>
+        <v>495554</v>
       </c>
       <c r="R47" t="n">
-        <v>7039937</v>
+        <v>7039840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5671,6 +5647,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5697,7 +5678,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809592</v>
+        <v>129809605</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5735,10 +5716,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495516</v>
+        <v>495546</v>
       </c>
       <c r="R48" t="n">
-        <v>7039796</v>
+        <v>7040104</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5771,11 +5752,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5828,10 +5804,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129809079</v>
+        <v>129809154</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5839,21 +5815,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5863,10 +5839,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495550</v>
+        <v>495635</v>
       </c>
       <c r="R49" t="n">
-        <v>7039807</v>
+        <v>7039937</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5899,11 +5875,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5930,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129809080</v>
+        <v>129809592</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5941,34 +5912,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495554</v>
+        <v>495516</v>
       </c>
       <c r="R50" t="n">
-        <v>7039840</v>
+        <v>7039796</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6005,7 +5979,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6014,28 +5988,54 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809142</v>
+        <v>129809606</v>
       </c>
       <c r="B51" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,34 +6043,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495682</v>
+        <v>495603</v>
       </c>
       <c r="R51" t="n">
-        <v>7039932</v>
+        <v>7040220</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6111,70 +6114,89 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809584</v>
+        <v>129809103</v>
       </c>
       <c r="B52" t="n">
-        <v>80222</v>
+        <v>83050</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495504</v>
+        <v>495680</v>
       </c>
       <c r="R52" t="n">
-        <v>7040027</v>
+        <v>7039973</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6209,92 +6231,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På barken av en smal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129809606</v>
+        <v>129809571</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6302,10 +6297,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495603</v>
+        <v>495699</v>
       </c>
       <c r="R53" t="n">
-        <v>7040220</v>
+        <v>7040018</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6340,6 +6335,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6357,22 +6357,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809103</v>
+        <v>129809142</v>
       </c>
       <c r="B54" t="n">
-        <v>83050</v>
+        <v>78094</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6401,21 +6401,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6425,10 +6425,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495680</v>
+        <v>495682</v>
       </c>
       <c r="R54" t="n">
-        <v>7039973</v>
+        <v>7039932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129809571</v>
+        <v>129809584</v>
       </c>
       <c r="B55" t="n">
-        <v>80215</v>
+        <v>80222</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6498,21 +6498,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495699</v>
+        <v>495504</v>
       </c>
       <c r="R55" t="n">
-        <v>7040018</v>
+        <v>7040027</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>På barken av en smal levande sälg.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6923,52 +6923,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129809563</v>
+        <v>129809143</v>
       </c>
       <c r="B59" t="n">
-        <v>92311</v>
+        <v>78094</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495549</v>
+        <v>495700</v>
       </c>
       <c r="R59" t="n">
-        <v>7039804</v>
+        <v>7040007</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7003,91 +6996,77 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809153</v>
+        <v>129809610</v>
       </c>
       <c r="B60" t="n">
-        <v>91613</v>
+        <v>100963</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495507</v>
+        <v>495622</v>
       </c>
       <c r="R60" t="n">
-        <v>7040063</v>
+        <v>7039966</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7128,50 +7107,56 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809133</v>
+        <v>129809150</v>
       </c>
       <c r="B61" t="n">
-        <v>80215</v>
+        <v>91589</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7181,10 +7166,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495563</v>
+        <v>495465</v>
       </c>
       <c r="R61" t="n">
-        <v>7039894</v>
+        <v>7039933</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7243,10 +7228,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129809150</v>
+        <v>129809562</v>
       </c>
       <c r="B62" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7254,34 +7239,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495465</v>
+        <v>495606</v>
       </c>
       <c r="R62" t="n">
-        <v>7039933</v>
+        <v>7040134</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7316,34 +7308,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809562</v>
+        <v>129809156</v>
       </c>
       <c r="B63" t="n">
-        <v>91593</v>
+        <v>82916</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7351,41 +7374,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495606</v>
+        <v>495664</v>
       </c>
       <c r="R63" t="n">
-        <v>7040134</v>
+        <v>7040037</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7420,65 +7436,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129809156</v>
+        <v>129809153</v>
       </c>
       <c r="B64" t="n">
-        <v>82916</v>
+        <v>91613</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7486,23 +7471,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7510,10 +7491,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495664</v>
+        <v>495507</v>
       </c>
       <c r="R64" t="n">
-        <v>7040037</v>
+        <v>7040063</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7572,10 +7553,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129809610</v>
+        <v>129809563</v>
       </c>
       <c r="B65" t="n">
-        <v>100963</v>
+        <v>92311</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7583,31 +7564,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7615,10 +7595,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495622</v>
+        <v>495549</v>
       </c>
       <c r="R65" t="n">
-        <v>7039966</v>
+        <v>7039804</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7653,6 +7633,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>I en knäckt gran.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7666,6 +7651,21 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7683,32 +7683,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129809143</v>
+        <v>129809133</v>
       </c>
       <c r="B66" t="n">
-        <v>78094</v>
+        <v>80215</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495700</v>
+        <v>495563</v>
       </c>
       <c r="R66" t="n">
-        <v>7040007</v>
+        <v>7039894</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809098</v>
+        <v>129809127</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7888,21 +7888,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495709</v>
+        <v>495608</v>
       </c>
       <c r="R68" t="n">
-        <v>7040119</v>
+        <v>7040209</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7948,6 +7948,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,7 +7979,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809099</v>
+        <v>129809098</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -8009,10 +8014,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495626</v>
+        <v>495709</v>
       </c>
       <c r="R69" t="n">
-        <v>7040099</v>
+        <v>7040119</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8071,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809129</v>
+        <v>129809099</v>
       </c>
       <c r="B70" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8082,21 +8087,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8106,10 +8111,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495522</v>
+        <v>495626</v>
       </c>
       <c r="R70" t="n">
-        <v>7039794</v>
+        <v>7040099</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8142,11 +8147,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8173,10 +8173,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809127</v>
+        <v>129809129</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8184,21 +8184,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495608</v>
+        <v>495522</v>
       </c>
       <c r="R71" t="n">
-        <v>7040209</v>
+        <v>7039794</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809585</v>
+        <v>129809568</v>
       </c>
       <c r="B73" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,28 +8383,29 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -8414,10 +8415,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495645</v>
+        <v>495618</v>
       </c>
       <c r="R73" t="n">
-        <v>7039861</v>
+        <v>7040130</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8452,13 +8453,17 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8502,7 +8507,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809568</v>
+        <v>129809122</v>
       </c>
       <c r="B74" t="n">
         <v>57736</v>
@@ -8531,24 +8536,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495618</v>
+        <v>495433</v>
       </c>
       <c r="R74" t="n">
-        <v>7040130</v>
+        <v>7039995</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8585,7 +8582,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8596,51 +8593,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809122</v>
+        <v>129809601</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8648,34 +8620,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495433</v>
+        <v>495583</v>
       </c>
       <c r="R75" t="n">
-        <v>7039995</v>
+        <v>7039969</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8710,36 +8685,57 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809601</v>
+        <v>129809607</v>
       </c>
       <c r="B76" t="n">
         <v>79081</v>
@@ -8769,7 +8765,11 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495583</v>
+        <v>495591</v>
       </c>
       <c r="R76" t="n">
-        <v>7039969</v>
+        <v>7040221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8813,6 +8813,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Med apothecier på gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8865,10 +8870,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809104</v>
+        <v>129809600</v>
       </c>
       <c r="B77" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8876,34 +8881,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495595</v>
+        <v>495604</v>
       </c>
       <c r="R77" t="n">
-        <v>7040220</v>
+        <v>7040032</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8938,34 +8946,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gran i äldre  granskog.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809607</v>
+        <v>129809104</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8973,41 +9012,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495591</v>
+        <v>495595</v>
       </c>
       <c r="R78" t="n">
-        <v>7040221</v>
+        <v>7040220</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9042,65 +9074,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Med apothecier på gran.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129809600</v>
+        <v>129809101</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9108,37 +9109,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>495604</v>
+        <v>495682</v>
       </c>
       <c r="R79" t="n">
-        <v>7040032</v>
+        <v>7039933</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9173,65 +9171,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran i äldre  granskog.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809101</v>
+        <v>129809579</v>
       </c>
       <c r="B80" t="n">
-        <v>83050</v>
+        <v>80186</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9239,34 +9206,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495682</v>
+        <v>495499</v>
       </c>
       <c r="R80" t="n">
-        <v>7039933</v>
+        <v>7040089</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9301,34 +9275,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På bark av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809579</v>
+        <v>129809130</v>
       </c>
       <c r="B81" t="n">
-        <v>80186</v>
+        <v>57896</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9336,41 +9341,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495499</v>
+        <v>495569</v>
       </c>
       <c r="R81" t="n">
-        <v>7040089</v>
+        <v>7039991</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9407,7 +9405,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9416,54 +9414,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129809130</v>
+        <v>129809585</v>
       </c>
       <c r="B82" t="n">
-        <v>57896</v>
+        <v>91589</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9471,34 +9443,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>495569</v>
+        <v>495645</v>
       </c>
       <c r="R82" t="n">
-        <v>7039991</v>
+        <v>7039861</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9533,29 +9512,50 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9993,32 +9993,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129809135</v>
+        <v>129809148</v>
       </c>
       <c r="B87" t="n">
-        <v>80215</v>
+        <v>91589</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>495536</v>
+        <v>495742</v>
       </c>
       <c r="R87" t="n">
-        <v>7040124</v>
+        <v>7040116</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10090,10 +10090,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129809580</v>
+        <v>129809081</v>
       </c>
       <c r="B88" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10101,41 +10101,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>495517</v>
+        <v>495568</v>
       </c>
       <c r="R88" t="n">
-        <v>7040108</v>
+        <v>7040032</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10172,7 +10165,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På barken av en upplyft död nedfallen sälg.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10181,54 +10174,28 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129809081</v>
+        <v>129809580</v>
       </c>
       <c r="B89" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10236,34 +10203,41 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>495568</v>
+        <v>495517</v>
       </c>
       <c r="R89" t="n">
-        <v>7040032</v>
+        <v>7040108</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10300,7 +10274,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På barken av en upplyft död nedfallen sälg.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10309,50 +10283,76 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129809148</v>
+        <v>129809135</v>
       </c>
       <c r="B90" t="n">
-        <v>91589</v>
+        <v>80215</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10362,10 +10362,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>495742</v>
+        <v>495536</v>
       </c>
       <c r="R90" t="n">
-        <v>7040116</v>
+        <v>7040124</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129809100</v>
+        <v>129809594</v>
       </c>
       <c r="B101" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11593,34 +11593,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>495592</v>
+        <v>495544</v>
       </c>
       <c r="R101" t="n">
-        <v>7039912</v>
+        <v>7039898</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11655,6 +11658,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11665,22 +11673,47 @@
       <c r="AG101" t="b">
         <v>0</v>
       </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129809594</v>
+        <v>129809598</v>
       </c>
       <c r="B102" t="n">
         <v>79081</v>
@@ -11718,10 +11751,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>495544</v>
+        <v>495684</v>
       </c>
       <c r="R102" t="n">
-        <v>7039898</v>
+        <v>7040002</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11754,11 +11787,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11811,10 +11839,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129809598</v>
+        <v>129809100</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>82916</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11822,37 +11850,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495684</v>
+        <v>495592</v>
       </c>
       <c r="R103" t="n">
-        <v>7040002</v>
+        <v>7039912</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11897,40 +11922,15 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12039,39 +12039,39 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129809581</v>
+        <v>129809586</v>
       </c>
       <c r="B105" t="n">
-        <v>80222</v>
+        <v>91589</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>495749</v>
+        <v>495477</v>
       </c>
       <c r="R105" t="n">
-        <v>7040011</v>
+        <v>7039974</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På bark på en smal sälg.</t>
+          <t>Växer i en stubbe av en knäckt gran.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12141,22 +12141,22 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12174,45 +12174,52 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129809102</v>
+        <v>129809581</v>
       </c>
       <c r="B106" t="n">
-        <v>83050</v>
+        <v>80222</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>495533</v>
+        <v>495749</v>
       </c>
       <c r="R106" t="n">
-        <v>7039800</v>
+        <v>7040011</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12247,34 +12254,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På bark på en smal sälg.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809586</v>
+        <v>129809113</v>
       </c>
       <c r="B107" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12282,41 +12320,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495477</v>
+        <v>495541</v>
       </c>
       <c r="R107" t="n">
-        <v>7039974</v>
+        <v>7039874</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12353,7 +12384,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Växer i en stubbe av en knäckt gran.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12362,51 +12393,25 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129809113</v>
+        <v>129809570</v>
       </c>
       <c r="B108" t="n">
         <v>57736</v>
@@ -12435,16 +12440,24 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>495541</v>
+        <v>495618</v>
       </c>
       <c r="R108" t="n">
-        <v>7039874</v>
+        <v>7040246</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12481,7 +12494,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12492,26 +12505,51 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129809570</v>
+        <v>129809102</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>83050</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12519,42 +12557,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>495618</v>
+        <v>495533</v>
       </c>
       <c r="R109" t="n">
-        <v>7040246</v>
+        <v>7039800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12589,11 +12619,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12602,80 +12627,56 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129809582</v>
+        <v>129809566</v>
       </c>
       <c r="B110" t="n">
-        <v>80222</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -12685,10 +12686,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>495698</v>
+        <v>495633</v>
       </c>
       <c r="R110" t="n">
-        <v>7040023</v>
+        <v>7040044</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12725,7 +12726,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12734,7 +12735,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12745,22 +12745,22 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12778,34 +12778,30 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129809085</v>
+        <v>129809151</v>
       </c>
       <c r="B111" t="n">
-        <v>80215</v>
+        <v>91613</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12813,10 +12809,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>495476</v>
+        <v>495456</v>
       </c>
       <c r="R111" t="n">
-        <v>7040074</v>
+        <v>7039928</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12875,41 +12871,52 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129809151</v>
+        <v>129809582</v>
       </c>
       <c r="B112" t="n">
-        <v>91613</v>
+        <v>80222</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>495456</v>
+        <v>495698</v>
       </c>
       <c r="R112" t="n">
-        <v>7039928</v>
+        <v>7040023</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12944,77 +12951,100 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129809566</v>
+        <v>129809085</v>
       </c>
       <c r="B113" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>495633</v>
+        <v>495476</v>
       </c>
       <c r="R113" t="n">
-        <v>7040044</v>
+        <v>7040074</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13049,11 +13079,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13062,41 +13087,16 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -13417,7 +13417,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129835889</v>
+        <v>129835890</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -13460,7 +13460,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>495434</v>
+        <v>495436</v>
       </c>
       <c r="R117" t="n">
         <v>7039822</v>
@@ -13527,7 +13527,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129835890</v>
+        <v>129835889</v>
       </c>
       <c r="B118" t="n">
         <v>57736</v>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>495436</v>
+        <v>495434</v>
       </c>
       <c r="R118" t="n">
         <v>7039822</v>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809611</v>
+        <v>129809603</v>
       </c>
       <c r="B2" t="n">
-        <v>100963</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495627</v>
+        <v>495504</v>
       </c>
       <c r="R2" t="n">
-        <v>7039995</v>
+        <v>7040017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +769,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809157</v>
+        <v>129809595</v>
       </c>
       <c r="B3" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495620</v>
+        <v>495548</v>
       </c>
       <c r="R3" t="n">
-        <v>7040063</v>
+        <v>7039913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,28 +888,54 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809603</v>
+        <v>129809157</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>82916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,37 +943,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495504</v>
+        <v>495620</v>
       </c>
       <c r="R4" t="n">
-        <v>7040017</v>
+        <v>7040063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,65 +1005,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809595</v>
+        <v>129809578</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,26 +1040,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495548</v>
+        <v>495701</v>
       </c>
       <c r="R5" t="n">
-        <v>7039913</v>
+        <v>7040014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,6 +1109,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1112,22 +1131,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1145,7 +1164,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809578</v>
+        <v>129809087</v>
       </c>
       <c r="B6" t="n">
         <v>80186</v>
@@ -1174,23 +1193,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495701</v>
+        <v>495710</v>
       </c>
       <c r="R6" t="n">
-        <v>7040014</v>
+        <v>7039992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,62 +1237,31 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809087</v>
+        <v>129809089</v>
       </c>
       <c r="B7" t="n">
         <v>80186</v>
@@ -1315,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495710</v>
+        <v>495476</v>
       </c>
       <c r="R7" t="n">
-        <v>7039992</v>
+        <v>7040074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,45 +1358,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809089</v>
+        <v>129809611</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>100967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495476</v>
+        <v>495627</v>
       </c>
       <c r="R8" t="n">
-        <v>7040074</v>
+        <v>7039995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,24 +1439,35 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809146</v>
+        <v>129809139</v>
       </c>
       <c r="B10" t="n">
-        <v>91589</v>
+        <v>80187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495659</v>
+        <v>495484</v>
       </c>
       <c r="R10" t="n">
-        <v>7039854</v>
+        <v>7040082</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,7 +1696,7 @@
         <v>129809107</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129809115</v>
+        <v>129809146</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495682</v>
+        <v>495659</v>
       </c>
       <c r="R12" t="n">
-        <v>7040065</v>
+        <v>7039854</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,11 +1861,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,45 +1887,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809082</v>
+        <v>129809573</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495470</v>
+        <v>495496</v>
       </c>
       <c r="R13" t="n">
-        <v>7039843</v>
+        <v>7040079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1969,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På bark av en levande sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1976,28 +1978,54 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809599</v>
+        <v>129809115</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,37 +2033,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495719</v>
+        <v>495682</v>
       </c>
       <c r="R14" t="n">
-        <v>7040059</v>
+        <v>7040065</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2097,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,54 +2106,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129809139</v>
+        <v>129809575</v>
       </c>
       <c r="B15" t="n">
-        <v>80187</v>
+        <v>56310</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,34 +2135,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>206004</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495484</v>
+        <v>495639</v>
       </c>
       <c r="R15" t="n">
-        <v>7040082</v>
+        <v>7039976</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,6 +2213,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2206,57 +2226,63 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129809573</v>
+        <v>129809599</v>
       </c>
       <c r="B16" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2264,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495496</v>
+        <v>495719</v>
       </c>
       <c r="R16" t="n">
-        <v>7040079</v>
+        <v>7040059</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2330,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,27 +2345,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2492,10 +2518,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129809575</v>
+        <v>129809082</v>
       </c>
       <c r="B18" t="n">
-        <v>56310</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,50 +2529,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495639</v>
+        <v>495470</v>
       </c>
       <c r="R18" t="n">
-        <v>7039976</v>
+        <v>7039843</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,7 +2593,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,36 +2604,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809144</v>
+        <v>129809114</v>
       </c>
       <c r="B19" t="n">
-        <v>78094</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495584</v>
+        <v>495559</v>
       </c>
       <c r="R19" t="n">
-        <v>7040207</v>
+        <v>7039895</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,6 +2691,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2717,10 +2722,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809076</v>
+        <v>129809144</v>
       </c>
       <c r="B20" t="n">
-        <v>91593</v>
+        <v>78094</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,21 +2733,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2757,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495663</v>
+        <v>495584</v>
       </c>
       <c r="R20" t="n">
-        <v>7040097</v>
+        <v>7040207</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809114</v>
+        <v>129809076</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>91597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,21 +2927,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2946,10 +2951,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495559</v>
+        <v>495663</v>
       </c>
       <c r="R22" t="n">
-        <v>7039895</v>
+        <v>7040097</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2982,11 +2987,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,34 +3013,30 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809134</v>
+        <v>129809152</v>
       </c>
       <c r="B23" t="n">
-        <v>80215</v>
+        <v>91617</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3048,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495561</v>
+        <v>495696</v>
       </c>
       <c r="R23" t="n">
-        <v>7039987</v>
+        <v>7040090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3110,48 +3106,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809602</v>
+        <v>129809134</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495479</v>
+        <v>495561</v>
       </c>
       <c r="R24" t="n">
-        <v>7039967</v>
+        <v>7039987</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,51 +3185,25 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129809596</v>
+        <v>129809602</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3274,10 +3241,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495570</v>
+        <v>495479</v>
       </c>
       <c r="R25" t="n">
-        <v>7039935</v>
+        <v>7039967</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129809152</v>
+        <v>129809596</v>
       </c>
       <c r="B26" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,30 +3340,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495696</v>
+        <v>495570</v>
       </c>
       <c r="R26" t="n">
-        <v>7040090</v>
+        <v>7039935</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3437,28 +3411,54 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129809147</v>
+        <v>129809096</v>
       </c>
       <c r="B27" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495722</v>
+        <v>495570</v>
       </c>
       <c r="R27" t="n">
-        <v>7040115</v>
+        <v>7040065</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129809124</v>
+        <v>129809131</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495478</v>
+        <v>495455</v>
       </c>
       <c r="R28" t="n">
-        <v>7040087</v>
+        <v>7040119</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129809096</v>
+        <v>129809147</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495570</v>
+        <v>495722</v>
       </c>
       <c r="R29" t="n">
-        <v>7040065</v>
+        <v>7040115</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129809131</v>
+        <v>129809124</v>
       </c>
       <c r="B30" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,21 +3762,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495455</v>
+        <v>495478</v>
       </c>
       <c r="R30" t="n">
-        <v>7040119</v>
+        <v>7040087</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,48 +3853,39 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129809137</v>
+        <v>129809572</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>80215</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3904,10 +3895,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495739</v>
+        <v>495579</v>
       </c>
       <c r="R31" t="n">
-        <v>7040024</v>
+        <v>7039969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3942,34 +3933,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På barken av en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809105</v>
+        <v>129809141</v>
       </c>
       <c r="B32" t="n">
-        <v>91557</v>
+        <v>80222</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,21 +3999,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4001,10 +4023,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495461</v>
+        <v>495483</v>
       </c>
       <c r="R32" t="n">
-        <v>7039930</v>
+        <v>7040081</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4063,10 +4085,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809094</v>
+        <v>129809137</v>
       </c>
       <c r="B33" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,30 +4096,50 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495459</v>
+        <v>495739</v>
       </c>
       <c r="R33" t="n">
-        <v>7039862</v>
+        <v>7040024</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4138,7 +4180,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4394,10 +4435,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129809572</v>
+        <v>129809105</v>
       </c>
       <c r="B36" t="n">
-        <v>80215</v>
+        <v>91561</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4405,41 +4446,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495579</v>
+        <v>495461</v>
       </c>
       <c r="R36" t="n">
-        <v>7039969</v>
+        <v>7039930</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4474,89 +4508,54 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På barken av en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129809141</v>
+        <v>129809094</v>
       </c>
       <c r="B37" t="n">
-        <v>80222</v>
+        <v>91617</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4564,10 +4563,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495483</v>
+        <v>495459</v>
       </c>
       <c r="R37" t="n">
-        <v>7040081</v>
+        <v>7039862</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4608,6 +4607,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129809084</v>
+        <v>129809140</v>
       </c>
       <c r="B38" t="n">
-        <v>80215</v>
+        <v>92050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495651</v>
+        <v>495671</v>
       </c>
       <c r="R38" t="n">
-        <v>7039928</v>
+        <v>7039845</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4723,10 +4723,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129809111</v>
+        <v>129809561</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>91597</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4734,34 +4734,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495558</v>
+        <v>495774</v>
       </c>
       <c r="R39" t="n">
-        <v>7039811</v>
+        <v>7040061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4798,7 +4805,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>I en upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4807,63 +4814,92 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129809083</v>
+        <v>129809604</v>
       </c>
       <c r="B40" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495476</v>
+        <v>495501</v>
       </c>
       <c r="R40" t="n">
-        <v>7040074</v>
+        <v>7040069</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4904,50 +4940,76 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809138</v>
+        <v>129809084</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>80215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4957,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495613</v>
+        <v>495651</v>
       </c>
       <c r="R41" t="n">
-        <v>7039922</v>
+        <v>7039928</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5019,32 +5081,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809140</v>
+        <v>129809111</v>
       </c>
       <c r="B42" t="n">
-        <v>92046</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5054,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495671</v>
+        <v>495558</v>
       </c>
       <c r="R42" t="n">
-        <v>7039845</v>
+        <v>7039811</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5090,6 +5152,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5116,52 +5183,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129809561</v>
+        <v>129809083</v>
       </c>
       <c r="B43" t="n">
-        <v>91593</v>
+        <v>56926</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495774</v>
+        <v>495476</v>
       </c>
       <c r="R43" t="n">
-        <v>7040061</v>
+        <v>7040074</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,65 +5256,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129809604</v>
+        <v>129809138</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5262,37 +5291,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495501</v>
+        <v>495613</v>
       </c>
       <c r="R44" t="n">
-        <v>7040069</v>
+        <v>7039922</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5333,44 +5359,18 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5380,7 +5380,7 @@
         <v>129809091</v>
       </c>
       <c r="B45" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,10 +5474,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129809079</v>
+        <v>129809605</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,34 +5485,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495550</v>
+        <v>495546</v>
       </c>
       <c r="R46" t="n">
-        <v>7039807</v>
+        <v>7040104</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5547,39 +5550,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129809080</v>
+        <v>129809154</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5587,21 +5611,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5611,10 +5635,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495554</v>
+        <v>495635</v>
       </c>
       <c r="R47" t="n">
-        <v>7039840</v>
+        <v>7039937</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5647,11 +5671,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5678,7 +5697,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809605</v>
+        <v>129809592</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5716,10 +5735,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495546</v>
+        <v>495516</v>
       </c>
       <c r="R48" t="n">
-        <v>7040104</v>
+        <v>7039796</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5752,6 +5771,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5804,10 +5828,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129809154</v>
+        <v>129809079</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5815,21 +5839,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5839,10 +5863,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495635</v>
+        <v>495550</v>
       </c>
       <c r="R49" t="n">
-        <v>7039937</v>
+        <v>7039807</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5875,6 +5899,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5930,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129809592</v>
+        <v>129809080</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5912,37 +5941,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495516</v>
+        <v>495554</v>
       </c>
       <c r="R50" t="n">
-        <v>7039796</v>
+        <v>7039840</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5979,7 +6005,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,54 +6014,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809606</v>
+        <v>129809103</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,37 +6043,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495603</v>
+        <v>495680</v>
       </c>
       <c r="R51" t="n">
-        <v>7040220</v>
+        <v>7039973</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6114,54 +6111,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809103</v>
+        <v>129809606</v>
       </c>
       <c r="B52" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6169,34 +6140,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495680</v>
+        <v>495603</v>
       </c>
       <c r="R52" t="n">
-        <v>7039973</v>
+        <v>7040220</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6237,28 +6211,54 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129809571</v>
+        <v>129809584</v>
       </c>
       <c r="B53" t="n">
-        <v>80215</v>
+        <v>80222</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6266,21 +6266,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495699</v>
+        <v>495504</v>
       </c>
       <c r="R53" t="n">
-        <v>7040018</v>
+        <v>7040027</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>På barken av en smal levande sälg.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6390,45 +6390,52 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809142</v>
+        <v>129809571</v>
       </c>
       <c r="B54" t="n">
-        <v>78094</v>
+        <v>80215</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495682</v>
+        <v>495699</v>
       </c>
       <c r="R54" t="n">
-        <v>7039932</v>
+        <v>7040018</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6463,76 +6470,100 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129809584</v>
+        <v>129809142</v>
       </c>
       <c r="B55" t="n">
-        <v>80222</v>
+        <v>78094</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495504</v>
+        <v>495682</v>
       </c>
       <c r="R55" t="n">
-        <v>7040027</v>
+        <v>7039932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6567,55 +6598,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På barken av en smal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129809143</v>
+        <v>129809150</v>
       </c>
       <c r="B59" t="n">
-        <v>78094</v>
+        <v>91593</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,21 +6934,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495700</v>
+        <v>495465</v>
       </c>
       <c r="R59" t="n">
-        <v>7040007</v>
+        <v>7039933</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7020,53 +7020,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809610</v>
+        <v>129809153</v>
       </c>
       <c r="B60" t="n">
-        <v>100963</v>
+        <v>91617</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495622</v>
+        <v>495507</v>
       </c>
       <c r="R60" t="n">
-        <v>7039966</v>
+        <v>7040063</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7107,56 +7095,50 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809150</v>
+        <v>129809133</v>
       </c>
       <c r="B61" t="n">
-        <v>91589</v>
+        <v>80215</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7166,10 +7148,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495465</v>
+        <v>495563</v>
       </c>
       <c r="R61" t="n">
-        <v>7039933</v>
+        <v>7039894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7228,10 +7210,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129809562</v>
+        <v>129809143</v>
       </c>
       <c r="B62" t="n">
-        <v>91593</v>
+        <v>78094</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7239,41 +7221,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495606</v>
+        <v>495700</v>
       </c>
       <c r="R62" t="n">
-        <v>7040134</v>
+        <v>7040007</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7308,65 +7283,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809156</v>
+        <v>129809562</v>
       </c>
       <c r="B63" t="n">
-        <v>82916</v>
+        <v>91597</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7374,34 +7318,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495664</v>
+        <v>495606</v>
       </c>
       <c r="R63" t="n">
-        <v>7040037</v>
+        <v>7040134</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7436,34 +7387,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129809153</v>
+        <v>129809156</v>
       </c>
       <c r="B64" t="n">
-        <v>91613</v>
+        <v>82916</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7471,19 +7453,23 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7491,10 +7477,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495507</v>
+        <v>495664</v>
       </c>
       <c r="R64" t="n">
-        <v>7040063</v>
+        <v>7040037</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7556,7 +7542,7 @@
         <v>129809563</v>
       </c>
       <c r="B65" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7683,10 +7669,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129809133</v>
+        <v>129809610</v>
       </c>
       <c r="B66" t="n">
-        <v>80215</v>
+        <v>100967</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7694,34 +7680,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495563</v>
+        <v>495622</v>
       </c>
       <c r="R66" t="n">
-        <v>7039894</v>
+        <v>7039966</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7762,18 +7756,24 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809127</v>
+        <v>129809098</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7888,21 +7888,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495608</v>
+        <v>495709</v>
       </c>
       <c r="R68" t="n">
-        <v>7040209</v>
+        <v>7040119</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7948,11 +7948,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7979,7 +7974,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809098</v>
+        <v>129809099</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -8014,10 +8009,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495709</v>
+        <v>495626</v>
       </c>
       <c r="R69" t="n">
-        <v>7040119</v>
+        <v>7040099</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8076,10 +8071,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809099</v>
+        <v>129809127</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8087,21 +8082,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8111,10 +8106,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495626</v>
+        <v>495608</v>
       </c>
       <c r="R70" t="n">
-        <v>7040099</v>
+        <v>7040209</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8147,6 +8142,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8278,7 +8278,7 @@
         <v>129809090</v>
       </c>
       <c r="B72" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809568</v>
+        <v>129809130</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,42 +8383,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495618</v>
+        <v>495569</v>
       </c>
       <c r="R73" t="n">
-        <v>7040130</v>
+        <v>7039991</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8455,7 +8447,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8466,48 +8458,23 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809122</v>
+        <v>129809568</v>
       </c>
       <c r="B74" t="n">
         <v>57736</v>
@@ -8536,16 +8503,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495433</v>
+        <v>495618</v>
       </c>
       <c r="R74" t="n">
-        <v>7039995</v>
+        <v>7040130</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8582,7 +8557,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8593,26 +8568,51 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809601</v>
+        <v>129809122</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8620,37 +8620,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495583</v>
+        <v>495433</v>
       </c>
       <c r="R75" t="n">
-        <v>7039969</v>
+        <v>7039995</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8685,60 +8682,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809607</v>
+        <v>129809585</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,28 +8722,28 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8777,10 +8753,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495591</v>
+        <v>495645</v>
       </c>
       <c r="R76" t="n">
-        <v>7040221</v>
+        <v>7039861</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8815,11 +8791,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Med apothecier på gran.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8847,12 +8818,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8870,10 +8841,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809600</v>
+        <v>129809579</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,26 +8852,30 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8908,10 +8883,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495604</v>
+        <v>495499</v>
       </c>
       <c r="R77" t="n">
-        <v>7040032</v>
+        <v>7040089</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8948,7 +8923,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran i äldre  granskog.</t>
+          <t>På bark av en levande sälg.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8968,22 +8943,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9195,10 +9170,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809579</v>
+        <v>129809601</v>
       </c>
       <c r="B80" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9206,30 +9181,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9237,10 +9208,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495499</v>
+        <v>495583</v>
       </c>
       <c r="R80" t="n">
-        <v>7040089</v>
+        <v>7039969</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9275,11 +9246,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På bark av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9297,22 +9263,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9330,10 +9296,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809130</v>
+        <v>129809607</v>
       </c>
       <c r="B81" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9341,34 +9307,41 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495569</v>
+        <v>495591</v>
       </c>
       <c r="R81" t="n">
-        <v>7039991</v>
+        <v>7040221</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9405,7 +9378,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Med apothecier på gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9414,28 +9387,54 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129809585</v>
+        <v>129809600</v>
       </c>
       <c r="B82" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9443,30 +9442,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9474,10 +9469,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>495645</v>
+        <v>495604</v>
       </c>
       <c r="R82" t="n">
-        <v>7039861</v>
+        <v>7040032</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9512,6 +9507,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gran i äldre  granskog.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
         <v>129809106</v>
       </c>
       <c r="B83" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9993,10 +9993,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129809148</v>
+        <v>129809081</v>
       </c>
       <c r="B87" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>495742</v>
+        <v>495568</v>
       </c>
       <c r="R87" t="n">
-        <v>7040116</v>
+        <v>7040032</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10064,6 +10064,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10090,10 +10095,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129809081</v>
+        <v>129809148</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10101,21 +10106,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10125,10 +10130,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>495568</v>
+        <v>495742</v>
       </c>
       <c r="R88" t="n">
-        <v>7040032</v>
+        <v>7040116</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10161,11 +10166,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10427,7 +10427,7 @@
         <v>129809587</v>
       </c>
       <c r="B91" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11034,10 +11034,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129809093</v>
+        <v>129809593</v>
       </c>
       <c r="B96" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11045,30 +11045,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>495655</v>
+        <v>495530</v>
       </c>
       <c r="R96" t="n">
-        <v>7040108</v>
+        <v>7039833</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11109,28 +11116,54 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129809593</v>
+        <v>129809093</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>91617</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11138,37 +11171,30 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>495530</v>
+        <v>495655</v>
       </c>
       <c r="R97" t="n">
-        <v>7039833</v>
+        <v>7040108</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11209,54 +11235,28 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129809569</v>
+        <v>129809088</v>
       </c>
       <c r="B98" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11264,42 +11264,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>495637</v>
+        <v>495461</v>
       </c>
       <c r="R98" t="n">
-        <v>7040173</v>
+        <v>7039960</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11334,11 +11326,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs några meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11347,48 +11334,23 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129809088</v>
+        <v>129809086</v>
       </c>
       <c r="B99" t="n">
         <v>80186</v>
@@ -11423,10 +11385,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>495461</v>
+        <v>495579</v>
       </c>
       <c r="R99" t="n">
-        <v>7039960</v>
+        <v>7040079</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11485,10 +11447,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129809086</v>
+        <v>129809569</v>
       </c>
       <c r="B100" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11496,34 +11458,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>495579</v>
+        <v>495637</v>
       </c>
       <c r="R100" t="n">
-        <v>7040079</v>
+        <v>7040173</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11558,6 +11528,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs några meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11566,26 +11541,51 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129809594</v>
+        <v>129809116</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11593,37 +11593,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>495544</v>
+        <v>495435</v>
       </c>
       <c r="R101" t="n">
-        <v>7039898</v>
+        <v>7039823</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11660,7 +11657,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11669,54 +11666,28 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129809598</v>
+        <v>129809100</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>82916</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11724,37 +11695,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>495684</v>
+        <v>495592</v>
       </c>
       <c r="R102" t="n">
-        <v>7040002</v>
+        <v>7039912</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11799,50 +11767,25 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129809100</v>
+        <v>129809594</v>
       </c>
       <c r="B103" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11850,34 +11793,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495592</v>
+        <v>495544</v>
       </c>
       <c r="R103" t="n">
-        <v>7039912</v>
+        <v>7039898</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11912,6 +11858,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11922,25 +11873,50 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129809116</v>
+        <v>129809598</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11948,34 +11924,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>495435</v>
+        <v>495684</v>
       </c>
       <c r="R104" t="n">
-        <v>7039823</v>
+        <v>7040002</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12010,39 +11989,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129809586</v>
+        <v>129809102</v>
       </c>
       <c r="B105" t="n">
-        <v>91589</v>
+        <v>83050</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12050,41 +12050,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>495477</v>
+        <v>495533</v>
       </c>
       <c r="R105" t="n">
-        <v>7039974</v>
+        <v>7039800</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12119,55 +12112,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Växer i en stubbe av en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12309,10 +12271,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809113</v>
+        <v>129809586</v>
       </c>
       <c r="B107" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12320,34 +12282,41 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495541</v>
+        <v>495477</v>
       </c>
       <c r="R107" t="n">
-        <v>7039874</v>
+        <v>7039974</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12384,7 +12353,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Växer i en stubbe av en knäckt gran.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12393,25 +12362,51 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129809570</v>
+        <v>129809113</v>
       </c>
       <c r="B108" t="n">
         <v>57736</v>
@@ -12440,24 +12435,16 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>495618</v>
+        <v>495541</v>
       </c>
       <c r="R108" t="n">
-        <v>7040246</v>
+        <v>7039874</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12494,7 +12481,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12505,51 +12492,26 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129809102</v>
+        <v>129809570</v>
       </c>
       <c r="B109" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12557,34 +12519,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>495533</v>
+        <v>495618</v>
       </c>
       <c r="R109" t="n">
-        <v>7039800</v>
+        <v>7040246</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12619,6 +12589,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12627,16 +12602,41 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12781,7 +12781,7 @@
         <v>129809151</v>
       </c>
       <c r="B111" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -932,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809157</v>
+        <v>129809087</v>
       </c>
       <c r="B4" t="n">
-        <v>82916</v>
+        <v>80186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495620</v>
+        <v>495710</v>
       </c>
       <c r="R4" t="n">
-        <v>7040063</v>
+        <v>7039992</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809087</v>
+        <v>129809089</v>
       </c>
       <c r="B6" t="n">
         <v>80186</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495710</v>
+        <v>495476</v>
       </c>
       <c r="R6" t="n">
-        <v>7039992</v>
+        <v>7040074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809089</v>
+        <v>129809157</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>82918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495476</v>
+        <v>495620</v>
       </c>
       <c r="R7" t="n">
-        <v>7040074</v>
+        <v>7040063</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,7 +1361,7 @@
         <v>129809611</v>
       </c>
       <c r="B8" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809139</v>
+        <v>129809599</v>
       </c>
       <c r="B10" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,34 +1607,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495484</v>
+        <v>495719</v>
       </c>
       <c r="R10" t="n">
-        <v>7040082</v>
+        <v>7040059</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,69 +1672,107 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129809107</v>
+        <v>129809573</v>
       </c>
       <c r="B11" t="n">
-        <v>91597</v>
+        <v>80215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495592</v>
+        <v>495496</v>
       </c>
       <c r="R11" t="n">
-        <v>7040205</v>
+        <v>7040079</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,69 +1807,107 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På bark av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129809146</v>
+        <v>129809583</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>80222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495659</v>
+        <v>495575</v>
       </c>
       <c r="R12" t="n">
-        <v>7039854</v>
+        <v>7039971</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,76 +1942,100 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På barken av en död sälglåga.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809573</v>
+        <v>129809139</v>
       </c>
       <c r="B13" t="n">
-        <v>80215</v>
+        <v>80187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495496</v>
+        <v>495484</v>
       </c>
       <c r="R13" t="n">
-        <v>7040079</v>
+        <v>7040082</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,65 +2070,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På bark av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809115</v>
+        <v>129809107</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,21 +2105,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2129,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495682</v>
+        <v>495592</v>
       </c>
       <c r="R14" t="n">
-        <v>7040065</v>
+        <v>7040205</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2093,11 +2165,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,10 +2191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129809575</v>
+        <v>129809146</v>
       </c>
       <c r="B15" t="n">
-        <v>56310</v>
+        <v>91595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,50 +2202,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495639</v>
+        <v>495659</v>
       </c>
       <c r="R15" t="n">
-        <v>7039976</v>
+        <v>7039854</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,11 +2264,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2226,36 +2272,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129809599</v>
+        <v>129809575</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>56310</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,37 +2299,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495719</v>
+        <v>495639</v>
       </c>
       <c r="R16" t="n">
-        <v>7040059</v>
+        <v>7039976</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,7 +2379,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,33 +2388,17 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2383,52 +2416,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129809583</v>
+        <v>129809115</v>
       </c>
       <c r="B17" t="n">
-        <v>80222</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495575</v>
+        <v>495682</v>
       </c>
       <c r="R17" t="n">
-        <v>7039971</v>
+        <v>7040065</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2491,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På barken av en död sälglåga.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,44 +2500,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809114</v>
+        <v>129809159</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>83044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495559</v>
+        <v>495530</v>
       </c>
       <c r="R19" t="n">
-        <v>7039895</v>
+        <v>7040111</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,11 +2691,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809144</v>
+        <v>129809602</v>
       </c>
       <c r="B20" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2733,34 +2728,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495584</v>
+        <v>495479</v>
       </c>
       <c r="R20" t="n">
-        <v>7040207</v>
+        <v>7039967</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,28 +2799,54 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129809159</v>
+        <v>129809596</v>
       </c>
       <c r="B21" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,34 +2854,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495530</v>
+        <v>495570</v>
       </c>
       <c r="R21" t="n">
-        <v>7040111</v>
+        <v>7039935</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,28 +2925,54 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809076</v>
+        <v>129809152</v>
       </c>
       <c r="B22" t="n">
-        <v>91597</v>
+        <v>91619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,23 +2980,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2951,10 +3000,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495663</v>
+        <v>495696</v>
       </c>
       <c r="R22" t="n">
-        <v>7040097</v>
+        <v>7040090</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3013,30 +3062,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809152</v>
+        <v>129809134</v>
       </c>
       <c r="B23" t="n">
-        <v>91617</v>
+        <v>80215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3044,10 +3097,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495696</v>
+        <v>495561</v>
       </c>
       <c r="R23" t="n">
-        <v>7040090</v>
+        <v>7039987</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3106,32 +3159,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809134</v>
+        <v>129809076</v>
       </c>
       <c r="B24" t="n">
-        <v>80215</v>
+        <v>91599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495561</v>
+        <v>495663</v>
       </c>
       <c r="R24" t="n">
-        <v>7039987</v>
+        <v>7040097</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129809602</v>
+        <v>129809144</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,37 +3267,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495479</v>
+        <v>495584</v>
       </c>
       <c r="R25" t="n">
-        <v>7039967</v>
+        <v>7040207</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,54 +3335,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129809596</v>
+        <v>129809114</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,37 +3364,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495570</v>
+        <v>495559</v>
       </c>
       <c r="R26" t="n">
-        <v>7039935</v>
+        <v>7039895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,50 +3426,29 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3657,7 +3657,7 @@
         <v>129809147</v>
       </c>
       <c r="B29" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129809572</v>
+        <v>129809105</v>
       </c>
       <c r="B31" t="n">
-        <v>80215</v>
+        <v>91563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,41 +3864,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495579</v>
+        <v>495461</v>
       </c>
       <c r="R31" t="n">
-        <v>7039969</v>
+        <v>7039930</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,89 +3926,54 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På barken av en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809141</v>
+        <v>129809094</v>
       </c>
       <c r="B32" t="n">
-        <v>80222</v>
+        <v>91619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4023,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495483</v>
+        <v>495459</v>
       </c>
       <c r="R32" t="n">
-        <v>7040081</v>
+        <v>7039862</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4067,6 +4025,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4085,10 +4044,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809137</v>
+        <v>129809567</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4096,16 +4055,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4113,20 +4072,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4136,10 +4087,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495739</v>
+        <v>495594</v>
       </c>
       <c r="R33" t="n">
-        <v>7040024</v>
+        <v>7039971</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,6 +4125,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4182,23 +4138,48 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809567</v>
+        <v>129809126</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -4227,24 +4208,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495594</v>
+        <v>495467</v>
       </c>
       <c r="R34" t="n">
-        <v>7039971</v>
+        <v>7040110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4281,7 +4254,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4292,86 +4265,68 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129809126</v>
+        <v>129809572</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495467</v>
+        <v>495579</v>
       </c>
       <c r="R35" t="n">
-        <v>7040110</v>
+        <v>7039969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4408,7 +4363,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På barken av en sälglåga.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4417,28 +4372,54 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129809105</v>
+        <v>129809141</v>
       </c>
       <c r="B36" t="n">
-        <v>91561</v>
+        <v>80222</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4446,21 +4427,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4470,10 +4451,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495461</v>
+        <v>495483</v>
       </c>
       <c r="R36" t="n">
-        <v>7039930</v>
+        <v>7040081</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4532,10 +4513,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129809094</v>
+        <v>129809137</v>
       </c>
       <c r="B37" t="n">
-        <v>91617</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4543,30 +4524,50 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495459</v>
+        <v>495739</v>
       </c>
       <c r="R37" t="n">
-        <v>7039862</v>
+        <v>7040024</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4607,7 +4608,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>129809140</v>
       </c>
       <c r="B38" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>129809561</v>
       </c>
       <c r="B39" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129809604</v>
+        <v>129809111</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4869,37 +4869,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495501</v>
+        <v>495558</v>
       </c>
       <c r="R40" t="n">
-        <v>7040069</v>
+        <v>7039811</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4934,60 +4931,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809084</v>
+        <v>129809083</v>
       </c>
       <c r="B41" t="n">
-        <v>80215</v>
+        <v>56926</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,21 +4971,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5019,10 +4995,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495651</v>
+        <v>495476</v>
       </c>
       <c r="R41" t="n">
-        <v>7039928</v>
+        <v>7040074</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5081,10 +5057,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809111</v>
+        <v>129809604</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,34 +5068,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495558</v>
+        <v>495501</v>
       </c>
       <c r="R42" t="n">
-        <v>7039811</v>
+        <v>7040069</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,39 +5133,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129809083</v>
+        <v>129809084</v>
       </c>
       <c r="B43" t="n">
-        <v>56926</v>
+        <v>80215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5194,21 +5194,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495476</v>
+        <v>495651</v>
       </c>
       <c r="R43" t="n">
-        <v>7040074</v>
+        <v>7039928</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5377,10 +5377,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129809091</v>
+        <v>129809605</v>
       </c>
       <c r="B45" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5388,34 +5388,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495490</v>
+        <v>495546</v>
       </c>
       <c r="R45" t="n">
-        <v>7039928</v>
+        <v>7040104</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5456,25 +5459,51 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129809605</v>
+        <v>129809154</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5503,19 +5532,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495546</v>
+        <v>495635</v>
       </c>
       <c r="R46" t="n">
-        <v>7040104</v>
+        <v>7039937</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5556,51 +5582,25 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129809154</v>
+        <v>129809592</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5629,16 +5629,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495635</v>
+        <v>495516</v>
       </c>
       <c r="R47" t="n">
-        <v>7039937</v>
+        <v>7039796</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5673,34 +5676,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809592</v>
+        <v>129809091</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,37 +5742,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495516</v>
+        <v>495490</v>
       </c>
       <c r="R48" t="n">
-        <v>7039796</v>
+        <v>7039928</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5773,55 +5804,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809103</v>
+        <v>129809606</v>
       </c>
       <c r="B51" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,34 +6043,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495680</v>
+        <v>495603</v>
       </c>
       <c r="R51" t="n">
-        <v>7039973</v>
+        <v>7040220</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6111,55 +6114,85 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809606</v>
+        <v>129809571</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6167,10 +6200,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495603</v>
+        <v>495699</v>
       </c>
       <c r="R52" t="n">
-        <v>7040220</v>
+        <v>7040018</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6205,6 +6238,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6222,22 +6260,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6390,52 +6428,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809571</v>
+        <v>129809103</v>
       </c>
       <c r="B54" t="n">
-        <v>80215</v>
+        <v>83052</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495699</v>
+        <v>495680</v>
       </c>
       <c r="R54" t="n">
-        <v>7040018</v>
+        <v>7039973</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6470,55 +6501,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6622,10 +6622,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129809155</v>
+        <v>129809078</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6633,21 +6633,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495737</v>
+        <v>495653</v>
       </c>
       <c r="R56" t="n">
-        <v>7040098</v>
+        <v>7039924</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6693,6 +6693,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6719,7 +6724,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129809078</v>
+        <v>129809110</v>
       </c>
       <c r="B57" t="n">
         <v>57736</v>
@@ -6754,10 +6759,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495653</v>
+        <v>495565</v>
       </c>
       <c r="R57" t="n">
-        <v>7039924</v>
+        <v>7039805</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6821,10 +6826,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129809110</v>
+        <v>129809155</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6832,21 +6837,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6856,10 +6861,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495565</v>
+        <v>495737</v>
       </c>
       <c r="R58" t="n">
-        <v>7039805</v>
+        <v>7040098</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6892,11 +6897,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6923,10 +6923,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129809150</v>
+        <v>129809153</v>
       </c>
       <c r="B59" t="n">
-        <v>91593</v>
+        <v>91619</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,23 +6934,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6958,10 +6954,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495465</v>
+        <v>495507</v>
       </c>
       <c r="R59" t="n">
-        <v>7039933</v>
+        <v>7040063</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7020,30 +7016,34 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809153</v>
+        <v>129809133</v>
       </c>
       <c r="B60" t="n">
-        <v>91617</v>
+        <v>80215</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495507</v>
+        <v>495563</v>
       </c>
       <c r="R60" t="n">
-        <v>7040063</v>
+        <v>7039894</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809133</v>
+        <v>129809150</v>
       </c>
       <c r="B61" t="n">
-        <v>80215</v>
+        <v>91595</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495563</v>
+        <v>495465</v>
       </c>
       <c r="R61" t="n">
-        <v>7039894</v>
+        <v>7039933</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7210,10 +7210,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129809143</v>
+        <v>129809562</v>
       </c>
       <c r="B62" t="n">
-        <v>78094</v>
+        <v>91599</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7221,34 +7221,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495700</v>
+        <v>495606</v>
       </c>
       <c r="R62" t="n">
-        <v>7040007</v>
+        <v>7040134</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7283,34 +7290,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809562</v>
+        <v>129809156</v>
       </c>
       <c r="B63" t="n">
-        <v>91597</v>
+        <v>82918</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7318,41 +7356,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495606</v>
+        <v>495664</v>
       </c>
       <c r="R63" t="n">
-        <v>7040134</v>
+        <v>7040037</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7387,65 +7418,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129809156</v>
+        <v>129809143</v>
       </c>
       <c r="B64" t="n">
-        <v>82916</v>
+        <v>78094</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7453,21 +7453,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7477,10 +7477,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495664</v>
+        <v>495700</v>
       </c>
       <c r="R64" t="n">
-        <v>7040037</v>
+        <v>7040007</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129809563</v>
+        <v>129809610</v>
       </c>
       <c r="B65" t="n">
-        <v>92315</v>
+        <v>100969</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7550,30 +7550,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7581,10 +7582,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495549</v>
+        <v>495622</v>
       </c>
       <c r="R65" t="n">
-        <v>7039804</v>
+        <v>7039966</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7619,11 +7620,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>I en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7637,21 +7633,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7669,10 +7650,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129809610</v>
+        <v>129809563</v>
       </c>
       <c r="B66" t="n">
-        <v>100967</v>
+        <v>92317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7680,31 +7661,30 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7712,10 +7692,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495622</v>
+        <v>495549</v>
       </c>
       <c r="R66" t="n">
-        <v>7039966</v>
+        <v>7039804</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7750,6 +7730,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>I en knäckt gran.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7763,6 +7748,21 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129809158</v>
+        <v>129809098</v>
       </c>
       <c r="B67" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,21 +7791,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495531</v>
+        <v>495709</v>
       </c>
       <c r="R67" t="n">
-        <v>7040125</v>
+        <v>7040119</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7877,7 +7877,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809098</v>
+        <v>129809099</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495709</v>
+        <v>495626</v>
       </c>
       <c r="R68" t="n">
-        <v>7040119</v>
+        <v>7040099</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7974,10 +7974,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809099</v>
+        <v>129809127</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7985,21 +7985,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495626</v>
+        <v>495608</v>
       </c>
       <c r="R69" t="n">
-        <v>7040099</v>
+        <v>7040209</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8045,6 +8045,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8071,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809127</v>
+        <v>129809129</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8082,21 +8087,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8106,10 +8111,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495608</v>
+        <v>495522</v>
       </c>
       <c r="R70" t="n">
-        <v>7040209</v>
+        <v>7039794</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8146,7 +8151,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8173,32 +8178,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809129</v>
+        <v>129809090</v>
       </c>
       <c r="B71" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8208,10 +8213,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495522</v>
+        <v>495544</v>
       </c>
       <c r="R71" t="n">
-        <v>7039794</v>
+        <v>7040035</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8244,11 +8249,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8275,32 +8275,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129809090</v>
+        <v>129809158</v>
       </c>
       <c r="B72" t="n">
-        <v>98778</v>
+        <v>83044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>495544</v>
+        <v>495531</v>
       </c>
       <c r="R72" t="n">
-        <v>7040035</v>
+        <v>7040125</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809130</v>
+        <v>129809568</v>
       </c>
       <c r="B73" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,34 +8383,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495569</v>
+        <v>495618</v>
       </c>
       <c r="R73" t="n">
-        <v>7039991</v>
+        <v>7040130</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8447,7 +8455,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8458,23 +8466,48 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809568</v>
+        <v>129809122</v>
       </c>
       <c r="B74" t="n">
         <v>57736</v>
@@ -8503,24 +8536,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495618</v>
+        <v>495433</v>
       </c>
       <c r="R74" t="n">
-        <v>7040130</v>
+        <v>7039995</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8557,7 +8582,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8568,51 +8593,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809122</v>
+        <v>129809601</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8620,34 +8620,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495433</v>
+        <v>495583</v>
       </c>
       <c r="R75" t="n">
-        <v>7039995</v>
+        <v>7039969</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8682,39 +8685,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809585</v>
+        <v>129809607</v>
       </c>
       <c r="B76" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8722,28 +8746,28 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8753,10 +8777,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495645</v>
+        <v>495591</v>
       </c>
       <c r="R76" t="n">
-        <v>7039861</v>
+        <v>7040221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8791,6 +8815,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Med apothecier på gran.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8818,12 +8847,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8841,10 +8870,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809579</v>
+        <v>129809600</v>
       </c>
       <c r="B77" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8852,30 +8881,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8883,10 +8908,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495499</v>
+        <v>495604</v>
       </c>
       <c r="R77" t="n">
-        <v>7040089</v>
+        <v>7040032</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8923,7 +8948,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>På gran i äldre  granskog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8943,22 +8968,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8976,10 +9001,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809104</v>
+        <v>129809579</v>
       </c>
       <c r="B78" t="n">
-        <v>83050</v>
+        <v>80186</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8987,34 +9012,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495595</v>
+        <v>495499</v>
       </c>
       <c r="R78" t="n">
-        <v>7040220</v>
+        <v>7040089</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9049,34 +9081,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På bark av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129809101</v>
+        <v>129809585</v>
       </c>
       <c r="B79" t="n">
-        <v>83050</v>
+        <v>91595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9084,34 +9147,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>495682</v>
+        <v>495645</v>
       </c>
       <c r="R79" t="n">
-        <v>7039933</v>
+        <v>7039861</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9152,28 +9222,54 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809601</v>
+        <v>129809104</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9181,37 +9277,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495583</v>
+        <v>495595</v>
       </c>
       <c r="R80" t="n">
-        <v>7039969</v>
+        <v>7040220</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9252,54 +9345,28 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809607</v>
+        <v>129809101</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9307,41 +9374,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495591</v>
+        <v>495682</v>
       </c>
       <c r="R81" t="n">
-        <v>7040221</v>
+        <v>7039933</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9376,65 +9436,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Med apothecier på gran.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129809600</v>
+        <v>129809130</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9442,37 +9471,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>495604</v>
+        <v>495569</v>
       </c>
       <c r="R82" t="n">
-        <v>7040032</v>
+        <v>7039991</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9509,7 +9535,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gran i äldre  granskog.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9518,54 +9544,28 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129809106</v>
+        <v>129809574</v>
       </c>
       <c r="B83" t="n">
-        <v>91597</v>
+        <v>57733</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9573,34 +9573,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>495777</v>
+        <v>495509</v>
       </c>
       <c r="R83" t="n">
-        <v>7040083</v>
+        <v>7040092</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9635,6 +9643,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9643,26 +9656,51 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129809125</v>
+        <v>129809106</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9670,21 +9708,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9694,10 +9732,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>495461</v>
+        <v>495777</v>
       </c>
       <c r="R84" t="n">
-        <v>7040125</v>
+        <v>7040083</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9730,11 +9768,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9761,10 +9794,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129809574</v>
+        <v>129809125</v>
       </c>
       <c r="B85" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9772,16 +9805,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9790,24 +9823,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>495509</v>
+        <v>495461</v>
       </c>
       <c r="R85" t="n">
-        <v>7040092</v>
+        <v>7040125</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9844,7 +9869,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9855,41 +9880,16 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9993,10 +9993,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129809081</v>
+        <v>129809148</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>495568</v>
+        <v>495742</v>
       </c>
       <c r="R87" t="n">
-        <v>7040032</v>
+        <v>7040116</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10064,11 +10064,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10095,32 +10090,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129809148</v>
+        <v>129809135</v>
       </c>
       <c r="B88" t="n">
-        <v>91593</v>
+        <v>80215</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10130,10 +10125,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>495742</v>
+        <v>495536</v>
       </c>
       <c r="R88" t="n">
-        <v>7040116</v>
+        <v>7040124</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10327,32 +10322,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129809135</v>
+        <v>129809081</v>
       </c>
       <c r="B90" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10362,10 +10357,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>495536</v>
+        <v>495568</v>
       </c>
       <c r="R90" t="n">
-        <v>7040124</v>
+        <v>7040032</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10398,6 +10393,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10427,7 +10427,7 @@
         <v>129809587</v>
       </c>
       <c r="B91" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11034,10 +11034,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129809593</v>
+        <v>129809093</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11045,37 +11045,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>495530</v>
+        <v>495655</v>
       </c>
       <c r="R96" t="n">
-        <v>7039833</v>
+        <v>7040108</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11116,54 +11109,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129809093</v>
+        <v>129809593</v>
       </c>
       <c r="B97" t="n">
-        <v>91617</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11171,30 +11138,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>495655</v>
+        <v>495530</v>
       </c>
       <c r="R97" t="n">
-        <v>7040108</v>
+        <v>7039833</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11235,18 +11209,44 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129809116</v>
+        <v>129809594</v>
       </c>
       <c r="B101" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11593,34 +11593,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>495435</v>
+        <v>495544</v>
       </c>
       <c r="R101" t="n">
-        <v>7039823</v>
+        <v>7039898</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11657,7 +11660,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11666,28 +11669,54 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129809100</v>
+        <v>129809598</v>
       </c>
       <c r="B102" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11695,34 +11724,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>495592</v>
+        <v>495684</v>
       </c>
       <c r="R102" t="n">
-        <v>7039912</v>
+        <v>7040002</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11767,25 +11799,50 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129809594</v>
+        <v>129809100</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>82918</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11793,37 +11850,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495544</v>
+        <v>495592</v>
       </c>
       <c r="R103" t="n">
-        <v>7039898</v>
+        <v>7039912</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11858,11 +11912,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11873,50 +11922,25 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129809598</v>
+        <v>129809116</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11924,37 +11948,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>495684</v>
+        <v>495435</v>
       </c>
       <c r="R104" t="n">
-        <v>7040002</v>
+        <v>7039823</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11989,95 +12010,81 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129809102</v>
+        <v>129809581</v>
       </c>
       <c r="B105" t="n">
-        <v>83050</v>
+        <v>80222</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>495533</v>
+        <v>495749</v>
       </c>
       <c r="R105" t="n">
-        <v>7039800</v>
+        <v>7040011</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12112,63 +12119,94 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På bark på en smal sälg.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129809581</v>
+        <v>129809586</v>
       </c>
       <c r="B106" t="n">
-        <v>80222</v>
+        <v>91595</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -12178,10 +12216,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>495749</v>
+        <v>495477</v>
       </c>
       <c r="R106" t="n">
-        <v>7040011</v>
+        <v>7039974</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12218,7 +12256,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På bark på en smal sälg.</t>
+          <t>Växer i en stubbe av en knäckt gran.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12238,22 +12276,22 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12271,10 +12309,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809586</v>
+        <v>129809102</v>
       </c>
       <c r="B107" t="n">
-        <v>91593</v>
+        <v>83052</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12282,41 +12320,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495477</v>
+        <v>495533</v>
       </c>
       <c r="R107" t="n">
-        <v>7039974</v>
+        <v>7039800</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12351,55 +12382,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Växer i en stubbe av en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129809566</v>
+        <v>129809151</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12654,42 +12654,30 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>495633</v>
+        <v>495456</v>
       </c>
       <c r="R110" t="n">
-        <v>7040044</v>
+        <v>7039928</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12724,11 +12712,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12737,82 +12720,68 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129809151</v>
+        <v>129809582</v>
       </c>
       <c r="B111" t="n">
-        <v>91617</v>
+        <v>80222</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>495456</v>
+        <v>495698</v>
       </c>
       <c r="R111" t="n">
-        <v>7039928</v>
+        <v>7040023</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12847,34 +12816,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129809582</v>
+        <v>129809085</v>
       </c>
       <c r="B112" t="n">
-        <v>80222</v>
+        <v>80215</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12882,41 +12882,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>495698</v>
+        <v>495476</v>
       </c>
       <c r="R112" t="n">
-        <v>7040023</v>
+        <v>7040074</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12951,100 +12944,77 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129809085</v>
+        <v>129809566</v>
       </c>
       <c r="B113" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>495476</v>
+        <v>495633</v>
       </c>
       <c r="R113" t="n">
-        <v>7040074</v>
+        <v>7040044</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13079,6 +13049,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13087,16 +13062,41 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -2094,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809107</v>
+        <v>129809115</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495592</v>
+        <v>495682</v>
       </c>
       <c r="R14" t="n">
-        <v>7040205</v>
+        <v>7040065</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,6 +2165,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129809146</v>
+        <v>129809082</v>
       </c>
       <c r="B15" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,21 +2207,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2226,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495659</v>
+        <v>495470</v>
       </c>
       <c r="R15" t="n">
-        <v>7039854</v>
+        <v>7039843</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2262,6 +2267,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2416,10 +2426,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129809115</v>
+        <v>129809107</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2427,21 +2437,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2451,10 +2461,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495682</v>
+        <v>495592</v>
       </c>
       <c r="R17" t="n">
-        <v>7040065</v>
+        <v>7040205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2487,11 +2497,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129809082</v>
+        <v>129809146</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2529,21 +2534,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2553,10 +2558,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495470</v>
+        <v>495659</v>
       </c>
       <c r="R18" t="n">
-        <v>7039843</v>
+        <v>7039854</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,11 +2594,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809602</v>
+        <v>129809076</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,37 +2728,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495479</v>
+        <v>495663</v>
       </c>
       <c r="R20" t="n">
-        <v>7039967</v>
+        <v>7040097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,54 +2796,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129809596</v>
+        <v>129809114</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,37 +2825,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495570</v>
+        <v>495559</v>
       </c>
       <c r="R21" t="n">
-        <v>7039935</v>
+        <v>7039895</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,60 +2887,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809152</v>
+        <v>129809144</v>
       </c>
       <c r="B22" t="n">
-        <v>91619</v>
+        <v>78094</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,19 +2927,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3000,10 +2951,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495696</v>
+        <v>495584</v>
       </c>
       <c r="R22" t="n">
-        <v>7040090</v>
+        <v>7040207</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3062,45 +3013,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809134</v>
+        <v>129809602</v>
       </c>
       <c r="B23" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495561</v>
+        <v>495479</v>
       </c>
       <c r="R23" t="n">
-        <v>7039987</v>
+        <v>7039967</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,28 +3095,54 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809076</v>
+        <v>129809596</v>
       </c>
       <c r="B24" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,34 +3150,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495663</v>
+        <v>495570</v>
       </c>
       <c r="R24" t="n">
-        <v>7040097</v>
+        <v>7039935</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,28 +3221,54 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129809144</v>
+        <v>129809152</v>
       </c>
       <c r="B25" t="n">
-        <v>78094</v>
+        <v>91619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,23 +3276,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3291,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495584</v>
+        <v>495696</v>
       </c>
       <c r="R25" t="n">
-        <v>7040207</v>
+        <v>7040090</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3353,32 +3358,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129809114</v>
+        <v>129809134</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3388,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495559</v>
+        <v>495561</v>
       </c>
       <c r="R26" t="n">
-        <v>7039895</v>
+        <v>7039987</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3424,11 +3429,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3950,10 +3950,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809094</v>
+        <v>129809567</v>
       </c>
       <c r="B32" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,30 +3961,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495459</v>
+        <v>495594</v>
       </c>
       <c r="R32" t="n">
-        <v>7039862</v>
+        <v>7039971</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,32 +4031,61 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809567</v>
+        <v>129809126</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -4073,24 +4114,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495594</v>
+        <v>495467</v>
       </c>
       <c r="R33" t="n">
-        <v>7039971</v>
+        <v>7040110</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,7 +4160,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4138,51 +4171,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809126</v>
+        <v>129809094</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,23 +4198,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4214,10 +4218,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495467</v>
+        <v>495459</v>
       </c>
       <c r="R34" t="n">
-        <v>7040110</v>
+        <v>7039862</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4252,17 +4256,13 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129809111</v>
+        <v>129809604</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4869,34 +4869,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495558</v>
+        <v>495501</v>
       </c>
       <c r="R40" t="n">
-        <v>7039811</v>
+        <v>7040069</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4931,39 +4934,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809083</v>
+        <v>129809084</v>
       </c>
       <c r="B41" t="n">
-        <v>56926</v>
+        <v>80215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4971,21 +4995,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4995,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495476</v>
+        <v>495651</v>
       </c>
       <c r="R41" t="n">
-        <v>7040074</v>
+        <v>7039928</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5057,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809604</v>
+        <v>129809138</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5068,37 +5092,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495501</v>
+        <v>495613</v>
       </c>
       <c r="R42" t="n">
-        <v>7040069</v>
+        <v>7039922</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,76 +5160,50 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129809084</v>
+        <v>129809111</v>
       </c>
       <c r="B43" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5218,10 +5213,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495651</v>
+        <v>495558</v>
       </c>
       <c r="R43" t="n">
-        <v>7039928</v>
+        <v>7039811</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5254,6 +5249,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,32 +5280,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129809138</v>
+        <v>129809083</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495613</v>
+        <v>495476</v>
       </c>
       <c r="R44" t="n">
-        <v>7039922</v>
+        <v>7040074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5377,10 +5377,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129809605</v>
+        <v>129809091</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5388,37 +5388,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495546</v>
+        <v>495490</v>
       </c>
       <c r="R45" t="n">
-        <v>7040104</v>
+        <v>7039928</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5459,54 +5456,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129809154</v>
+        <v>129809079</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5514,21 +5485,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5538,10 +5509,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495635</v>
+        <v>495550</v>
       </c>
       <c r="R46" t="n">
-        <v>7039937</v>
+        <v>7039807</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5574,6 +5545,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5600,10 +5576,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129809592</v>
+        <v>129809080</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5611,37 +5587,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495516</v>
+        <v>495554</v>
       </c>
       <c r="R47" t="n">
-        <v>7039796</v>
+        <v>7039840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5678,7 +5651,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5687,54 +5660,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809091</v>
+        <v>129809605</v>
       </c>
       <c r="B48" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5742,34 +5689,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495490</v>
+        <v>495546</v>
       </c>
       <c r="R48" t="n">
-        <v>7039928</v>
+        <v>7040104</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5810,28 +5760,54 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129809079</v>
+        <v>129809154</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5839,21 +5815,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5863,10 +5839,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495550</v>
+        <v>495635</v>
       </c>
       <c r="R49" t="n">
-        <v>7039807</v>
+        <v>7039937</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5899,11 +5875,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5930,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129809080</v>
+        <v>129809592</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5941,34 +5912,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495554</v>
+        <v>495516</v>
       </c>
       <c r="R50" t="n">
-        <v>7039840</v>
+        <v>7039796</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6005,7 +5979,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6014,28 +5988,54 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809606</v>
+        <v>129809142</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,37 +6043,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495603</v>
+        <v>495682</v>
       </c>
       <c r="R51" t="n">
-        <v>7040220</v>
+        <v>7039932</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6114,44 +6111,18 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6525,10 +6496,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129809142</v>
+        <v>129809606</v>
       </c>
       <c r="B55" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6536,34 +6507,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495682</v>
+        <v>495603</v>
       </c>
       <c r="R55" t="n">
-        <v>7039932</v>
+        <v>7040220</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6604,28 +6578,54 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129809078</v>
+        <v>129809155</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6633,21 +6633,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495653</v>
+        <v>495737</v>
       </c>
       <c r="R56" t="n">
-        <v>7039924</v>
+        <v>7040098</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6693,11 +6693,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6724,7 +6719,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129809110</v>
+        <v>129809078</v>
       </c>
       <c r="B57" t="n">
         <v>57736</v>
@@ -6759,10 +6754,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495565</v>
+        <v>495653</v>
       </c>
       <c r="R57" t="n">
-        <v>7039805</v>
+        <v>7039924</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6826,10 +6821,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129809155</v>
+        <v>129809110</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6837,21 +6832,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6861,10 +6856,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495737</v>
+        <v>495565</v>
       </c>
       <c r="R58" t="n">
-        <v>7040098</v>
+        <v>7039805</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6897,6 +6892,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7780,10 +7780,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129809098</v>
+        <v>129809158</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>83044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,21 +7791,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495709</v>
+        <v>495531</v>
       </c>
       <c r="R67" t="n">
-        <v>7040119</v>
+        <v>7040125</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7877,7 +7877,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809099</v>
+        <v>129809098</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495626</v>
+        <v>495709</v>
       </c>
       <c r="R68" t="n">
-        <v>7040099</v>
+        <v>7040119</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7974,10 +7974,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809127</v>
+        <v>129809099</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7985,21 +7985,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495608</v>
+        <v>495626</v>
       </c>
       <c r="R69" t="n">
-        <v>7040209</v>
+        <v>7040099</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8045,11 +8045,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8076,10 +8071,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809129</v>
+        <v>129809127</v>
       </c>
       <c r="B70" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8087,21 +8082,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8111,10 +8106,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495522</v>
+        <v>495608</v>
       </c>
       <c r="R70" t="n">
-        <v>7039794</v>
+        <v>7040209</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8151,7 +8146,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8178,32 +8173,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809090</v>
+        <v>129809129</v>
       </c>
       <c r="B71" t="n">
-        <v>98780</v>
+        <v>57896</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8213,10 +8208,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495544</v>
+        <v>495522</v>
       </c>
       <c r="R71" t="n">
-        <v>7040035</v>
+        <v>7039794</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8249,6 +8244,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8275,32 +8275,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129809158</v>
+        <v>129809090</v>
       </c>
       <c r="B72" t="n">
-        <v>83044</v>
+        <v>98780</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>495531</v>
+        <v>495544</v>
       </c>
       <c r="R72" t="n">
-        <v>7040125</v>
+        <v>7040035</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809568</v>
+        <v>129809601</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,31 +8383,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8415,10 +8410,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495618</v>
+        <v>495583</v>
       </c>
       <c r="R73" t="n">
-        <v>7040130</v>
+        <v>7039969</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8453,17 +8448,13 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8484,12 +8475,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8507,10 +8498,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809122</v>
+        <v>129809607</v>
       </c>
       <c r="B74" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8518,34 +8509,41 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495433</v>
+        <v>495591</v>
       </c>
       <c r="R74" t="n">
-        <v>7039995</v>
+        <v>7040221</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8582,7 +8580,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Med apothecier på gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8591,25 +8589,51 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809601</v>
+        <v>129809600</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8647,10 +8671,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495583</v>
+        <v>495604</v>
       </c>
       <c r="R75" t="n">
-        <v>7039969</v>
+        <v>7040032</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8683,6 +8707,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran i äldre  granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8735,10 +8764,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809607</v>
+        <v>129809104</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,41 +8775,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495591</v>
+        <v>495595</v>
       </c>
       <c r="R76" t="n">
-        <v>7040221</v>
+        <v>7040220</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8815,65 +8837,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Med apothecier på gran.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809600</v>
+        <v>129809101</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,37 +8872,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495604</v>
+        <v>495682</v>
       </c>
       <c r="R77" t="n">
-        <v>7040032</v>
+        <v>7039933</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8946,65 +8934,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gran i äldre  granskog.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809579</v>
+        <v>129809568</v>
       </c>
       <c r="B78" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9012,28 +8969,29 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9043,10 +9001,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495499</v>
+        <v>495618</v>
       </c>
       <c r="R78" t="n">
-        <v>7040089</v>
+        <v>7040130</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9083,7 +9041,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9092,7 +9050,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9103,22 +9060,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9136,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129809585</v>
+        <v>129809122</v>
       </c>
       <c r="B79" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9147,41 +9104,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>495645</v>
+        <v>495433</v>
       </c>
       <c r="R79" t="n">
-        <v>7039861</v>
+        <v>7039995</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9216,60 +9166,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809104</v>
+        <v>129809579</v>
       </c>
       <c r="B80" t="n">
-        <v>83052</v>
+        <v>80186</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9277,34 +9206,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495595</v>
+        <v>495499</v>
       </c>
       <c r="R80" t="n">
-        <v>7040220</v>
+        <v>7040089</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9339,34 +9275,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På bark av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809101</v>
+        <v>129809585</v>
       </c>
       <c r="B81" t="n">
-        <v>83052</v>
+        <v>91595</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9374,34 +9341,41 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495682</v>
+        <v>495645</v>
       </c>
       <c r="R81" t="n">
-        <v>7039933</v>
+        <v>7039861</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9442,18 +9416,44 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10424,10 +10424,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129809587</v>
+        <v>129809095</v>
       </c>
       <c r="B91" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10435,41 +10435,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>495597</v>
+        <v>495614</v>
       </c>
       <c r="R91" t="n">
-        <v>7040221</v>
+        <v>7039909</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10504,55 +10497,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>I en stående levande gran.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10811,10 +10773,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129809095</v>
+        <v>129809587</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10822,34 +10784,41 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>495614</v>
+        <v>495597</v>
       </c>
       <c r="R94" t="n">
-        <v>7039909</v>
+        <v>7040221</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10884,24 +10853,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>I en stående levande gran.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -12174,10 +12174,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129809586</v>
+        <v>129809113</v>
       </c>
       <c r="B106" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12185,41 +12185,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>495477</v>
+        <v>495541</v>
       </c>
       <c r="R106" t="n">
-        <v>7039974</v>
+        <v>7039874</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12256,7 +12249,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Växer i en stubbe av en knäckt gran.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12265,54 +12258,28 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809102</v>
+        <v>129809570</v>
       </c>
       <c r="B107" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12320,34 +12287,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495533</v>
+        <v>495618</v>
       </c>
       <c r="R107" t="n">
-        <v>7039800</v>
+        <v>7040246</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12382,6 +12357,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12390,26 +12370,51 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129809113</v>
+        <v>129809586</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12417,34 +12422,41 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>495541</v>
+        <v>495477</v>
       </c>
       <c r="R108" t="n">
-        <v>7039874</v>
+        <v>7039974</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12481,7 +12493,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Växer i en stubbe av en knäckt gran.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12490,28 +12502,54 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129809570</v>
+        <v>129809102</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12519,42 +12557,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>495618</v>
+        <v>495533</v>
       </c>
       <c r="R109" t="n">
-        <v>7040246</v>
+        <v>7039800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12589,11 +12619,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12602,41 +12627,16 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809603</v>
+        <v>129809087</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495504</v>
+        <v>495710</v>
       </c>
       <c r="R2" t="n">
-        <v>7040017</v>
+        <v>7039992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,65 +748,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809595</v>
+        <v>129809578</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +783,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495548</v>
+        <v>495701</v>
       </c>
       <c r="R3" t="n">
-        <v>7039913</v>
+        <v>7040014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +852,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -899,22 +874,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809087</v>
+        <v>129809089</v>
       </c>
       <c r="B4" t="n">
         <v>80186</v>
@@ -967,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495710</v>
+        <v>495476</v>
       </c>
       <c r="R4" t="n">
-        <v>7039992</v>
+        <v>7040074</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809578</v>
+        <v>129809157</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>82918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,41 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495701</v>
+        <v>495620</v>
       </c>
       <c r="R5" t="n">
-        <v>7040014</v>
+        <v>7040063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,65 +1077,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809089</v>
+        <v>129809603</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,34 +1112,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495476</v>
+        <v>495504</v>
       </c>
       <c r="R6" t="n">
-        <v>7040074</v>
+        <v>7040017</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,34 +1177,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809157</v>
+        <v>129809595</v>
       </c>
       <c r="B7" t="n">
-        <v>82918</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,34 +1243,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495620</v>
+        <v>495548</v>
       </c>
       <c r="R7" t="n">
-        <v>7040063</v>
+        <v>7039913</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,60 +1314,98 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809611</v>
+        <v>129809109</v>
       </c>
       <c r="B8" t="n">
-        <v>100969</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1401,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495627</v>
+        <v>495738</v>
       </c>
       <c r="R8" t="n">
-        <v>7039995</v>
+        <v>7040008</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1453,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,78 +1462,60 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129809109</v>
+        <v>129809611</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>100969</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1529,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495738</v>
+        <v>495627</v>
       </c>
       <c r="R9" t="n">
-        <v>7040008</v>
+        <v>7039995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1563,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,18 +1572,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809567</v>
+        <v>129809094</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,42 +3961,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495594</v>
+        <v>495459</v>
       </c>
       <c r="R32" t="n">
-        <v>7039971</v>
+        <v>7039862</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4031,61 +4019,32 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809126</v>
+        <v>129809567</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -4114,16 +4073,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495467</v>
+        <v>495594</v>
       </c>
       <c r="R33" t="n">
-        <v>7040110</v>
+        <v>7039971</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4160,7 +4127,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4171,26 +4138,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809094</v>
+        <v>129809126</v>
       </c>
       <c r="B34" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4198,19 +4190,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4218,10 +4214,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495459</v>
+        <v>495467</v>
       </c>
       <c r="R34" t="n">
-        <v>7039862</v>
+        <v>7040110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,13 +4252,17 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129809604</v>
+        <v>129809111</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4869,37 +4869,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495501</v>
+        <v>495558</v>
       </c>
       <c r="R40" t="n">
-        <v>7040069</v>
+        <v>7039811</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4934,60 +4931,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809084</v>
+        <v>129809083</v>
       </c>
       <c r="B41" t="n">
-        <v>80215</v>
+        <v>56926</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,21 +4971,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5019,10 +4995,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495651</v>
+        <v>495476</v>
       </c>
       <c r="R41" t="n">
-        <v>7039928</v>
+        <v>7040074</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5081,10 +5057,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809138</v>
+        <v>129809604</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,34 +5068,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495613</v>
+        <v>495501</v>
       </c>
       <c r="R42" t="n">
-        <v>7039922</v>
+        <v>7040069</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5160,50 +5139,76 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129809111</v>
+        <v>129809084</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5213,10 +5218,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495558</v>
+        <v>495651</v>
       </c>
       <c r="R43" t="n">
-        <v>7039811</v>
+        <v>7039928</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5249,11 +5254,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,32 +5280,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129809083</v>
+        <v>129809138</v>
       </c>
       <c r="B44" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495476</v>
+        <v>495613</v>
       </c>
       <c r="R44" t="n">
-        <v>7040074</v>
+        <v>7039922</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5377,10 +5377,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129809091</v>
+        <v>129809605</v>
       </c>
       <c r="B45" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5388,34 +5388,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495490</v>
+        <v>495546</v>
       </c>
       <c r="R45" t="n">
-        <v>7039928</v>
+        <v>7040104</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5456,28 +5459,54 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129809079</v>
+        <v>129809154</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,21 +5514,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5509,10 +5538,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495550</v>
+        <v>495635</v>
       </c>
       <c r="R46" t="n">
-        <v>7039807</v>
+        <v>7039937</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5545,11 +5574,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5576,10 +5600,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129809080</v>
+        <v>129809592</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5587,34 +5611,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495554</v>
+        <v>495516</v>
       </c>
       <c r="R47" t="n">
-        <v>7039840</v>
+        <v>7039796</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5651,7 +5678,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5660,28 +5687,54 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809605</v>
+        <v>129809079</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5689,37 +5742,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495546</v>
+        <v>495550</v>
       </c>
       <c r="R48" t="n">
-        <v>7040104</v>
+        <v>7039807</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5754,60 +5804,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129809154</v>
+        <v>129809080</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5815,21 +5844,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5839,10 +5868,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495635</v>
+        <v>495554</v>
       </c>
       <c r="R49" t="n">
-        <v>7039937</v>
+        <v>7039840</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5875,6 +5904,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5935,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129809592</v>
+        <v>129809091</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5912,37 +5946,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495516</v>
+        <v>495490</v>
       </c>
       <c r="R50" t="n">
-        <v>7039796</v>
+        <v>7039928</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5977,55 +6008,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129809158</v>
+        <v>129809098</v>
       </c>
       <c r="B67" t="n">
-        <v>83044</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,21 +7791,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495531</v>
+        <v>495709</v>
       </c>
       <c r="R67" t="n">
-        <v>7040125</v>
+        <v>7040119</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7877,7 +7877,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809098</v>
+        <v>129809099</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495709</v>
+        <v>495626</v>
       </c>
       <c r="R68" t="n">
-        <v>7040119</v>
+        <v>7040099</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7974,10 +7974,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809099</v>
+        <v>129809127</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7985,21 +7985,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495626</v>
+        <v>495608</v>
       </c>
       <c r="R69" t="n">
-        <v>7040099</v>
+        <v>7040209</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8045,6 +8045,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8071,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809127</v>
+        <v>129809129</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8082,21 +8087,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8106,10 +8111,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495608</v>
+        <v>495522</v>
       </c>
       <c r="R70" t="n">
-        <v>7040209</v>
+        <v>7039794</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8146,7 +8151,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8173,32 +8178,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809129</v>
+        <v>129809090</v>
       </c>
       <c r="B71" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8208,10 +8213,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495522</v>
+        <v>495544</v>
       </c>
       <c r="R71" t="n">
-        <v>7039794</v>
+        <v>7040035</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8244,11 +8249,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8275,32 +8275,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129809090</v>
+        <v>129809158</v>
       </c>
       <c r="B72" t="n">
-        <v>98780</v>
+        <v>83044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>495544</v>
+        <v>495531</v>
       </c>
       <c r="R72" t="n">
-        <v>7040035</v>
+        <v>7040125</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10424,10 +10424,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129809095</v>
+        <v>129809587</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10435,34 +10435,41 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>495614</v>
+        <v>495597</v>
       </c>
       <c r="R91" t="n">
-        <v>7039909</v>
+        <v>7040221</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10497,24 +10504,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>I en stående levande gran.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10773,10 +10811,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129809587</v>
+        <v>129809095</v>
       </c>
       <c r="B94" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10784,41 +10822,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>495597</v>
+        <v>495614</v>
       </c>
       <c r="R94" t="n">
-        <v>7040221</v>
+        <v>7039909</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10853,55 +10884,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>I en stående levande gran.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129809594</v>
+        <v>129809116</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11593,37 +11593,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>495544</v>
+        <v>495435</v>
       </c>
       <c r="R101" t="n">
-        <v>7039898</v>
+        <v>7039823</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11660,7 +11657,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11669,51 +11666,25 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129809598</v>
+        <v>129809594</v>
       </c>
       <c r="B102" t="n">
         <v>79081</v>
@@ -11751,10 +11722,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>495684</v>
+        <v>495544</v>
       </c>
       <c r="R102" t="n">
-        <v>7040002</v>
+        <v>7039898</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11787,6 +11758,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11839,10 +11815,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129809100</v>
+        <v>129809598</v>
       </c>
       <c r="B103" t="n">
-        <v>82918</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11850,34 +11826,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495592</v>
+        <v>495684</v>
       </c>
       <c r="R103" t="n">
-        <v>7039912</v>
+        <v>7040002</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11922,25 +11901,50 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129809116</v>
+        <v>129809100</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>82918</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11948,21 +11952,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11972,10 +11976,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>495435</v>
+        <v>495592</v>
       </c>
       <c r="R104" t="n">
-        <v>7039823</v>
+        <v>7039912</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12010,17 +12014,13 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -3950,10 +3950,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809094</v>
+        <v>129809567</v>
       </c>
       <c r="B32" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,30 +3961,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495459</v>
+        <v>495594</v>
       </c>
       <c r="R32" t="n">
-        <v>7039862</v>
+        <v>7039971</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,32 +4031,61 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809567</v>
+        <v>129809126</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -4073,24 +4114,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495594</v>
+        <v>495467</v>
       </c>
       <c r="R33" t="n">
-        <v>7039971</v>
+        <v>7040110</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,7 +4160,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4138,51 +4171,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809126</v>
+        <v>129809094</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,23 +4198,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4214,10 +4218,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495467</v>
+        <v>495459</v>
       </c>
       <c r="R34" t="n">
-        <v>7040110</v>
+        <v>7039862</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4252,17 +4256,13 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809087</v>
+        <v>129809603</v>
       </c>
       <c r="B2" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495710</v>
+        <v>495504</v>
       </c>
       <c r="R2" t="n">
-        <v>7039992</v>
+        <v>7040017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,34 +751,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809578</v>
+        <v>129809595</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,30 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495701</v>
+        <v>495548</v>
       </c>
       <c r="R3" t="n">
-        <v>7040014</v>
+        <v>7039913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +882,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -874,22 +899,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,7 +932,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809089</v>
+        <v>129809087</v>
       </c>
       <c r="B4" t="n">
         <v>80186</v>
@@ -942,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495476</v>
+        <v>495710</v>
       </c>
       <c r="R4" t="n">
-        <v>7040074</v>
+        <v>7039992</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809157</v>
+        <v>129809578</v>
       </c>
       <c r="B5" t="n">
-        <v>82918</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,34 +1040,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495620</v>
+        <v>495701</v>
       </c>
       <c r="R5" t="n">
-        <v>7040063</v>
+        <v>7040014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,34 +1109,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809603</v>
+        <v>129809089</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,37 +1175,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495504</v>
+        <v>495476</v>
       </c>
       <c r="R6" t="n">
-        <v>7040017</v>
+        <v>7040074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,65 +1237,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809595</v>
+        <v>129809109</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,26 +1272,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1270,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495548</v>
+        <v>495738</v>
       </c>
       <c r="R7" t="n">
-        <v>7039913</v>
+        <v>7040008</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,60 +1354,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809109</v>
+        <v>129809157</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>82918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,54 +1394,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495738</v>
+        <v>495620</v>
       </c>
       <c r="R8" t="n">
-        <v>7040008</v>
+        <v>7040063</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,11 +1454,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,7 +1483,7 @@
         <v>129809611</v>
       </c>
       <c r="B9" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809599</v>
+        <v>129809139</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,37 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495719</v>
+        <v>495484</v>
       </c>
       <c r="R10" t="n">
-        <v>7040059</v>
+        <v>7040082</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,107 +1669,85 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129809573</v>
+        <v>129809575</v>
       </c>
       <c r="B11" t="n">
-        <v>80215</v>
+        <v>56310</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495496</v>
+        <v>495639</v>
       </c>
       <c r="R11" t="n">
-        <v>7040079</v>
+        <v>7039976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1784,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1793,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1827,24 +1801,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1862,52 +1821,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129809583</v>
+        <v>129809107</v>
       </c>
       <c r="B12" t="n">
-        <v>80222</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495575</v>
+        <v>495592</v>
       </c>
       <c r="R12" t="n">
-        <v>7039971</v>
+        <v>7040205</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1942,65 +1894,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På barken av en död sälglåga.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809139</v>
+        <v>129809146</v>
       </c>
       <c r="B13" t="n">
-        <v>80187</v>
+        <v>91595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,21 +1929,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2032,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495484</v>
+        <v>495659</v>
       </c>
       <c r="R13" t="n">
-        <v>7040082</v>
+        <v>7039854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2094,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809115</v>
+        <v>129809599</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,34 +2026,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495682</v>
+        <v>495719</v>
       </c>
       <c r="R14" t="n">
-        <v>7040065</v>
+        <v>7040059</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2169,7 +2093,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,63 +2102,96 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129809082</v>
+        <v>129809573</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495470</v>
+        <v>495496</v>
       </c>
       <c r="R15" t="n">
-        <v>7039843</v>
+        <v>7040079</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2271,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På bark av en levande sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,79 +2237,96 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129809575</v>
+        <v>129809583</v>
       </c>
       <c r="B16" t="n">
-        <v>56310</v>
+        <v>80222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206004</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495639</v>
+        <v>495575</v>
       </c>
       <c r="R16" t="n">
-        <v>7039976</v>
+        <v>7039971</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2389,7 +2363,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
+          <t>På barken av en död sälglåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,6 +2372,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2406,9 +2381,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2426,10 +2416,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129809107</v>
+        <v>129809115</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2437,21 +2427,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2461,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495592</v>
+        <v>495682</v>
       </c>
       <c r="R17" t="n">
-        <v>7040205</v>
+        <v>7040065</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2497,6 +2487,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2518,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129809146</v>
+        <v>129809082</v>
       </c>
       <c r="B18" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,21 +2529,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2558,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495659</v>
+        <v>495470</v>
       </c>
       <c r="R18" t="n">
-        <v>7039854</v>
+        <v>7039843</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,6 +2589,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809159</v>
+        <v>129809076</v>
       </c>
       <c r="B19" t="n">
-        <v>83044</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495530</v>
+        <v>495663</v>
       </c>
       <c r="R19" t="n">
-        <v>7040111</v>
+        <v>7040097</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809076</v>
+        <v>129809159</v>
       </c>
       <c r="B20" t="n">
-        <v>91599</v>
+        <v>83044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495663</v>
+        <v>495530</v>
       </c>
       <c r="R20" t="n">
-        <v>7040097</v>
+        <v>7040111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809567</v>
+        <v>129809094</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,42 +3961,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495594</v>
+        <v>495459</v>
       </c>
       <c r="R32" t="n">
-        <v>7039971</v>
+        <v>7039862</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4031,99 +4019,77 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809126</v>
+        <v>129809572</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495467</v>
+        <v>495579</v>
       </c>
       <c r="R33" t="n">
-        <v>7040110</v>
+        <v>7039969</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4160,7 +4126,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På barken av en sälglåga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4169,48 +4135,78 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809094</v>
+        <v>129809141</v>
       </c>
       <c r="B34" t="n">
-        <v>91619</v>
+        <v>80222</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4218,10 +4214,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495459</v>
+        <v>495483</v>
       </c>
       <c r="R34" t="n">
-        <v>7039862</v>
+        <v>7040081</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4262,7 +4258,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4281,39 +4276,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129809572</v>
+        <v>129809137</v>
       </c>
       <c r="B35" t="n">
-        <v>80215</v>
+        <v>57733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4323,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495579</v>
+        <v>495739</v>
       </c>
       <c r="R35" t="n">
-        <v>7039969</v>
+        <v>7040024</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4361,100 +4365,77 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På barken av en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129809141</v>
+        <v>129809567</v>
       </c>
       <c r="B36" t="n">
-        <v>80222</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495483</v>
+        <v>495594</v>
       </c>
       <c r="R36" t="n">
-        <v>7040081</v>
+        <v>7039971</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4489,6 +4470,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4497,26 +4483,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129809137</v>
+        <v>129809126</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,16 +4535,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4541,33 +4552,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495739</v>
+        <v>495467</v>
       </c>
       <c r="R37" t="n">
-        <v>7040024</v>
+        <v>7040110</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4600,6 +4595,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4626,32 +4626,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129809140</v>
+        <v>129809111</v>
       </c>
       <c r="B38" t="n">
-        <v>92052</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495671</v>
+        <v>495558</v>
       </c>
       <c r="R38" t="n">
-        <v>7039845</v>
+        <v>7039811</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4697,6 +4697,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4723,52 +4728,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129809561</v>
+        <v>129809083</v>
       </c>
       <c r="B39" t="n">
-        <v>91599</v>
+        <v>56926</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495774</v>
+        <v>495476</v>
       </c>
       <c r="R39" t="n">
-        <v>7040061</v>
+        <v>7040074</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4803,65 +4801,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129809111</v>
+        <v>129809561</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4869,34 +4836,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495558</v>
+        <v>495774</v>
       </c>
       <c r="R40" t="n">
-        <v>7039811</v>
+        <v>7040061</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4933,7 +4907,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>I en upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4942,50 +4916,76 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809083</v>
+        <v>129809140</v>
       </c>
       <c r="B41" t="n">
-        <v>56926</v>
+        <v>92052</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495476</v>
+        <v>495671</v>
       </c>
       <c r="R41" t="n">
-        <v>7040074</v>
+        <v>7039845</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5377,10 +5377,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129809605</v>
+        <v>129809091</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5388,37 +5388,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495546</v>
+        <v>495490</v>
       </c>
       <c r="R45" t="n">
-        <v>7040104</v>
+        <v>7039928</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5459,54 +5456,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129809154</v>
+        <v>129809079</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5514,21 +5485,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5538,10 +5509,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495635</v>
+        <v>495550</v>
       </c>
       <c r="R46" t="n">
-        <v>7039937</v>
+        <v>7039807</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5574,6 +5545,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5600,7 +5576,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129809592</v>
+        <v>129809605</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5638,10 +5614,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495516</v>
+        <v>495546</v>
       </c>
       <c r="R47" t="n">
-        <v>7039796</v>
+        <v>7040104</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5674,11 +5650,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5731,10 +5702,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809079</v>
+        <v>129809154</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5742,21 +5713,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5766,10 +5737,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495550</v>
+        <v>495635</v>
       </c>
       <c r="R48" t="n">
-        <v>7039807</v>
+        <v>7039937</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5802,11 +5773,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5833,10 +5799,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129809080</v>
+        <v>129809592</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5844,34 +5810,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495554</v>
+        <v>495516</v>
       </c>
       <c r="R49" t="n">
-        <v>7039840</v>
+        <v>7039796</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5908,7 +5877,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5917,28 +5886,54 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129809091</v>
+        <v>129809080</v>
       </c>
       <c r="B50" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5946,21 +5941,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5970,10 +5965,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495490</v>
+        <v>495554</v>
       </c>
       <c r="R50" t="n">
-        <v>7039928</v>
+        <v>7039840</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6006,6 +6001,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6032,45 +6032,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809142</v>
+        <v>129809571</v>
       </c>
       <c r="B51" t="n">
-        <v>78094</v>
+        <v>80215</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495682</v>
+        <v>495699</v>
       </c>
       <c r="R51" t="n">
-        <v>7039932</v>
+        <v>7040018</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6105,34 +6112,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809571</v>
+        <v>129809584</v>
       </c>
       <c r="B52" t="n">
-        <v>80215</v>
+        <v>80222</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6140,21 +6178,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6171,10 +6209,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495699</v>
+        <v>495504</v>
       </c>
       <c r="R52" t="n">
-        <v>7040018</v>
+        <v>7040027</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6211,7 +6249,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>På barken av en smal levande sälg.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6264,41 +6302,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129809584</v>
+        <v>129809606</v>
       </c>
       <c r="B53" t="n">
-        <v>80222</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6306,10 +6340,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495504</v>
+        <v>495603</v>
       </c>
       <c r="R53" t="n">
-        <v>7040027</v>
+        <v>7040220</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6344,11 +6378,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På barken av en smal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6366,22 +6395,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6496,10 +6525,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129809606</v>
+        <v>129809142</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6507,37 +6536,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495603</v>
+        <v>495682</v>
       </c>
       <c r="R55" t="n">
-        <v>7040220</v>
+        <v>7039932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6578,44 +6604,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6923,41 +6923,52 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129809153</v>
+        <v>129809563</v>
       </c>
       <c r="B59" t="n">
-        <v>91619</v>
+        <v>92317</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495507</v>
+        <v>495549</v>
       </c>
       <c r="R59" t="n">
-        <v>7040063</v>
+        <v>7039804</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6992,56 +7003,82 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I en knäckt gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809133</v>
+        <v>129809150</v>
       </c>
       <c r="B60" t="n">
-        <v>80215</v>
+        <v>91595</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7051,10 +7088,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495563</v>
+        <v>495465</v>
       </c>
       <c r="R60" t="n">
-        <v>7039894</v>
+        <v>7039933</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7113,10 +7150,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809150</v>
+        <v>129809562</v>
       </c>
       <c r="B61" t="n">
-        <v>91595</v>
+        <v>91599</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7124,34 +7161,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495465</v>
+        <v>495606</v>
       </c>
       <c r="R61" t="n">
-        <v>7039933</v>
+        <v>7040134</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7186,34 +7230,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129809562</v>
+        <v>129809156</v>
       </c>
       <c r="B62" t="n">
-        <v>91599</v>
+        <v>82918</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7221,41 +7296,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495606</v>
+        <v>495664</v>
       </c>
       <c r="R62" t="n">
-        <v>7040134</v>
+        <v>7040037</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7290,65 +7358,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809156</v>
+        <v>129809153</v>
       </c>
       <c r="B63" t="n">
-        <v>82918</v>
+        <v>91619</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7356,23 +7393,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7380,10 +7413,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495664</v>
+        <v>495507</v>
       </c>
       <c r="R63" t="n">
-        <v>7040037</v>
+        <v>7040063</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7442,32 +7475,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129809143</v>
+        <v>129809133</v>
       </c>
       <c r="B64" t="n">
-        <v>78094</v>
+        <v>80215</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7477,10 +7510,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495700</v>
+        <v>495563</v>
       </c>
       <c r="R64" t="n">
-        <v>7040007</v>
+        <v>7039894</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7539,53 +7572,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129809610</v>
+        <v>129809143</v>
       </c>
       <c r="B65" t="n">
-        <v>100969</v>
+        <v>78094</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495622</v>
+        <v>495700</v>
       </c>
       <c r="R65" t="n">
-        <v>7039966</v>
+        <v>7040007</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7626,34 +7651,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129809563</v>
+        <v>129809610</v>
       </c>
       <c r="B66" t="n">
-        <v>92317</v>
+        <v>100979</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7661,30 +7680,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7692,10 +7712,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495549</v>
+        <v>495622</v>
       </c>
       <c r="R66" t="n">
-        <v>7039804</v>
+        <v>7039966</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7730,11 +7750,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>I en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7748,21 +7763,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129809098</v>
+        <v>129809127</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,21 +7791,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495709</v>
+        <v>495608</v>
       </c>
       <c r="R67" t="n">
-        <v>7040119</v>
+        <v>7040209</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7851,6 +7851,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7877,32 +7882,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809099</v>
+        <v>129809090</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7912,10 +7917,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495626</v>
+        <v>495544</v>
       </c>
       <c r="R68" t="n">
-        <v>7040099</v>
+        <v>7040035</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7974,10 +7979,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809127</v>
+        <v>129809158</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>83044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7985,21 +7990,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8009,10 +8014,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495608</v>
+        <v>495531</v>
       </c>
       <c r="R69" t="n">
-        <v>7040209</v>
+        <v>7040125</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8045,11 +8050,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809129</v>
+        <v>129809098</v>
       </c>
       <c r="B70" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495522</v>
+        <v>495709</v>
       </c>
       <c r="R70" t="n">
-        <v>7039794</v>
+        <v>7040119</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8147,11 +8147,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8178,32 +8173,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809090</v>
+        <v>129809099</v>
       </c>
       <c r="B71" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8213,10 +8208,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495544</v>
+        <v>495626</v>
       </c>
       <c r="R71" t="n">
-        <v>7040035</v>
+        <v>7040099</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8275,10 +8270,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129809158</v>
+        <v>129809129</v>
       </c>
       <c r="B72" t="n">
-        <v>83044</v>
+        <v>57896</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8286,21 +8281,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8310,10 +8305,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>495531</v>
+        <v>495522</v>
       </c>
       <c r="R72" t="n">
-        <v>7040125</v>
+        <v>7039794</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8346,6 +8341,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809601</v>
+        <v>129809585</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,26 +8383,30 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8410,10 +8414,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495583</v>
+        <v>495645</v>
       </c>
       <c r="R73" t="n">
-        <v>7039969</v>
+        <v>7039861</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8475,12 +8479,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8498,10 +8502,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809607</v>
+        <v>129809579</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8509,28 +8513,28 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -8540,10 +8544,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495591</v>
+        <v>495499</v>
       </c>
       <c r="R74" t="n">
-        <v>7040221</v>
+        <v>7040089</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8580,7 +8584,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Med apothecier på gran.</t>
+          <t>På bark av en levande sälg.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8600,22 +8604,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8633,7 +8637,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809600</v>
+        <v>129809601</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8671,10 +8675,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495604</v>
+        <v>495583</v>
       </c>
       <c r="R75" t="n">
-        <v>7040032</v>
+        <v>7039969</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8707,11 +8711,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På gran i äldre  granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8764,10 +8763,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809104</v>
+        <v>129809607</v>
       </c>
       <c r="B76" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8775,34 +8774,41 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495595</v>
+        <v>495591</v>
       </c>
       <c r="R76" t="n">
-        <v>7040220</v>
+        <v>7040221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8837,34 +8843,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Med apothecier på gran.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809101</v>
+        <v>129809600</v>
       </c>
       <c r="B77" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8872,34 +8909,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495682</v>
+        <v>495604</v>
       </c>
       <c r="R77" t="n">
-        <v>7039933</v>
+        <v>7040032</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8934,34 +8974,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gran i äldre  granskog.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809568</v>
+        <v>129809104</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8969,42 +9040,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495618</v>
+        <v>495595</v>
       </c>
       <c r="R78" t="n">
-        <v>7040130</v>
+        <v>7040220</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9039,11 +9102,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9052,51 +9110,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129809122</v>
+        <v>129809101</v>
       </c>
       <c r="B79" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9104,21 +9137,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9128,10 +9161,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>495433</v>
+        <v>495682</v>
       </c>
       <c r="R79" t="n">
-        <v>7039995</v>
+        <v>7039933</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9164,11 +9197,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9195,10 +9223,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809579</v>
+        <v>129809568</v>
       </c>
       <c r="B80" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9206,28 +9234,29 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9237,10 +9266,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495499</v>
+        <v>495618</v>
       </c>
       <c r="R80" t="n">
-        <v>7040089</v>
+        <v>7040130</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9277,7 +9306,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9286,7 +9315,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9297,22 +9325,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9330,10 +9358,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809585</v>
+        <v>129809122</v>
       </c>
       <c r="B81" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9341,41 +9369,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495645</v>
+        <v>495433</v>
       </c>
       <c r="R81" t="n">
-        <v>7039861</v>
+        <v>7039995</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9410,50 +9431,29 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9697,10 +9697,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129809106</v>
+        <v>129809125</v>
       </c>
       <c r="B84" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9708,21 +9708,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9732,10 +9732,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>495777</v>
+        <v>495461</v>
       </c>
       <c r="R84" t="n">
-        <v>7040083</v>
+        <v>7040125</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9768,6 +9768,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9794,10 +9799,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129809125</v>
+        <v>129809106</v>
       </c>
       <c r="B85" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9805,21 +9810,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9829,10 +9834,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>495461</v>
+        <v>495777</v>
       </c>
       <c r="R85" t="n">
-        <v>7040125</v>
+        <v>7040083</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9865,11 +9870,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10090,32 +10090,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129809135</v>
+        <v>129809081</v>
       </c>
       <c r="B88" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>495536</v>
+        <v>495568</v>
       </c>
       <c r="R88" t="n">
-        <v>7040124</v>
+        <v>7040032</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10161,6 +10161,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10187,52 +10192,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129809580</v>
+        <v>129809135</v>
       </c>
       <c r="B89" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>495517</v>
+        <v>495536</v>
       </c>
       <c r="R89" t="n">
-        <v>7040108</v>
+        <v>7040124</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10267,65 +10265,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På barken av en upplyft död nedfallen sälg.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129809081</v>
+        <v>129809580</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10333,34 +10300,41 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>495568</v>
+        <v>495517</v>
       </c>
       <c r="R90" t="n">
-        <v>7040032</v>
+        <v>7040108</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10397,7 +10371,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På barken av en upplyft död nedfallen sälg.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10406,18 +10380,44 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11253,10 +11253,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129809088</v>
+        <v>129809569</v>
       </c>
       <c r="B98" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11264,34 +11264,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>495461</v>
+        <v>495637</v>
       </c>
       <c r="R98" t="n">
-        <v>7039960</v>
+        <v>7040173</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11326,6 +11334,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs några meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11334,23 +11347,48 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129809086</v>
+        <v>129809088</v>
       </c>
       <c r="B99" t="n">
         <v>80186</v>
@@ -11385,10 +11423,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>495579</v>
+        <v>495461</v>
       </c>
       <c r="R99" t="n">
-        <v>7040079</v>
+        <v>7039960</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11447,10 +11485,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129809569</v>
+        <v>129809086</v>
       </c>
       <c r="B100" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11458,42 +11496,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>495637</v>
+        <v>495579</v>
       </c>
       <c r="R100" t="n">
-        <v>7040173</v>
+        <v>7040079</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11528,11 +11558,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs några meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11541,51 +11566,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129809116</v>
+        <v>129809594</v>
       </c>
       <c r="B101" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11593,34 +11593,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>495435</v>
+        <v>495544</v>
       </c>
       <c r="R101" t="n">
-        <v>7039823</v>
+        <v>7039898</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11657,7 +11660,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11666,25 +11669,51 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129809594</v>
+        <v>129809598</v>
       </c>
       <c r="B102" t="n">
         <v>79081</v>
@@ -11722,10 +11751,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>495544</v>
+        <v>495684</v>
       </c>
       <c r="R102" t="n">
-        <v>7039898</v>
+        <v>7040002</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11758,11 +11787,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11815,10 +11839,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129809598</v>
+        <v>129809100</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>82918</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11826,37 +11850,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495684</v>
+        <v>495592</v>
       </c>
       <c r="R103" t="n">
-        <v>7040002</v>
+        <v>7039912</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11901,50 +11922,25 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129809100</v>
+        <v>129809116</v>
       </c>
       <c r="B104" t="n">
-        <v>82918</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11952,21 +11948,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11976,10 +11972,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>495592</v>
+        <v>495435</v>
       </c>
       <c r="R104" t="n">
-        <v>7039912</v>
+        <v>7039823</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12014,13 +12010,17 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12276,10 +12276,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809570</v>
+        <v>129809586</v>
       </c>
       <c r="B107" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12287,29 +12287,28 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -12319,10 +12318,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495618</v>
+        <v>495477</v>
       </c>
       <c r="R107" t="n">
-        <v>7040246</v>
+        <v>7039974</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12359,7 +12358,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Växer i en stubbe av en knäckt gran.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12368,6 +12367,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12388,12 +12388,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12411,10 +12411,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129809586</v>
+        <v>129809102</v>
       </c>
       <c r="B108" t="n">
-        <v>91595</v>
+        <v>83052</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12422,41 +12422,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>495477</v>
+        <v>495533</v>
       </c>
       <c r="R108" t="n">
-        <v>7039974</v>
+        <v>7039800</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12491,65 +12484,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Växer i en stubbe av en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129809102</v>
+        <v>129809570</v>
       </c>
       <c r="B109" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12557,34 +12519,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>495533</v>
+        <v>495618</v>
       </c>
       <c r="R109" t="n">
-        <v>7039800</v>
+        <v>7040246</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12619,6 +12589,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12627,16 +12602,41 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -2620,32 +2620,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809076</v>
+        <v>129809134</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>80215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495663</v>
+        <v>495561</v>
       </c>
       <c r="R19" t="n">
-        <v>7040097</v>
+        <v>7039987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809159</v>
+        <v>129809076</v>
       </c>
       <c r="B20" t="n">
-        <v>83044</v>
+        <v>91599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495530</v>
+        <v>495663</v>
       </c>
       <c r="R20" t="n">
-        <v>7040111</v>
+        <v>7040097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129809114</v>
+        <v>129809159</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>83044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495559</v>
+        <v>495530</v>
       </c>
       <c r="R21" t="n">
-        <v>7039895</v>
+        <v>7040111</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,11 +2885,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809144</v>
+        <v>129809602</v>
       </c>
       <c r="B22" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,34 +2922,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495584</v>
+        <v>495479</v>
       </c>
       <c r="R22" t="n">
-        <v>7040207</v>
+        <v>7039967</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2995,25 +2993,51 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809602</v>
+        <v>129809596</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -3051,10 +3075,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495479</v>
+        <v>495570</v>
       </c>
       <c r="R23" t="n">
-        <v>7039967</v>
+        <v>7039935</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,10 +3163,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809596</v>
+        <v>129809152</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,37 +3174,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495570</v>
+        <v>495696</v>
       </c>
       <c r="R24" t="n">
-        <v>7039935</v>
+        <v>7040090</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3221,54 +3238,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129809152</v>
+        <v>129809114</v>
       </c>
       <c r="B25" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,19 +3267,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3296,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495696</v>
+        <v>495559</v>
       </c>
       <c r="R25" t="n">
-        <v>7040090</v>
+        <v>7039895</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,6 +3327,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3358,32 +3358,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129809134</v>
+        <v>129809144</v>
       </c>
       <c r="B26" t="n">
-        <v>80215</v>
+        <v>78094</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495561</v>
+        <v>495584</v>
       </c>
       <c r="R26" t="n">
-        <v>7039987</v>
+        <v>7040207</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129809096</v>
+        <v>129809147</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495570</v>
+        <v>495722</v>
       </c>
       <c r="R27" t="n">
-        <v>7040065</v>
+        <v>7040115</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129809131</v>
+        <v>129809096</v>
       </c>
       <c r="B28" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495455</v>
+        <v>495570</v>
       </c>
       <c r="R28" t="n">
-        <v>7040119</v>
+        <v>7040065</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,11 +3623,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,10 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129809147</v>
+        <v>129809124</v>
       </c>
       <c r="B29" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,21 +3660,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3689,10 +3684,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495722</v>
+        <v>495478</v>
       </c>
       <c r="R29" t="n">
-        <v>7040115</v>
+        <v>7040087</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3725,6 +3720,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3751,10 +3751,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129809124</v>
+        <v>129809131</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,21 +3762,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495478</v>
+        <v>495455</v>
       </c>
       <c r="R30" t="n">
-        <v>7040087</v>
+        <v>7040119</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -6032,41 +6032,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809571</v>
+        <v>129809606</v>
       </c>
       <c r="B51" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6074,10 +6070,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495699</v>
+        <v>495603</v>
       </c>
       <c r="R51" t="n">
-        <v>7040018</v>
+        <v>7040220</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6112,11 +6108,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6134,22 +6125,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6167,52 +6158,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809584</v>
+        <v>129809142</v>
       </c>
       <c r="B52" t="n">
-        <v>80222</v>
+        <v>78094</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495504</v>
+        <v>495682</v>
       </c>
       <c r="R52" t="n">
-        <v>7040027</v>
+        <v>7039932</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6247,65 +6231,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På barken av en smal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129809606</v>
+        <v>129809103</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6313,37 +6266,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495603</v>
+        <v>495680</v>
       </c>
       <c r="R53" t="n">
-        <v>7040220</v>
+        <v>7039973</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6384,89 +6334,70 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809103</v>
+        <v>129809571</v>
       </c>
       <c r="B54" t="n">
-        <v>83052</v>
+        <v>80215</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495680</v>
+        <v>495699</v>
       </c>
       <c r="R54" t="n">
-        <v>7039973</v>
+        <v>7040018</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6501,69 +6432,107 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129809142</v>
+        <v>129809584</v>
       </c>
       <c r="B55" t="n">
-        <v>78094</v>
+        <v>80222</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495682</v>
+        <v>495504</v>
       </c>
       <c r="R55" t="n">
-        <v>7039932</v>
+        <v>7040027</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6598,24 +6567,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På barken av en smal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -11839,10 +11839,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129809100</v>
+        <v>129809116</v>
       </c>
       <c r="B103" t="n">
-        <v>82918</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11850,21 +11850,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11874,10 +11874,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495592</v>
+        <v>495435</v>
       </c>
       <c r="R103" t="n">
-        <v>7039912</v>
+        <v>7039823</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11912,13 +11912,17 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11937,10 +11941,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129809116</v>
+        <v>129809100</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>82918</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11948,21 +11952,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11972,10 +11976,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>495435</v>
+        <v>495592</v>
       </c>
       <c r="R104" t="n">
-        <v>7039823</v>
+        <v>7039912</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12010,17 +12014,13 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12039,39 +12039,39 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129809581</v>
+        <v>129809586</v>
       </c>
       <c r="B105" t="n">
-        <v>80222</v>
+        <v>91595</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>495749</v>
+        <v>495477</v>
       </c>
       <c r="R105" t="n">
-        <v>7040011</v>
+        <v>7039974</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På bark på en smal sälg.</t>
+          <t>Växer i en stubbe av en knäckt gran.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12141,22 +12141,22 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12174,10 +12174,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129809113</v>
+        <v>129809102</v>
       </c>
       <c r="B106" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12185,21 +12185,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12209,10 +12209,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>495541</v>
+        <v>495533</v>
       </c>
       <c r="R106" t="n">
-        <v>7039874</v>
+        <v>7039800</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12245,11 +12245,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12276,39 +12271,39 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809586</v>
+        <v>129809581</v>
       </c>
       <c r="B107" t="n">
-        <v>91595</v>
+        <v>80222</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -12318,10 +12313,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495477</v>
+        <v>495749</v>
       </c>
       <c r="R107" t="n">
-        <v>7039974</v>
+        <v>7040011</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12358,7 +12353,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Växer i en stubbe av en knäckt gran.</t>
+          <t>På bark på en smal sälg.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12378,22 +12373,22 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12411,10 +12406,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129809102</v>
+        <v>129809113</v>
       </c>
       <c r="B108" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12422,21 +12417,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12446,10 +12441,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>495533</v>
+        <v>495541</v>
       </c>
       <c r="R108" t="n">
-        <v>7039800</v>
+        <v>7039874</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12482,6 +12477,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809603</v>
+        <v>129809157</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>82921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495504</v>
+        <v>495620</v>
       </c>
       <c r="R2" t="n">
-        <v>7040017</v>
+        <v>7040063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,55 +748,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -809,7 +775,7 @@
         <v>129809595</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809087</v>
+        <v>129809603</v>
       </c>
       <c r="B4" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,34 +909,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495710</v>
+        <v>495504</v>
       </c>
       <c r="R4" t="n">
-        <v>7039992</v>
+        <v>7040017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,24 +974,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
         <v>129809578</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>129809089</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129809109</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809157</v>
+        <v>129809087</v>
       </c>
       <c r="B8" t="n">
-        <v>82918</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,21 +1394,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495620</v>
+        <v>495710</v>
       </c>
       <c r="R8" t="n">
-        <v>7040063</v>
+        <v>7039992</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,7 +1483,7 @@
         <v>129809611</v>
       </c>
       <c r="B9" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809139</v>
+        <v>129809599</v>
       </c>
       <c r="B10" t="n">
-        <v>80187</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,34 +1607,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495484</v>
+        <v>495719</v>
       </c>
       <c r="R10" t="n">
-        <v>7040082</v>
+        <v>7040059</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,24 +1672,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1824,7 +1858,7 @@
         <v>129809107</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1955,7 @@
         <v>129809146</v>
       </c>
       <c r="B13" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809599</v>
+        <v>129809139</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>80190</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,37 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495719</v>
+        <v>495484</v>
       </c>
       <c r="R14" t="n">
-        <v>7040059</v>
+        <v>7040082</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,55 +2122,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
         <v>129809573</v>
       </c>
       <c r="B15" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129809583</v>
       </c>
       <c r="B16" t="n">
-        <v>80222</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>129809115</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129809082</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809134</v>
+        <v>129809159</v>
       </c>
       <c r="B19" t="n">
-        <v>80215</v>
+        <v>83047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495561</v>
+        <v>495530</v>
       </c>
       <c r="R19" t="n">
-        <v>7039987</v>
+        <v>7040111</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,7 +2720,7 @@
         <v>129809076</v>
       </c>
       <c r="B20" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129809159</v>
+        <v>129809152</v>
       </c>
       <c r="B21" t="n">
-        <v>83044</v>
+        <v>91622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,23 +2825,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2849,10 +2845,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495530</v>
+        <v>495696</v>
       </c>
       <c r="R21" t="n">
-        <v>7040111</v>
+        <v>7040090</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2910,7 @@
         <v>129809602</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3036,7 @@
         <v>129809596</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,30 +3159,34 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809152</v>
+        <v>129809134</v>
       </c>
       <c r="B24" t="n">
-        <v>91619</v>
+        <v>80218</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495696</v>
+        <v>495561</v>
       </c>
       <c r="R24" t="n">
-        <v>7040090</v>
+        <v>7039987</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
         <v>129809114</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>129809144</v>
       </c>
       <c r="B26" t="n">
-        <v>78094</v>
+        <v>78097</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129809147</v>
+        <v>129809124</v>
       </c>
       <c r="B27" t="n">
-        <v>91595</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495722</v>
+        <v>495478</v>
       </c>
       <c r="R27" t="n">
-        <v>7040115</v>
+        <v>7040087</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,6 +3526,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3552,10 +3557,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129809096</v>
+        <v>129809131</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>57895</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,21 +3568,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3587,10 +3592,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495570</v>
+        <v>495455</v>
       </c>
       <c r="R28" t="n">
-        <v>7040065</v>
+        <v>7040119</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,6 +3628,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,10 +3659,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129809124</v>
+        <v>129809147</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>91598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3660,21 +3670,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3684,10 +3694,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495478</v>
+        <v>495722</v>
       </c>
       <c r="R29" t="n">
-        <v>7040087</v>
+        <v>7040115</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,11 +3730,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3751,10 +3756,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129809131</v>
+        <v>129809096</v>
       </c>
       <c r="B30" t="n">
-        <v>57896</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,21 +3767,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3786,10 +3791,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495455</v>
+        <v>495570</v>
       </c>
       <c r="R30" t="n">
-        <v>7040119</v>
+        <v>7040065</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,11 +3827,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129809105</v>
+        <v>129809572</v>
       </c>
       <c r="B31" t="n">
-        <v>91563</v>
+        <v>80218</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,34 +3864,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495461</v>
+        <v>495579</v>
       </c>
       <c r="R31" t="n">
-        <v>7039930</v>
+        <v>7039969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3926,54 +3933,89 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På barken av en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809094</v>
+        <v>129809141</v>
       </c>
       <c r="B32" t="n">
-        <v>91619</v>
+        <v>80225</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3981,10 +4023,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495459</v>
+        <v>495483</v>
       </c>
       <c r="R32" t="n">
-        <v>7039862</v>
+        <v>7040081</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4025,7 +4067,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4044,39 +4085,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809572</v>
+        <v>129809567</v>
       </c>
       <c r="B33" t="n">
-        <v>80215</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4086,10 +4128,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495579</v>
+        <v>495594</v>
       </c>
       <c r="R33" t="n">
-        <v>7039969</v>
+        <v>7039971</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,7 +4168,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På barken av en sälglåga.</t>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4135,7 +4177,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4146,22 +4187,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4179,32 +4220,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809141</v>
+        <v>129809126</v>
       </c>
       <c r="B34" t="n">
-        <v>80222</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4214,10 +4255,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495483</v>
+        <v>495467</v>
       </c>
       <c r="R34" t="n">
-        <v>7040081</v>
+        <v>7040110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4250,6 +4291,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4276,61 +4322,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129809137</v>
+        <v>129809105</v>
       </c>
       <c r="B35" t="n">
-        <v>57733</v>
+        <v>91566</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495739</v>
+        <v>495461</v>
       </c>
       <c r="R35" t="n">
-        <v>7040024</v>
+        <v>7039930</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4419,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129809567</v>
+        <v>129809094</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>91622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4400,42 +4430,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495594</v>
+        <v>495459</v>
       </c>
       <c r="R36" t="n">
-        <v>7039971</v>
+        <v>7039862</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4470,64 +4488,35 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129809126</v>
+        <v>129809137</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,16 +4524,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4552,17 +4541,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495467</v>
+        <v>495739</v>
       </c>
       <c r="R37" t="n">
-        <v>7040110</v>
+        <v>7040024</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4595,11 +4600,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4626,32 +4626,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129809111</v>
+        <v>129809140</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>92055</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495558</v>
+        <v>495671</v>
       </c>
       <c r="R38" t="n">
-        <v>7039811</v>
+        <v>7039845</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4697,11 +4697,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4728,45 +4723,52 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129809083</v>
+        <v>129809561</v>
       </c>
       <c r="B39" t="n">
-        <v>56926</v>
+        <v>91602</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495476</v>
+        <v>495774</v>
       </c>
       <c r="R39" t="n">
-        <v>7040074</v>
+        <v>7040061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4801,34 +4803,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129809561</v>
+        <v>129809604</v>
       </c>
       <c r="B40" t="n">
-        <v>91599</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4836,30 +4869,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4867,10 +4896,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495774</v>
+        <v>495501</v>
       </c>
       <c r="R40" t="n">
-        <v>7040061</v>
+        <v>7040069</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4905,11 +4934,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4937,12 +4961,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4960,32 +4984,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809140</v>
+        <v>129809138</v>
       </c>
       <c r="B41" t="n">
-        <v>92052</v>
+        <v>57734</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4995,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495671</v>
+        <v>495613</v>
       </c>
       <c r="R41" t="n">
-        <v>7039845</v>
+        <v>7039922</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5057,48 +5081,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809604</v>
+        <v>129809084</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>80218</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495501</v>
+        <v>495651</v>
       </c>
       <c r="R42" t="n">
-        <v>7040069</v>
+        <v>7039928</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,76 +5160,50 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129809084</v>
+        <v>129809111</v>
       </c>
       <c r="B43" t="n">
-        <v>80215</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5218,10 +5213,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495651</v>
+        <v>495558</v>
       </c>
       <c r="R43" t="n">
-        <v>7039928</v>
+        <v>7039811</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5254,6 +5249,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,32 +5280,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129809138</v>
+        <v>129809083</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>56927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495613</v>
+        <v>495476</v>
       </c>
       <c r="R44" t="n">
-        <v>7039922</v>
+        <v>7040074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5377,10 +5377,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129809091</v>
+        <v>129809605</v>
       </c>
       <c r="B45" t="n">
-        <v>91595</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5388,34 +5388,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495490</v>
+        <v>495546</v>
       </c>
       <c r="R45" t="n">
-        <v>7039928</v>
+        <v>7040104</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5456,28 +5459,54 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129809079</v>
+        <v>129809154</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,21 +5514,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5509,10 +5538,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495550</v>
+        <v>495635</v>
       </c>
       <c r="R46" t="n">
-        <v>7039807</v>
+        <v>7039937</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5545,11 +5574,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5576,10 +5600,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129809605</v>
+        <v>129809592</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,10 +5638,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495546</v>
+        <v>495516</v>
       </c>
       <c r="R47" t="n">
-        <v>7040104</v>
+        <v>7039796</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5650,6 +5674,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5702,10 +5731,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809154</v>
+        <v>129809091</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>91598</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5713,21 +5742,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5737,10 +5766,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495635</v>
+        <v>495490</v>
       </c>
       <c r="R48" t="n">
-        <v>7039937</v>
+        <v>7039928</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5799,10 +5828,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129809592</v>
+        <v>129809079</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5810,37 +5839,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495516</v>
+        <v>495550</v>
       </c>
       <c r="R49" t="n">
-        <v>7039796</v>
+        <v>7039807</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5877,7 +5903,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5886,44 +5912,18 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
         <v>129809080</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>129809606</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>129809142</v>
       </c>
       <c r="B52" t="n">
-        <v>78094</v>
+        <v>78097</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>129809103</v>
       </c>
       <c r="B53" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6352,10 +6352,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809571</v>
+        <v>129809584</v>
       </c>
       <c r="B54" t="n">
-        <v>80215</v>
+        <v>80225</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6363,21 +6363,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495699</v>
+        <v>495504</v>
       </c>
       <c r="R54" t="n">
-        <v>7040018</v>
+        <v>7040027</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>På barken av en smal levande sälg.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6487,10 +6487,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129809584</v>
+        <v>129809571</v>
       </c>
       <c r="B55" t="n">
-        <v>80222</v>
+        <v>80218</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6498,21 +6498,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495504</v>
+        <v>495699</v>
       </c>
       <c r="R55" t="n">
-        <v>7040027</v>
+        <v>7040018</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På barken av en smal levande sälg.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6625,7 +6625,7 @@
         <v>129809155</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>129809078</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>129809110</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6923,52 +6923,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129809563</v>
+        <v>129809150</v>
       </c>
       <c r="B59" t="n">
-        <v>92317</v>
+        <v>91598</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495549</v>
+        <v>495465</v>
       </c>
       <c r="R59" t="n">
-        <v>7039804</v>
+        <v>7039933</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7003,60 +6996,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809150</v>
+        <v>129809562</v>
       </c>
       <c r="B60" t="n">
-        <v>91595</v>
+        <v>91602</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7064,34 +7031,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495465</v>
+        <v>495606</v>
       </c>
       <c r="R60" t="n">
-        <v>7039933</v>
+        <v>7040134</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7126,34 +7100,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809562</v>
+        <v>129809156</v>
       </c>
       <c r="B61" t="n">
-        <v>91599</v>
+        <v>82921</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7161,41 +7166,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495606</v>
+        <v>495664</v>
       </c>
       <c r="R61" t="n">
-        <v>7040134</v>
+        <v>7040037</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7230,87 +7228,56 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129809156</v>
+        <v>129809133</v>
       </c>
       <c r="B62" t="n">
-        <v>82918</v>
+        <v>80218</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7320,10 +7287,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495664</v>
+        <v>495563</v>
       </c>
       <c r="R62" t="n">
-        <v>7040037</v>
+        <v>7039894</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7382,41 +7349,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809153</v>
+        <v>129809610</v>
       </c>
       <c r="B63" t="n">
-        <v>91619</v>
+        <v>100983</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495507</v>
+        <v>495622</v>
       </c>
       <c r="R63" t="n">
-        <v>7040063</v>
+        <v>7039966</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7457,52 +7436,54 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129809133</v>
+        <v>129809153</v>
       </c>
       <c r="B64" t="n">
-        <v>80215</v>
+        <v>91622</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7510,10 +7491,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495563</v>
+        <v>495507</v>
       </c>
       <c r="R64" t="n">
-        <v>7039894</v>
+        <v>7040063</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7572,45 +7553,52 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129809143</v>
+        <v>129809563</v>
       </c>
       <c r="B65" t="n">
-        <v>78094</v>
+        <v>92320</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495700</v>
+        <v>495549</v>
       </c>
       <c r="R65" t="n">
-        <v>7040007</v>
+        <v>7039804</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7645,77 +7633,95 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>I en knäckt gran.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129809610</v>
+        <v>129809143</v>
       </c>
       <c r="B66" t="n">
-        <v>100979</v>
+        <v>78097</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495622</v>
+        <v>495700</v>
       </c>
       <c r="R66" t="n">
-        <v>7039966</v>
+        <v>7040007</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7756,34 +7762,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129809127</v>
+        <v>129809158</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>83047</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,21 +7791,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495608</v>
+        <v>495531</v>
       </c>
       <c r="R67" t="n">
-        <v>7040209</v>
+        <v>7040125</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7851,11 +7851,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7882,32 +7877,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809090</v>
+        <v>129809099</v>
       </c>
       <c r="B68" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7917,10 +7912,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495544</v>
+        <v>495626</v>
       </c>
       <c r="R68" t="n">
-        <v>7040035</v>
+        <v>7040099</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7979,10 +7974,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809158</v>
+        <v>129809098</v>
       </c>
       <c r="B69" t="n">
-        <v>83044</v>
+        <v>79084</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7990,21 +7985,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8014,10 +8009,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495531</v>
+        <v>495709</v>
       </c>
       <c r="R69" t="n">
-        <v>7040125</v>
+        <v>7040119</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8076,10 +8071,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809098</v>
+        <v>129809129</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>57895</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8087,21 +8082,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8111,10 +8106,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495709</v>
+        <v>495522</v>
       </c>
       <c r="R70" t="n">
-        <v>7040119</v>
+        <v>7039794</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8147,6 +8142,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8173,32 +8173,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809099</v>
+        <v>129809090</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495626</v>
+        <v>495544</v>
       </c>
       <c r="R71" t="n">
-        <v>7040099</v>
+        <v>7040035</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8270,10 +8270,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129809129</v>
+        <v>129809127</v>
       </c>
       <c r="B72" t="n">
-        <v>57896</v>
+        <v>57737</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8281,21 +8281,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>495522</v>
+        <v>495608</v>
       </c>
       <c r="R72" t="n">
-        <v>7039794</v>
+        <v>7040209</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809585</v>
+        <v>129809601</v>
       </c>
       <c r="B73" t="n">
-        <v>91595</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,30 +8383,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8414,10 +8410,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495645</v>
+        <v>495583</v>
       </c>
       <c r="R73" t="n">
-        <v>7039861</v>
+        <v>7039969</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8479,12 +8475,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8502,10 +8498,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809579</v>
+        <v>129809600</v>
       </c>
       <c r="B74" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8513,30 +8509,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8544,10 +8536,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495499</v>
+        <v>495604</v>
       </c>
       <c r="R74" t="n">
-        <v>7040089</v>
+        <v>7040032</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8584,7 +8576,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>På gran i äldre  granskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8604,22 +8596,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8637,10 +8629,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809601</v>
+        <v>129809607</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8667,7 +8659,11 @@
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8675,10 +8671,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495583</v>
+        <v>495591</v>
       </c>
       <c r="R75" t="n">
-        <v>7039969</v>
+        <v>7040221</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8711,6 +8707,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Med apothecier på gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8763,10 +8764,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809607</v>
+        <v>129809579</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8774,28 +8775,28 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8805,10 +8806,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495591</v>
+        <v>495499</v>
       </c>
       <c r="R76" t="n">
-        <v>7040221</v>
+        <v>7040089</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8845,7 +8846,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Med apothecier på gran.</t>
+          <t>På bark av en levande sälg.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8865,22 +8866,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8898,10 +8899,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809600</v>
+        <v>129809568</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8909,26 +8910,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8936,10 +8942,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495604</v>
+        <v>495618</v>
       </c>
       <c r="R77" t="n">
-        <v>7040032</v>
+        <v>7040130</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8976,7 +8982,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran i äldre  granskog.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8985,7 +8991,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9006,12 +9011,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9029,10 +9034,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809104</v>
+        <v>129809122</v>
       </c>
       <c r="B78" t="n">
-        <v>83052</v>
+        <v>57737</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9040,21 +9045,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9064,10 +9069,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495595</v>
+        <v>495433</v>
       </c>
       <c r="R78" t="n">
-        <v>7040220</v>
+        <v>7039995</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9100,6 +9105,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9126,10 +9136,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129809101</v>
+        <v>129809130</v>
       </c>
       <c r="B79" t="n">
-        <v>83052</v>
+        <v>57895</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9137,21 +9147,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9161,10 +9171,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>495682</v>
+        <v>495569</v>
       </c>
       <c r="R79" t="n">
-        <v>7039933</v>
+        <v>7039991</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9197,6 +9207,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9223,10 +9238,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809568</v>
+        <v>129809585</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>91598</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9234,29 +9249,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9266,10 +9280,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495618</v>
+        <v>495645</v>
       </c>
       <c r="R80" t="n">
-        <v>7040130</v>
+        <v>7039861</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9304,17 +9318,13 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9358,10 +9368,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809122</v>
+        <v>129809104</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>83055</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9369,21 +9379,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9393,10 +9403,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495433</v>
+        <v>495595</v>
       </c>
       <c r="R81" t="n">
-        <v>7039995</v>
+        <v>7040220</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9429,11 +9439,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9460,10 +9465,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129809130</v>
+        <v>129809101</v>
       </c>
       <c r="B82" t="n">
-        <v>57896</v>
+        <v>83055</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9471,21 +9476,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9495,10 +9500,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>495569</v>
+        <v>495682</v>
       </c>
       <c r="R82" t="n">
-        <v>7039991</v>
+        <v>7039933</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9531,11 +9536,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9562,10 +9562,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129809574</v>
+        <v>129809106</v>
       </c>
       <c r="B83" t="n">
-        <v>57733</v>
+        <v>91602</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9573,42 +9573,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>495509</v>
+        <v>495777</v>
       </c>
       <c r="R83" t="n">
-        <v>7040092</v>
+        <v>7040083</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9643,11 +9635,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9656,41 +9643,16 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9700,7 +9662,7 @@
         <v>129809125</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9799,10 +9761,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129809106</v>
+        <v>129809574</v>
       </c>
       <c r="B85" t="n">
-        <v>91599</v>
+        <v>57734</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9810,34 +9772,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>495777</v>
+        <v>495509</v>
       </c>
       <c r="R85" t="n">
-        <v>7040083</v>
+        <v>7040092</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9872,6 +9842,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9880,16 +9855,41 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9899,7 +9899,7 @@
         <v>129809145</v>
       </c>
       <c r="B86" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>129809148</v>
       </c>
       <c r="B87" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10090,32 +10090,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129809081</v>
+        <v>129809135</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>80218</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>495568</v>
+        <v>495536</v>
       </c>
       <c r="R88" t="n">
-        <v>7040032</v>
+        <v>7040124</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10161,11 +10161,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10192,45 +10187,52 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129809135</v>
+        <v>129809580</v>
       </c>
       <c r="B89" t="n">
-        <v>80215</v>
+        <v>80189</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>495536</v>
+        <v>495517</v>
       </c>
       <c r="R89" t="n">
-        <v>7040124</v>
+        <v>7040108</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10265,34 +10267,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På barken av en upplyft död nedfallen sälg.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129809580</v>
+        <v>129809081</v>
       </c>
       <c r="B90" t="n">
-        <v>80186</v>
+        <v>57737</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10300,41 +10333,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>495517</v>
+        <v>495568</v>
       </c>
       <c r="R90" t="n">
-        <v>7040108</v>
+        <v>7040032</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10371,7 +10397,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På barken av en upplyft död nedfallen sälg.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10380,44 +10406,18 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10427,7 +10427,7 @@
         <v>129809587</v>
       </c>
       <c r="B91" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>129809608</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>129809597</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>129809095</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>129809590</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>129809093</v>
       </c>
       <c r="B96" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>129809593</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11253,10 +11253,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129809569</v>
+        <v>129809086</v>
       </c>
       <c r="B98" t="n">
-        <v>57736</v>
+        <v>80189</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11264,42 +11264,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>495637</v>
+        <v>495579</v>
       </c>
       <c r="R98" t="n">
-        <v>7040173</v>
+        <v>7040079</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11334,11 +11326,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs några meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11347,51 +11334,26 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129809088</v>
+        <v>129809569</v>
       </c>
       <c r="B99" t="n">
-        <v>80186</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11399,34 +11361,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>495461</v>
+        <v>495637</v>
       </c>
       <c r="R99" t="n">
-        <v>7039960</v>
+        <v>7040173</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11461,6 +11431,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs några meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11469,26 +11444,51 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129809086</v>
+        <v>129809088</v>
       </c>
       <c r="B100" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11520,10 +11520,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>495579</v>
+        <v>495461</v>
       </c>
       <c r="R100" t="n">
-        <v>7040079</v>
+        <v>7039960</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129809594</v>
+        <v>129809100</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>82921</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11593,37 +11593,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>495544</v>
+        <v>495592</v>
       </c>
       <c r="R101" t="n">
-        <v>7039898</v>
+        <v>7039912</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11658,11 +11655,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11673,50 +11665,25 @@
       <c r="AG101" t="b">
         <v>0</v>
       </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129809598</v>
+        <v>129809594</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11751,10 +11718,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>495684</v>
+        <v>495544</v>
       </c>
       <c r="R102" t="n">
-        <v>7040002</v>
+        <v>7039898</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11787,6 +11754,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11839,10 +11811,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129809116</v>
+        <v>129809598</v>
       </c>
       <c r="B103" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11850,34 +11822,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495435</v>
+        <v>495684</v>
       </c>
       <c r="R103" t="n">
-        <v>7039823</v>
+        <v>7040002</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11912,39 +11887,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129809100</v>
+        <v>129809116</v>
       </c>
       <c r="B104" t="n">
-        <v>82918</v>
+        <v>57737</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11952,21 +11948,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11976,10 +11972,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>495592</v>
+        <v>495435</v>
       </c>
       <c r="R104" t="n">
-        <v>7039912</v>
+        <v>7039823</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12014,13 +12010,17 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>129809586</v>
       </c>
       <c r="B105" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>129809102</v>
       </c>
       <c r="B106" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>129809581</v>
       </c>
       <c r="B107" t="n">
-        <v>80222</v>
+        <v>80225</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>129809113</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>129809570</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>129809151</v>
       </c>
       <c r="B110" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>129809582</v>
       </c>
       <c r="B111" t="n">
-        <v>80222</v>
+        <v>80225</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>129809085</v>
       </c>
       <c r="B112" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>129809566</v>
       </c>
       <c r="B113" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>129835891</v>
       </c>
       <c r="B114" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>129835888</v>
       </c>
       <c r="B115" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>129835887</v>
       </c>
       <c r="B116" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>129835890</v>
       </c>
       <c r="B117" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>129835889</v>
       </c>
       <c r="B118" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809157</v>
+        <v>129809109</v>
       </c>
       <c r="B2" t="n">
-        <v>82921</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495620</v>
+        <v>495738</v>
       </c>
       <c r="R2" t="n">
-        <v>7040063</v>
+        <v>7040008</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +766,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809595</v>
+        <v>129809157</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>82921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495548</v>
+        <v>495620</v>
       </c>
       <c r="R3" t="n">
-        <v>7039913</v>
+        <v>7040063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,51 +876,25 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809603</v>
+        <v>129809595</v>
       </c>
       <c r="B4" t="n">
         <v>79084</v>
@@ -936,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495504</v>
+        <v>495548</v>
       </c>
       <c r="R4" t="n">
-        <v>7040017</v>
+        <v>7039913</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809578</v>
+        <v>129809603</v>
       </c>
       <c r="B5" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,30 +1031,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495701</v>
+        <v>495504</v>
       </c>
       <c r="R5" t="n">
-        <v>7040014</v>
+        <v>7040017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1118,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1164,7 +1151,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809089</v>
+        <v>129809578</v>
       </c>
       <c r="B6" t="n">
         <v>80189</v>
@@ -1193,16 +1180,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495476</v>
+        <v>495701</v>
       </c>
       <c r="R6" t="n">
-        <v>7040074</v>
+        <v>7040014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,34 +1231,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809109</v>
+        <v>129809087</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,54 +1297,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495738</v>
+        <v>495710</v>
       </c>
       <c r="R7" t="n">
-        <v>7040008</v>
+        <v>7039992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,11 +1357,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,7 +1383,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809087</v>
+        <v>129809089</v>
       </c>
       <c r="B8" t="n">
         <v>80189</v>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495710</v>
+        <v>495476</v>
       </c>
       <c r="R8" t="n">
-        <v>7039992</v>
+        <v>7040074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809599</v>
+        <v>129809139</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>80190</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,37 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495719</v>
+        <v>495484</v>
       </c>
       <c r="R10" t="n">
-        <v>7040059</v>
+        <v>7040082</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,65 +1669,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129809575</v>
+        <v>129809599</v>
       </c>
       <c r="B11" t="n">
-        <v>56310</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,50 +1704,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495639</v>
+        <v>495719</v>
       </c>
       <c r="R11" t="n">
-        <v>7039976</v>
+        <v>7040059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,7 +1771,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,17 +1780,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2049,45 +2018,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809139</v>
+        <v>129809573</v>
       </c>
       <c r="B14" t="n">
-        <v>80190</v>
+        <v>80218</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495484</v>
+        <v>495496</v>
       </c>
       <c r="R14" t="n">
-        <v>7040082</v>
+        <v>7040079</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,34 +2098,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På bark av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129809573</v>
+        <v>129809583</v>
       </c>
       <c r="B15" t="n">
-        <v>80218</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,21 +2164,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2188,10 +2195,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495496</v>
+        <v>495575</v>
       </c>
       <c r="R15" t="n">
-        <v>7040079</v>
+        <v>7039971</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2235,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>På barken av en död sälglåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,12 +2265,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2281,52 +2288,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129809583</v>
+        <v>129809115</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495575</v>
+        <v>495682</v>
       </c>
       <c r="R16" t="n">
-        <v>7039971</v>
+        <v>7040065</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På barken av en död sälglåga.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,51 +2372,25 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129809115</v>
+        <v>129809082</v>
       </c>
       <c r="B17" t="n">
         <v>57737</v>
@@ -2451,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495682</v>
+        <v>495470</v>
       </c>
       <c r="R17" t="n">
-        <v>7040065</v>
+        <v>7039843</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2518,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129809082</v>
+        <v>129809575</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>56310</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2529,34 +2503,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495470</v>
+        <v>495639</v>
       </c>
       <c r="R18" t="n">
-        <v>7039843</v>
+        <v>7039976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2583,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,26 +2594,36 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809159</v>
+        <v>129809076</v>
       </c>
       <c r="B19" t="n">
-        <v>83047</v>
+        <v>91602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495530</v>
+        <v>495663</v>
       </c>
       <c r="R19" t="n">
-        <v>7040111</v>
+        <v>7040097</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809076</v>
+        <v>129809134</v>
       </c>
       <c r="B20" t="n">
-        <v>91602</v>
+        <v>80218</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495663</v>
+        <v>495561</v>
       </c>
       <c r="R20" t="n">
-        <v>7040097</v>
+        <v>7039987</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129809152</v>
+        <v>129809159</v>
       </c>
       <c r="B21" t="n">
-        <v>91622</v>
+        <v>83047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,19 +2825,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2845,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495696</v>
+        <v>495530</v>
       </c>
       <c r="R21" t="n">
-        <v>7040090</v>
+        <v>7040111</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2907,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809602</v>
+        <v>129809152</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>91622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2918,37 +2922,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495479</v>
+        <v>495696</v>
       </c>
       <c r="R22" t="n">
-        <v>7039967</v>
+        <v>7040090</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2989,51 +2986,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809596</v>
+        <v>129809602</v>
       </c>
       <c r="B23" t="n">
         <v>79084</v>
@@ -3071,10 +3042,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495570</v>
+        <v>495479</v>
       </c>
       <c r="R23" t="n">
-        <v>7039935</v>
+        <v>7039967</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,45 +3130,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809134</v>
+        <v>129809596</v>
       </c>
       <c r="B24" t="n">
-        <v>80218</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495561</v>
+        <v>495570</v>
       </c>
       <c r="R24" t="n">
-        <v>7039987</v>
+        <v>7039935</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,18 +3212,44 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129809124</v>
+        <v>129809096</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495478</v>
+        <v>495570</v>
       </c>
       <c r="R27" t="n">
-        <v>7040087</v>
+        <v>7040065</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,11 +3526,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3557,10 +3552,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129809131</v>
+        <v>129809124</v>
       </c>
       <c r="B28" t="n">
-        <v>57895</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3568,21 +3563,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3592,10 +3587,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495455</v>
+        <v>495478</v>
       </c>
       <c r="R28" t="n">
-        <v>7040119</v>
+        <v>7040087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3632,7 +3627,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3659,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129809147</v>
+        <v>129809131</v>
       </c>
       <c r="B29" t="n">
-        <v>91598</v>
+        <v>57895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3670,21 +3665,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3694,10 +3689,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495722</v>
+        <v>495455</v>
       </c>
       <c r="R29" t="n">
-        <v>7040115</v>
+        <v>7040119</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3730,6 +3725,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129809096</v>
+        <v>129809147</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>91598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495570</v>
+        <v>495722</v>
       </c>
       <c r="R30" t="n">
-        <v>7040065</v>
+        <v>7040115</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3853,39 +3853,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129809572</v>
+        <v>129809137</v>
       </c>
       <c r="B31" t="n">
-        <v>80218</v>
+        <v>57734</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3895,10 +3904,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495579</v>
+        <v>495739</v>
       </c>
       <c r="R31" t="n">
-        <v>7039969</v>
+        <v>7040024</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,65 +3942,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På barken av en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809141</v>
+        <v>129809105</v>
       </c>
       <c r="B32" t="n">
-        <v>80225</v>
+        <v>91566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,21 +3977,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4023,10 +4001,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495483</v>
+        <v>495461</v>
       </c>
       <c r="R32" t="n">
-        <v>7040081</v>
+        <v>7039930</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4085,10 +4063,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809567</v>
+        <v>129809094</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4096,42 +4074,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495594</v>
+        <v>495459</v>
       </c>
       <c r="R33" t="n">
-        <v>7039971</v>
+        <v>7039862</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4166,99 +4132,77 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809126</v>
+        <v>129809572</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>80218</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495467</v>
+        <v>495579</v>
       </c>
       <c r="R34" t="n">
-        <v>7040110</v>
+        <v>7039969</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4295,7 +4239,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På barken av en sälglåga.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4304,28 +4248,54 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129809105</v>
+        <v>129809141</v>
       </c>
       <c r="B35" t="n">
-        <v>91566</v>
+        <v>80225</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4357,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495461</v>
+        <v>495483</v>
       </c>
       <c r="R35" t="n">
-        <v>7039930</v>
+        <v>7040081</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4419,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129809094</v>
+        <v>129809567</v>
       </c>
       <c r="B36" t="n">
-        <v>91622</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,30 +4400,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495459</v>
+        <v>495594</v>
       </c>
       <c r="R36" t="n">
-        <v>7039862</v>
+        <v>7039971</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4488,35 +4470,64 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129809137</v>
+        <v>129809126</v>
       </c>
       <c r="B37" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,16 +4535,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4541,33 +4552,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495739</v>
+        <v>495467</v>
       </c>
       <c r="R37" t="n">
-        <v>7040024</v>
+        <v>7040110</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4600,6 +4595,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4626,32 +4626,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129809140</v>
+        <v>129809111</v>
       </c>
       <c r="B38" t="n">
-        <v>92055</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495671</v>
+        <v>495558</v>
       </c>
       <c r="R38" t="n">
-        <v>7039845</v>
+        <v>7039811</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4697,6 +4697,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4723,52 +4728,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129809561</v>
+        <v>129809083</v>
       </c>
       <c r="B39" t="n">
-        <v>91602</v>
+        <v>56927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495774</v>
+        <v>495476</v>
       </c>
       <c r="R39" t="n">
-        <v>7040061</v>
+        <v>7040074</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4803,103 +4801,69 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129809604</v>
+        <v>129809140</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>92055</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495501</v>
+        <v>495671</v>
       </c>
       <c r="R40" t="n">
-        <v>7040069</v>
+        <v>7039845</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4940,54 +4904,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809138</v>
+        <v>129809561</v>
       </c>
       <c r="B41" t="n">
-        <v>57734</v>
+        <v>91602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,34 +4933,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495613</v>
+        <v>495774</v>
       </c>
       <c r="R41" t="n">
-        <v>7039922</v>
+        <v>7040061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5057,69 +5002,103 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809084</v>
+        <v>129809604</v>
       </c>
       <c r="B42" t="n">
-        <v>80218</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495651</v>
+        <v>495501</v>
       </c>
       <c r="R42" t="n">
-        <v>7039928</v>
+        <v>7040069</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5160,50 +5139,76 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129809111</v>
+        <v>129809084</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>80218</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5213,10 +5218,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495558</v>
+        <v>495651</v>
       </c>
       <c r="R43" t="n">
-        <v>7039811</v>
+        <v>7039928</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5249,11 +5254,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,32 +5280,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129809083</v>
+        <v>129809138</v>
       </c>
       <c r="B44" t="n">
-        <v>56927</v>
+        <v>57734</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495476</v>
+        <v>495613</v>
       </c>
       <c r="R44" t="n">
-        <v>7040074</v>
+        <v>7039922</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809142</v>
+        <v>129809103</v>
       </c>
       <c r="B52" t="n">
-        <v>78097</v>
+        <v>83055</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6169,21 +6169,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495682</v>
+        <v>495680</v>
       </c>
       <c r="R52" t="n">
-        <v>7039932</v>
+        <v>7039973</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6255,45 +6255,52 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129809103</v>
+        <v>129809584</v>
       </c>
       <c r="B53" t="n">
-        <v>83055</v>
+        <v>80225</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495680</v>
+        <v>495504</v>
       </c>
       <c r="R53" t="n">
-        <v>7039973</v>
+        <v>7040027</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6328,34 +6335,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På barken av en smal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809584</v>
+        <v>129809571</v>
       </c>
       <c r="B54" t="n">
-        <v>80225</v>
+        <v>80218</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6363,21 +6401,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6394,10 +6432,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495504</v>
+        <v>495699</v>
       </c>
       <c r="R54" t="n">
-        <v>7040027</v>
+        <v>7040018</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6434,7 +6472,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På barken av en smal levande sälg.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6487,52 +6525,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129809571</v>
+        <v>129809142</v>
       </c>
       <c r="B55" t="n">
-        <v>80218</v>
+        <v>78097</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495699</v>
+        <v>495682</v>
       </c>
       <c r="R55" t="n">
-        <v>7040018</v>
+        <v>7039932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6567,55 +6598,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129809150</v>
+        <v>129809562</v>
       </c>
       <c r="B59" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,34 +6934,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495465</v>
+        <v>495606</v>
       </c>
       <c r="R59" t="n">
-        <v>7039933</v>
+        <v>7040134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6996,34 +7003,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809562</v>
+        <v>129809156</v>
       </c>
       <c r="B60" t="n">
-        <v>91602</v>
+        <v>82921</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7031,41 +7069,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495606</v>
+        <v>495664</v>
       </c>
       <c r="R60" t="n">
-        <v>7040134</v>
+        <v>7040037</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7100,65 +7131,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809156</v>
+        <v>129809150</v>
       </c>
       <c r="B61" t="n">
-        <v>82921</v>
+        <v>91598</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7166,21 +7166,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7190,10 +7190,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495664</v>
+        <v>495465</v>
       </c>
       <c r="R61" t="n">
-        <v>7040037</v>
+        <v>7039933</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7252,10 +7252,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129809133</v>
+        <v>129809610</v>
       </c>
       <c r="B62" t="n">
-        <v>80218</v>
+        <v>100983</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7263,34 +7263,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495563</v>
+        <v>495622</v>
       </c>
       <c r="R62" t="n">
-        <v>7039894</v>
+        <v>7039966</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7331,28 +7339,34 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809610</v>
+        <v>129809563</v>
       </c>
       <c r="B63" t="n">
-        <v>100983</v>
+        <v>92320</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7360,31 +7374,30 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7392,10 +7405,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495622</v>
+        <v>495549</v>
       </c>
       <c r="R63" t="n">
-        <v>7039966</v>
+        <v>7039804</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7430,6 +7443,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I en knäckt gran.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7443,6 +7461,21 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7553,10 +7586,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129809563</v>
+        <v>129809133</v>
       </c>
       <c r="B65" t="n">
-        <v>92320</v>
+        <v>80218</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7564,41 +7597,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495549</v>
+        <v>495563</v>
       </c>
       <c r="R65" t="n">
-        <v>7039804</v>
+        <v>7039894</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7633,50 +7659,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>I en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129809158</v>
+        <v>129809127</v>
       </c>
       <c r="B67" t="n">
-        <v>83047</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,21 +7791,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495531</v>
+        <v>495608</v>
       </c>
       <c r="R67" t="n">
-        <v>7040125</v>
+        <v>7040209</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7851,6 +7851,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7877,10 +7882,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809099</v>
+        <v>129809129</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>57895</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7888,21 +7893,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7912,10 +7917,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495626</v>
+        <v>495522</v>
       </c>
       <c r="R68" t="n">
-        <v>7040099</v>
+        <v>7039794</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7948,6 +7953,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,32 +7984,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809098</v>
+        <v>129809090</v>
       </c>
       <c r="B69" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8009,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495709</v>
+        <v>495544</v>
       </c>
       <c r="R69" t="n">
-        <v>7040119</v>
+        <v>7040035</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8071,10 +8081,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809129</v>
+        <v>129809158</v>
       </c>
       <c r="B70" t="n">
-        <v>57895</v>
+        <v>83047</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8082,21 +8092,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8106,10 +8116,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495522</v>
+        <v>495531</v>
       </c>
       <c r="R70" t="n">
-        <v>7039794</v>
+        <v>7040125</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8142,11 +8152,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8173,32 +8178,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809090</v>
+        <v>129809099</v>
       </c>
       <c r="B71" t="n">
-        <v>98794</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8208,10 +8213,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495544</v>
+        <v>495626</v>
       </c>
       <c r="R71" t="n">
-        <v>7040035</v>
+        <v>7040099</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8270,10 +8275,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129809127</v>
+        <v>129809098</v>
       </c>
       <c r="B72" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8281,21 +8286,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8305,10 +8310,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>495608</v>
+        <v>495709</v>
       </c>
       <c r="R72" t="n">
-        <v>7040209</v>
+        <v>7040119</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8341,11 +8346,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8498,10 +8498,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809600</v>
+        <v>129809585</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>91598</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8509,26 +8509,30 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8536,10 +8540,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495604</v>
+        <v>495645</v>
       </c>
       <c r="R74" t="n">
-        <v>7040032</v>
+        <v>7039861</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8574,11 +8578,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gran i äldre  granskog.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8606,12 +8605,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8629,7 +8628,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809607</v>
+        <v>129809600</v>
       </c>
       <c r="B75" t="n">
         <v>79084</v>
@@ -8659,11 +8658,7 @@
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8671,10 +8666,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495591</v>
+        <v>495604</v>
       </c>
       <c r="R75" t="n">
-        <v>7040221</v>
+        <v>7040032</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8711,7 +8706,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Med apothecier på gran.</t>
+          <t>På gran i äldre  granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8764,10 +8759,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809579</v>
+        <v>129809607</v>
       </c>
       <c r="B76" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8775,28 +8770,28 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8806,10 +8801,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495499</v>
+        <v>495591</v>
       </c>
       <c r="R76" t="n">
-        <v>7040089</v>
+        <v>7040221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8846,7 +8841,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>Med apothecier på gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8866,22 +8861,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8899,10 +8894,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809568</v>
+        <v>129809104</v>
       </c>
       <c r="B77" t="n">
-        <v>57737</v>
+        <v>83055</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8910,42 +8905,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495618</v>
+        <v>495595</v>
       </c>
       <c r="R77" t="n">
-        <v>7040130</v>
+        <v>7040220</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8980,11 +8967,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8993,51 +8975,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809122</v>
+        <v>129809101</v>
       </c>
       <c r="B78" t="n">
-        <v>57737</v>
+        <v>83055</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9045,21 +9002,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9069,10 +9026,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495433</v>
+        <v>495682</v>
       </c>
       <c r="R78" t="n">
-        <v>7039995</v>
+        <v>7039933</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9105,11 +9062,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9136,10 +9088,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129809130</v>
+        <v>129809579</v>
       </c>
       <c r="B79" t="n">
-        <v>57895</v>
+        <v>80189</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9147,34 +9099,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>495569</v>
+        <v>495499</v>
       </c>
       <c r="R79" t="n">
-        <v>7039991</v>
+        <v>7040089</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9211,7 +9170,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>På bark av en levande sälg.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9220,28 +9179,54 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809585</v>
+        <v>129809568</v>
       </c>
       <c r="B80" t="n">
-        <v>91598</v>
+        <v>57737</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9249,28 +9234,29 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9280,10 +9266,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495645</v>
+        <v>495618</v>
       </c>
       <c r="R80" t="n">
-        <v>7039861</v>
+        <v>7040130</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,13 +9304,17 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9368,10 +9358,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809104</v>
+        <v>129809122</v>
       </c>
       <c r="B81" t="n">
-        <v>83055</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9379,21 +9369,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9403,10 +9393,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495595</v>
+        <v>495433</v>
       </c>
       <c r="R81" t="n">
-        <v>7040220</v>
+        <v>7039995</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9439,6 +9429,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9465,10 +9460,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129809101</v>
+        <v>129809130</v>
       </c>
       <c r="B82" t="n">
-        <v>83055</v>
+        <v>57895</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9476,21 +9471,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9500,10 +9495,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>495682</v>
+        <v>495569</v>
       </c>
       <c r="R82" t="n">
-        <v>7039933</v>
+        <v>7039991</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9536,6 +9531,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10908,10 +10908,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129809590</v>
+        <v>129809093</v>
       </c>
       <c r="B95" t="n">
-        <v>79084</v>
+        <v>91622</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10919,37 +10919,30 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>495644</v>
+        <v>495655</v>
       </c>
       <c r="R95" t="n">
-        <v>7039865</v>
+        <v>7040108</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10990,54 +10983,28 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129809093</v>
+        <v>129809590</v>
       </c>
       <c r="B96" t="n">
-        <v>91622</v>
+        <v>79084</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11045,30 +11012,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>495655</v>
+        <v>495644</v>
       </c>
       <c r="R96" t="n">
-        <v>7040108</v>
+        <v>7039865</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11109,18 +11083,44 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129809086</v>
+        <v>129809088</v>
       </c>
       <c r="B98" t="n">
         <v>80189</v>
@@ -11288,10 +11288,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>495579</v>
+        <v>495461</v>
       </c>
       <c r="R98" t="n">
-        <v>7040079</v>
+        <v>7039960</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11350,10 +11350,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129809569</v>
+        <v>129809086</v>
       </c>
       <c r="B99" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11361,42 +11361,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>495637</v>
+        <v>495579</v>
       </c>
       <c r="R99" t="n">
-        <v>7040173</v>
+        <v>7040079</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11431,11 +11423,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs några meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11444,51 +11431,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129809088</v>
+        <v>129809569</v>
       </c>
       <c r="B100" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11496,34 +11458,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>495461</v>
+        <v>495637</v>
       </c>
       <c r="R100" t="n">
-        <v>7039960</v>
+        <v>7040173</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11558,6 +11528,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs några meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11566,16 +11541,41 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12736,39 +12736,40 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129809582</v>
+        <v>129809566</v>
       </c>
       <c r="B111" t="n">
-        <v>80225</v>
+        <v>57737</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -12778,10 +12779,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>495698</v>
+        <v>495633</v>
       </c>
       <c r="R111" t="n">
-        <v>7040023</v>
+        <v>7040044</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12818,7 +12819,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12827,7 +12828,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12838,22 +12838,22 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129809085</v>
+        <v>129809582</v>
       </c>
       <c r="B112" t="n">
-        <v>80218</v>
+        <v>80225</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12882,34 +12882,41 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>495476</v>
+        <v>495698</v>
       </c>
       <c r="R112" t="n">
-        <v>7040074</v>
+        <v>7040023</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12944,77 +12951,100 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129809566</v>
+        <v>129809085</v>
       </c>
       <c r="B113" t="n">
-        <v>57737</v>
+        <v>80218</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>495633</v>
+        <v>495476</v>
       </c>
       <c r="R113" t="n">
-        <v>7040044</v>
+        <v>7040074</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13049,11 +13079,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13062,41 +13087,16 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129809096</v>
+        <v>129809147</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>91598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495570</v>
+        <v>495722</v>
       </c>
       <c r="R27" t="n">
-        <v>7040065</v>
+        <v>7040115</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129809124</v>
+        <v>129809096</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495478</v>
+        <v>495570</v>
       </c>
       <c r="R28" t="n">
-        <v>7040087</v>
+        <v>7040065</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,11 +3623,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,10 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129809131</v>
+        <v>129809124</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,21 +3660,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3689,10 +3684,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495455</v>
+        <v>495478</v>
       </c>
       <c r="R29" t="n">
-        <v>7040119</v>
+        <v>7040087</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3729,7 +3724,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,10 +3751,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129809147</v>
+        <v>129809131</v>
       </c>
       <c r="B30" t="n">
-        <v>91598</v>
+        <v>57895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,21 +3762,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3791,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495722</v>
+        <v>495455</v>
       </c>
       <c r="R30" t="n">
-        <v>7040115</v>
+        <v>7040119</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3827,6 +3822,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5731,10 +5731,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809091</v>
+        <v>129809079</v>
       </c>
       <c r="B48" t="n">
-        <v>91598</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495490</v>
+        <v>495550</v>
       </c>
       <c r="R48" t="n">
-        <v>7039928</v>
+        <v>7039807</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5802,6 +5802,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5828,7 +5833,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129809079</v>
+        <v>129809080</v>
       </c>
       <c r="B49" t="n">
         <v>57737</v>
@@ -5863,10 +5868,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495550</v>
+        <v>495554</v>
       </c>
       <c r="R49" t="n">
-        <v>7039807</v>
+        <v>7039840</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5930,10 +5935,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129809080</v>
+        <v>129809091</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>91598</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5941,21 +5946,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5965,10 +5970,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495554</v>
+        <v>495490</v>
       </c>
       <c r="R50" t="n">
-        <v>7039840</v>
+        <v>7039928</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6001,11 +6006,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -13417,7 +13417,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129835890</v>
+        <v>129835889</v>
       </c>
       <c r="B117" t="n">
         <v>57737</v>
@@ -13460,7 +13460,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>495436</v>
+        <v>495434</v>
       </c>
       <c r="R117" t="n">
         <v>7039822</v>
@@ -13527,7 +13527,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129835889</v>
+        <v>129835890</v>
       </c>
       <c r="B118" t="n">
         <v>57737</v>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>495434</v>
+        <v>495436</v>
       </c>
       <c r="R118" t="n">
         <v>7039822</v>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809157</v>
+        <v>129809603</v>
       </c>
       <c r="B2" t="n">
-        <v>82939</v>
+        <v>79095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495620</v>
+        <v>495504</v>
       </c>
       <c r="R2" t="n">
-        <v>7040063</v>
+        <v>7040017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +751,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -898,42 +932,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809611</v>
+        <v>129809578</v>
       </c>
       <c r="B4" t="n">
-        <v>101020</v>
+        <v>80200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495627</v>
+        <v>495701</v>
       </c>
       <c r="R4" t="n">
-        <v>7039995</v>
+        <v>7040014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +1014,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,6 +1030,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1014,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809603</v>
+        <v>129809087</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,37 +1078,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495504</v>
+        <v>495710</v>
       </c>
       <c r="R5" t="n">
-        <v>7040017</v>
+        <v>7039992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,62 +1140,31 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809578</v>
+        <v>129809089</v>
       </c>
       <c r="B6" t="n">
         <v>80200</v>
@@ -1174,23 +1193,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495701</v>
+        <v>495476</v>
       </c>
       <c r="R6" t="n">
-        <v>7040014</v>
+        <v>7040074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,65 +1237,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809087</v>
+        <v>129809157</v>
       </c>
       <c r="B7" t="n">
-        <v>80200</v>
+        <v>82939</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,21 +1272,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495710</v>
+        <v>495620</v>
       </c>
       <c r="R7" t="n">
-        <v>7039992</v>
+        <v>7040063</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,45 +1358,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809089</v>
+        <v>129809611</v>
       </c>
       <c r="B8" t="n">
-        <v>80200</v>
+        <v>101020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495476</v>
+        <v>495627</v>
       </c>
       <c r="R8" t="n">
-        <v>7040074</v>
+        <v>7039995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,24 +1439,35 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809107</v>
+        <v>129809146</v>
       </c>
       <c r="B10" t="n">
-        <v>91639</v>
+        <v>91635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495592</v>
+        <v>495659</v>
       </c>
       <c r="R10" t="n">
-        <v>7040205</v>
+        <v>7039854</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129809575</v>
+        <v>129809107</v>
       </c>
       <c r="B11" t="n">
-        <v>56314</v>
+        <v>91639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,50 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495639</v>
+        <v>495592</v>
       </c>
       <c r="R11" t="n">
-        <v>7039976</v>
+        <v>7040205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,11 +1766,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1795,36 +1774,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129809115</v>
+        <v>129809139</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>80201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495682</v>
+        <v>495484</v>
       </c>
       <c r="R12" t="n">
-        <v>7040065</v>
+        <v>7040082</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,11 +1861,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809082</v>
+        <v>129809599</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,34 +1898,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495470</v>
+        <v>495719</v>
       </c>
       <c r="R13" t="n">
-        <v>7039843</v>
+        <v>7040059</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1965,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,63 +1974,96 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809146</v>
+        <v>129809573</v>
       </c>
       <c r="B14" t="n">
-        <v>91635</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495659</v>
+        <v>495496</v>
       </c>
       <c r="R14" t="n">
-        <v>7039854</v>
+        <v>7040079</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,69 +2098,107 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På bark av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129809139</v>
+        <v>129809583</v>
       </c>
       <c r="B15" t="n">
-        <v>80201</v>
+        <v>80236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495484</v>
+        <v>495575</v>
       </c>
       <c r="R15" t="n">
-        <v>7040082</v>
+        <v>7039971</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,34 +2233,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På barken av en död sälglåga.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129809599</v>
+        <v>129809115</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,37 +2299,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495719</v>
+        <v>495682</v>
       </c>
       <c r="R16" t="n">
-        <v>7040059</v>
+        <v>7040065</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2363,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,96 +2372,63 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129809573</v>
+        <v>129809082</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>57741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495496</v>
+        <v>495470</v>
       </c>
       <c r="R17" t="n">
-        <v>7040079</v>
+        <v>7039843</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,7 +2465,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,96 +2474,79 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129809583</v>
+        <v>129809575</v>
       </c>
       <c r="B18" t="n">
-        <v>80236</v>
+        <v>56314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>206004</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495575</v>
+        <v>495639</v>
       </c>
       <c r="R18" t="n">
-        <v>7039971</v>
+        <v>7039976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,7 +2583,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På barken av en död sälglåga.</t>
+          <t>En individ i vit vinterpäls som blev skrämd och flydde.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,7 +2592,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2585,24 +2600,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2620,48 +2620,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809602</v>
+        <v>129809134</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495479</v>
+        <v>495561</v>
       </c>
       <c r="R19" t="n">
-        <v>7039967</v>
+        <v>7039987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2702,54 +2699,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809596</v>
+        <v>129809159</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>83065</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,37 +2728,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495570</v>
+        <v>495530</v>
       </c>
       <c r="R20" t="n">
-        <v>7039935</v>
+        <v>7040111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2828,44 +2796,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2969,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809159</v>
+        <v>129809602</v>
       </c>
       <c r="B22" t="n">
-        <v>83065</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,34 +2922,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495530</v>
+        <v>495479</v>
       </c>
       <c r="R22" t="n">
-        <v>7040111</v>
+        <v>7039967</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,28 +2993,54 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809152</v>
+        <v>129809596</v>
       </c>
       <c r="B23" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,30 +3048,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495696</v>
+        <v>495570</v>
       </c>
       <c r="R23" t="n">
-        <v>7040090</v>
+        <v>7039935</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,52 +3119,74 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809134</v>
+        <v>129809152</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>91659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495561</v>
+        <v>495696</v>
       </c>
       <c r="R24" t="n">
-        <v>7039987</v>
+        <v>7040090</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129809096</v>
+        <v>129809131</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495570</v>
+        <v>495455</v>
       </c>
       <c r="R27" t="n">
-        <v>7040065</v>
+        <v>7040119</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,6 +3526,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3552,10 +3557,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129809147</v>
+        <v>129809096</v>
       </c>
       <c r="B28" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,21 +3568,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3587,10 +3592,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495722</v>
+        <v>495570</v>
       </c>
       <c r="R28" t="n">
-        <v>7040115</v>
+        <v>7040065</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,10 +3756,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129809131</v>
+        <v>129809147</v>
       </c>
       <c r="B30" t="n">
-        <v>57900</v>
+        <v>91635</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,21 +3767,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3786,10 +3791,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495455</v>
+        <v>495722</v>
       </c>
       <c r="R30" t="n">
-        <v>7040119</v>
+        <v>7040115</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,11 +3827,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129809572</v>
+        <v>129809105</v>
       </c>
       <c r="B31" t="n">
-        <v>80229</v>
+        <v>91603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,41 +3864,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495579</v>
+        <v>495461</v>
       </c>
       <c r="R31" t="n">
-        <v>7039969</v>
+        <v>7039930</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,89 +3926,54 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På barken av en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809141</v>
+        <v>129809094</v>
       </c>
       <c r="B32" t="n">
-        <v>80236</v>
+        <v>91659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4023,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495483</v>
+        <v>495459</v>
       </c>
       <c r="R32" t="n">
-        <v>7040081</v>
+        <v>7039862</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4067,6 +4025,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4198,10 +4157,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809105</v>
+        <v>129809572</v>
       </c>
       <c r="B34" t="n">
-        <v>91603</v>
+        <v>80229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,34 +4168,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495461</v>
+        <v>495579</v>
       </c>
       <c r="R34" t="n">
-        <v>7039930</v>
+        <v>7039969</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,54 +4237,89 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På barken av en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129809094</v>
+        <v>129809141</v>
       </c>
       <c r="B35" t="n">
-        <v>91659</v>
+        <v>80236</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4326,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495459</v>
+        <v>495483</v>
       </c>
       <c r="R35" t="n">
-        <v>7039862</v>
+        <v>7040081</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4370,7 +4371,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4626,10 +4626,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129809111</v>
+        <v>129809604</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,34 +4637,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495558</v>
+        <v>495501</v>
       </c>
       <c r="R38" t="n">
-        <v>7039811</v>
+        <v>7040069</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4699,77 +4702,95 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129809604</v>
+        <v>129809084</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495501</v>
+        <v>495651</v>
       </c>
       <c r="R39" t="n">
-        <v>7040069</v>
+        <v>7039928</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4810,76 +4831,50 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129809084</v>
+        <v>129809138</v>
       </c>
       <c r="B40" t="n">
-        <v>80229</v>
+        <v>57738</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4889,10 +4884,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495651</v>
+        <v>495613</v>
       </c>
       <c r="R40" t="n">
-        <v>7039928</v>
+        <v>7039922</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4951,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809138</v>
+        <v>129809111</v>
       </c>
       <c r="B41" t="n">
-        <v>57738</v>
+        <v>57741</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4962,16 +4957,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4986,10 +4981,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495613</v>
+        <v>495558</v>
       </c>
       <c r="R41" t="n">
-        <v>7039922</v>
+        <v>7039811</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5022,6 +5017,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5474,7 +5474,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129809592</v>
+        <v>129809605</v>
       </c>
       <c r="B46" t="n">
         <v>79095</v>
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495516</v>
+        <v>495546</v>
       </c>
       <c r="R46" t="n">
-        <v>7039796</v>
+        <v>7040104</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5548,11 +5548,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5605,7 +5600,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129809605</v>
+        <v>129809154</v>
       </c>
       <c r="B47" t="n">
         <v>79095</v>
@@ -5634,19 +5629,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495546</v>
+        <v>495635</v>
       </c>
       <c r="R47" t="n">
-        <v>7040104</v>
+        <v>7039937</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5687,51 +5679,25 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129809154</v>
+        <v>129809592</v>
       </c>
       <c r="B48" t="n">
         <v>79095</v>
@@ -5760,16 +5726,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495635</v>
+        <v>495516</v>
       </c>
       <c r="R48" t="n">
-        <v>7039937</v>
+        <v>7039796</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5804,24 +5773,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6032,52 +6032,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809584</v>
+        <v>129809142</v>
       </c>
       <c r="B51" t="n">
-        <v>80236</v>
+        <v>78107</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495504</v>
+        <v>495682</v>
       </c>
       <c r="R51" t="n">
-        <v>7040027</v>
+        <v>7039932</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6112,107 +6105,69 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På barken av en smal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809571</v>
+        <v>129809103</v>
       </c>
       <c r="B52" t="n">
-        <v>80229</v>
+        <v>83073</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495699</v>
+        <v>495680</v>
       </c>
       <c r="R52" t="n">
-        <v>7040018</v>
+        <v>7039973</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6247,65 +6202,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129809103</v>
+        <v>129809606</v>
       </c>
       <c r="B53" t="n">
-        <v>83073</v>
+        <v>79095</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6313,34 +6237,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495680</v>
+        <v>495603</v>
       </c>
       <c r="R53" t="n">
-        <v>7039973</v>
+        <v>7040220</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6381,55 +6308,85 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809606</v>
+        <v>129809584</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>80236</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6437,10 +6394,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495603</v>
+        <v>495504</v>
       </c>
       <c r="R54" t="n">
-        <v>7040220</v>
+        <v>7040027</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6475,6 +6432,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På barken av en smal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6492,22 +6454,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6525,45 +6487,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129809142</v>
+        <v>129809571</v>
       </c>
       <c r="B55" t="n">
-        <v>78107</v>
+        <v>80229</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495682</v>
+        <v>495699</v>
       </c>
       <c r="R55" t="n">
-        <v>7039932</v>
+        <v>7040018</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6598,24 +6567,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6923,52 +6923,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129809563</v>
+        <v>129809143</v>
       </c>
       <c r="B59" t="n">
-        <v>92357</v>
+        <v>78107</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495549</v>
+        <v>495700</v>
       </c>
       <c r="R59" t="n">
-        <v>7039804</v>
+        <v>7040007</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7003,82 +6996,56 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I en knäckt gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809562</v>
+        <v>129809563</v>
       </c>
       <c r="B60" t="n">
-        <v>91639</v>
+        <v>92357</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7095,10 +7062,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495606</v>
+        <v>495549</v>
       </c>
       <c r="R60" t="n">
-        <v>7040134</v>
+        <v>7039804</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7135,7 +7102,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>I en upplyft granlåga i granskog.</t>
+          <t>I en knäckt gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7163,14 +7130,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7188,10 +7150,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809156</v>
+        <v>129809562</v>
       </c>
       <c r="B61" t="n">
-        <v>82939</v>
+        <v>91639</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,34 +7161,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495664</v>
+        <v>495606</v>
       </c>
       <c r="R61" t="n">
-        <v>7040037</v>
+        <v>7040134</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7261,77 +7230,100 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129809610</v>
+        <v>129809156</v>
       </c>
       <c r="B62" t="n">
-        <v>101020</v>
+        <v>82939</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495622</v>
+        <v>495664</v>
       </c>
       <c r="R62" t="n">
-        <v>7039966</v>
+        <v>7040037</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7372,65 +7364,71 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809153</v>
+        <v>129809610</v>
       </c>
       <c r="B63" t="n">
-        <v>91659</v>
+        <v>101020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495507</v>
+        <v>495622</v>
       </c>
       <c r="R63" t="n">
-        <v>7040063</v>
+        <v>7039966</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7471,52 +7469,54 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129809133</v>
+        <v>129809153</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>91659</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495563</v>
+        <v>495507</v>
       </c>
       <c r="R64" t="n">
-        <v>7039894</v>
+        <v>7040063</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7586,32 +7586,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129809150</v>
+        <v>129809133</v>
       </c>
       <c r="B65" t="n">
-        <v>91635</v>
+        <v>80229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495465</v>
+        <v>495563</v>
       </c>
       <c r="R65" t="n">
-        <v>7039933</v>
+        <v>7039894</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7683,10 +7683,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129809143</v>
+        <v>129809150</v>
       </c>
       <c r="B66" t="n">
-        <v>78107</v>
+        <v>91635</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7694,21 +7694,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495700</v>
+        <v>495465</v>
       </c>
       <c r="R66" t="n">
-        <v>7040007</v>
+        <v>7039933</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809098</v>
+        <v>129809127</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7888,21 +7888,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495709</v>
+        <v>495608</v>
       </c>
       <c r="R68" t="n">
-        <v>7040119</v>
+        <v>7040209</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7948,6 +7948,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,10 +7979,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809127</v>
+        <v>129809158</v>
       </c>
       <c r="B69" t="n">
-        <v>57741</v>
+        <v>83065</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7985,21 +7990,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8009,10 +8014,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495608</v>
+        <v>495531</v>
       </c>
       <c r="R69" t="n">
-        <v>7040209</v>
+        <v>7040125</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8045,11 +8050,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809129</v>
+        <v>129809098</v>
       </c>
       <c r="B70" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495522</v>
+        <v>495709</v>
       </c>
       <c r="R70" t="n">
-        <v>7039794</v>
+        <v>7040119</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8147,11 +8147,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8178,32 +8173,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809090</v>
+        <v>129809129</v>
       </c>
       <c r="B71" t="n">
-        <v>98831</v>
+        <v>57900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8213,10 +8208,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495544</v>
+        <v>495522</v>
       </c>
       <c r="R71" t="n">
-        <v>7040035</v>
+        <v>7039794</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8249,6 +8244,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8275,32 +8275,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129809158</v>
+        <v>129809090</v>
       </c>
       <c r="B72" t="n">
-        <v>83065</v>
+        <v>98831</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>495531</v>
+        <v>495544</v>
       </c>
       <c r="R72" t="n">
-        <v>7040125</v>
+        <v>7040035</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809568</v>
+        <v>129809579</v>
       </c>
       <c r="B73" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,29 +8383,28 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -8415,10 +8414,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495618</v>
+        <v>495499</v>
       </c>
       <c r="R73" t="n">
-        <v>7040130</v>
+        <v>7040089</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8455,7 +8454,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På bark av en levande sälg.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8464,6 +8463,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809122</v>
+        <v>129809585</v>
       </c>
       <c r="B74" t="n">
-        <v>57741</v>
+        <v>91635</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8518,34 +8518,41 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495433</v>
+        <v>495645</v>
       </c>
       <c r="R74" t="n">
-        <v>7039995</v>
+        <v>7039861</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8580,39 +8587,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809585</v>
+        <v>129809601</v>
       </c>
       <c r="B75" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8620,30 +8648,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8651,10 +8675,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495645</v>
+        <v>495583</v>
       </c>
       <c r="R75" t="n">
-        <v>7039861</v>
+        <v>7039969</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8716,12 +8740,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8739,7 +8763,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809601</v>
+        <v>129809607</v>
       </c>
       <c r="B76" t="n">
         <v>79095</v>
@@ -8769,7 +8793,11 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8777,10 +8805,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495583</v>
+        <v>495591</v>
       </c>
       <c r="R76" t="n">
-        <v>7039969</v>
+        <v>7040221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8813,6 +8841,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Med apothecier på gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8865,7 +8898,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809607</v>
+        <v>129809600</v>
       </c>
       <c r="B77" t="n">
         <v>79095</v>
@@ -8895,11 +8928,7 @@
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8907,10 +8936,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495591</v>
+        <v>495604</v>
       </c>
       <c r="R77" t="n">
-        <v>7040221</v>
+        <v>7040032</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8947,7 +8976,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Med apothecier på gran.</t>
+          <t>På gran i äldre  granskog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9000,10 +9029,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809600</v>
+        <v>129809104</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>83073</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9011,37 +9040,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495604</v>
+        <v>495595</v>
       </c>
       <c r="R78" t="n">
-        <v>7040032</v>
+        <v>7040220</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9076,65 +9102,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran i äldre  granskog.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129809579</v>
+        <v>129809101</v>
       </c>
       <c r="B79" t="n">
-        <v>80200</v>
+        <v>83073</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9142,41 +9137,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>495499</v>
+        <v>495682</v>
       </c>
       <c r="R79" t="n">
-        <v>7040089</v>
+        <v>7039933</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9211,65 +9199,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På bark av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809104</v>
+        <v>129809568</v>
       </c>
       <c r="B80" t="n">
-        <v>83073</v>
+        <v>57741</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9277,34 +9234,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495595</v>
+        <v>495618</v>
       </c>
       <c r="R80" t="n">
-        <v>7040220</v>
+        <v>7040130</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9339,6 +9304,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9347,26 +9317,51 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809101</v>
+        <v>129809122</v>
       </c>
       <c r="B81" t="n">
-        <v>83073</v>
+        <v>57741</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9374,21 +9369,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9398,10 +9393,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495682</v>
+        <v>495433</v>
       </c>
       <c r="R81" t="n">
-        <v>7039933</v>
+        <v>7039995</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9434,6 +9429,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9659,10 +9659,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129809125</v>
+        <v>129809574</v>
       </c>
       <c r="B84" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9670,16 +9670,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9688,16 +9688,24 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>495461</v>
+        <v>495509</v>
       </c>
       <c r="R84" t="n">
-        <v>7040125</v>
+        <v>7040092</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9734,7 +9742,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9745,26 +9753,51 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129809574</v>
+        <v>129809125</v>
       </c>
       <c r="B85" t="n">
-        <v>57738</v>
+        <v>57741</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9772,16 +9805,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9790,24 +9823,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>495509</v>
+        <v>495461</v>
       </c>
       <c r="R85" t="n">
-        <v>7040092</v>
+        <v>7040125</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9844,7 +9869,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9855,41 +9880,16 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9993,10 +9993,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129809148</v>
+        <v>129809081</v>
       </c>
       <c r="B87" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>495742</v>
+        <v>495568</v>
       </c>
       <c r="R87" t="n">
-        <v>7040116</v>
+        <v>7040032</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10064,6 +10064,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10090,10 +10095,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129809580</v>
+        <v>129809148</v>
       </c>
       <c r="B88" t="n">
-        <v>80200</v>
+        <v>91635</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10101,41 +10106,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>495517</v>
+        <v>495742</v>
       </c>
       <c r="R88" t="n">
-        <v>7040108</v>
+        <v>7040116</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10170,100 +10168,76 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På barken av en upplyft död nedfallen sälg.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129809135</v>
+        <v>129809580</v>
       </c>
       <c r="B89" t="n">
-        <v>80229</v>
+        <v>80200</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>495536</v>
+        <v>495517</v>
       </c>
       <c r="R89" t="n">
-        <v>7040124</v>
+        <v>7040108</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10298,56 +10272,87 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På barken av en upplyft död nedfallen sälg.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129809081</v>
+        <v>129809135</v>
       </c>
       <c r="B90" t="n">
-        <v>57741</v>
+        <v>80229</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10357,10 +10362,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>495568</v>
+        <v>495536</v>
       </c>
       <c r="R90" t="n">
-        <v>7040032</v>
+        <v>7040124</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10393,11 +10398,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129809597</v>
+        <v>129809587</v>
       </c>
       <c r="B91" t="n">
-        <v>79095</v>
+        <v>91635</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10435,26 +10435,30 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10462,10 +10466,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>495598</v>
+        <v>495597</v>
       </c>
       <c r="R91" t="n">
-        <v>7039942</v>
+        <v>7040221</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10500,6 +10504,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>I en stående levande gran.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10527,12 +10536,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10773,10 +10782,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129809587</v>
+        <v>129809597</v>
       </c>
       <c r="B94" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10784,30 +10793,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10815,10 +10820,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>495597</v>
+        <v>495598</v>
       </c>
       <c r="R94" t="n">
-        <v>7040221</v>
+        <v>7039942</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10853,11 +10858,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>I en stående levande gran.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10885,12 +10885,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12039,45 +12039,52 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129809102</v>
+        <v>129809581</v>
       </c>
       <c r="B105" t="n">
-        <v>83073</v>
+        <v>80236</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>495533</v>
+        <v>495749</v>
       </c>
       <c r="R105" t="n">
-        <v>7039800</v>
+        <v>7040011</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12112,24 +12119,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På bark på en smal sälg.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12271,52 +12309,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809581</v>
+        <v>129809102</v>
       </c>
       <c r="B107" t="n">
-        <v>80236</v>
+        <v>83073</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495749</v>
+        <v>495533</v>
       </c>
       <c r="R107" t="n">
-        <v>7040011</v>
+        <v>7039800</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12351,55 +12382,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>På bark på en smal sälg.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129809566</v>
+        <v>129809151</v>
       </c>
       <c r="B110" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12654,42 +12654,30 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>495633</v>
+        <v>495456</v>
       </c>
       <c r="R110" t="n">
-        <v>7040044</v>
+        <v>7039928</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12724,11 +12712,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12737,82 +12720,68 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129809151</v>
+        <v>129809582</v>
       </c>
       <c r="B111" t="n">
-        <v>91659</v>
+        <v>80236</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>495456</v>
+        <v>495698</v>
       </c>
       <c r="R111" t="n">
-        <v>7039928</v>
+        <v>7040023</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12847,34 +12816,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129809582</v>
+        <v>129809085</v>
       </c>
       <c r="B112" t="n">
-        <v>80236</v>
+        <v>80229</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12882,41 +12882,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>495698</v>
+        <v>495476</v>
       </c>
       <c r="R112" t="n">
-        <v>7040023</v>
+        <v>7040074</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12951,100 +12944,77 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129809085</v>
+        <v>129809566</v>
       </c>
       <c r="B113" t="n">
-        <v>80229</v>
+        <v>57741</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>495476</v>
+        <v>495633</v>
       </c>
       <c r="R113" t="n">
-        <v>7040074</v>
+        <v>7040044</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13079,6 +13049,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13087,16 +13062,41 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809603</v>
+        <v>129809157</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>82939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495504</v>
+        <v>495620</v>
       </c>
       <c r="R2" t="n">
-        <v>7040017</v>
+        <v>7040063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,55 +748,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -932,41 +898,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809578</v>
+        <v>129809611</v>
       </c>
       <c r="B4" t="n">
-        <v>80200</v>
+        <v>101020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -974,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495701</v>
+        <v>495627</v>
       </c>
       <c r="R4" t="n">
-        <v>7040014</v>
+        <v>7039995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +981,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,26 +997,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1067,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809087</v>
+        <v>129809603</v>
       </c>
       <c r="B5" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,34 +1025,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495710</v>
+        <v>495504</v>
       </c>
       <c r="R5" t="n">
-        <v>7039992</v>
+        <v>7040017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,31 +1090,62 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809089</v>
+        <v>129809578</v>
       </c>
       <c r="B6" t="n">
         <v>80200</v>
@@ -1193,16 +1174,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495476</v>
+        <v>495701</v>
       </c>
       <c r="R6" t="n">
-        <v>7040074</v>
+        <v>7040014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,34 +1225,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809157</v>
+        <v>129809087</v>
       </c>
       <c r="B7" t="n">
-        <v>82939</v>
+        <v>80200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,21 +1291,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1296,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495620</v>
+        <v>495710</v>
       </c>
       <c r="R7" t="n">
-        <v>7040063</v>
+        <v>7039992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,53 +1377,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809611</v>
+        <v>129809089</v>
       </c>
       <c r="B8" t="n">
-        <v>101020</v>
+        <v>80200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495627</v>
+        <v>495476</v>
       </c>
       <c r="R8" t="n">
-        <v>7039995</v>
+        <v>7040074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,35 +1450,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -4626,48 +4626,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129809604</v>
+        <v>129809140</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>92092</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495501</v>
+        <v>495671</v>
       </c>
       <c r="R38" t="n">
-        <v>7040069</v>
+        <v>7039845</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,44 +4705,18 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5048,32 +5019,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809140</v>
+        <v>129809083</v>
       </c>
       <c r="B42" t="n">
-        <v>92092</v>
+        <v>56931</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5083,10 +5054,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495671</v>
+        <v>495476</v>
       </c>
       <c r="R42" t="n">
-        <v>7039845</v>
+        <v>7040074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5280,45 +5251,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129809083</v>
+        <v>129809604</v>
       </c>
       <c r="B44" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495476</v>
+        <v>495501</v>
       </c>
       <c r="R44" t="n">
-        <v>7040074</v>
+        <v>7040069</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5359,18 +5333,44 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6032,45 +6032,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809142</v>
+        <v>129809584</v>
       </c>
       <c r="B51" t="n">
-        <v>78107</v>
+        <v>80236</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495682</v>
+        <v>495504</v>
       </c>
       <c r="R51" t="n">
-        <v>7039932</v>
+        <v>7040027</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6105,69 +6112,107 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På barken av en smal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809103</v>
+        <v>129809571</v>
       </c>
       <c r="B52" t="n">
-        <v>83073</v>
+        <v>80229</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495680</v>
+        <v>495699</v>
       </c>
       <c r="R52" t="n">
-        <v>7039973</v>
+        <v>7040018</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,34 +6247,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129809606</v>
+        <v>129809103</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>83073</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6237,37 +6313,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495603</v>
+        <v>495680</v>
       </c>
       <c r="R53" t="n">
-        <v>7040220</v>
+        <v>7039973</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6308,85 +6381,55 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809584</v>
+        <v>129809606</v>
       </c>
       <c r="B54" t="n">
-        <v>80236</v>
+        <v>79095</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6394,10 +6437,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495504</v>
+        <v>495603</v>
       </c>
       <c r="R54" t="n">
-        <v>7040027</v>
+        <v>7040220</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6432,11 +6475,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På barken av en smal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6454,22 +6492,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6487,52 +6525,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129809571</v>
+        <v>129809142</v>
       </c>
       <c r="B55" t="n">
-        <v>80229</v>
+        <v>78107</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495699</v>
+        <v>495682</v>
       </c>
       <c r="R55" t="n">
-        <v>7040018</v>
+        <v>7039932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6567,55 +6598,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6923,45 +6923,52 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129809143</v>
+        <v>129809563</v>
       </c>
       <c r="B59" t="n">
-        <v>78107</v>
+        <v>92357</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495700</v>
+        <v>495549</v>
       </c>
       <c r="R59" t="n">
-        <v>7040007</v>
+        <v>7039804</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6996,56 +7003,82 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I en knäckt gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809563</v>
+        <v>129809562</v>
       </c>
       <c r="B60" t="n">
-        <v>92357</v>
+        <v>91639</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7062,10 +7095,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495549</v>
+        <v>495606</v>
       </c>
       <c r="R60" t="n">
-        <v>7039804</v>
+        <v>7040134</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7102,7 +7135,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>I en knäckt gran.</t>
+          <t>I en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7130,9 +7163,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7150,10 +7188,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809562</v>
+        <v>129809156</v>
       </c>
       <c r="B61" t="n">
-        <v>91639</v>
+        <v>82939</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7161,41 +7199,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495606</v>
+        <v>495664</v>
       </c>
       <c r="R61" t="n">
-        <v>7040134</v>
+        <v>7040037</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7230,65 +7261,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129809156</v>
+        <v>129809153</v>
       </c>
       <c r="B62" t="n">
-        <v>82939</v>
+        <v>91659</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7296,23 +7296,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7320,10 +7316,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495664</v>
+        <v>495507</v>
       </c>
       <c r="R62" t="n">
-        <v>7040037</v>
+        <v>7040063</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7382,10 +7378,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809610</v>
+        <v>129809133</v>
       </c>
       <c r="B63" t="n">
-        <v>101020</v>
+        <v>80229</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,42 +7389,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495622</v>
+        <v>495563</v>
       </c>
       <c r="R63" t="n">
-        <v>7039966</v>
+        <v>7039894</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7469,34 +7457,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129809153</v>
+        <v>129809150</v>
       </c>
       <c r="B64" t="n">
-        <v>91659</v>
+        <v>91635</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7504,19 +7486,23 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7524,10 +7510,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495507</v>
+        <v>495465</v>
       </c>
       <c r="R64" t="n">
-        <v>7040063</v>
+        <v>7039933</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7586,10 +7572,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129809133</v>
+        <v>129809610</v>
       </c>
       <c r="B65" t="n">
-        <v>80229</v>
+        <v>101020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,34 +7583,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495563</v>
+        <v>495622</v>
       </c>
       <c r="R65" t="n">
-        <v>7039894</v>
+        <v>7039966</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7665,28 +7659,34 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129809150</v>
+        <v>129809143</v>
       </c>
       <c r="B66" t="n">
-        <v>91635</v>
+        <v>78107</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7694,21 +7694,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495465</v>
+        <v>495700</v>
       </c>
       <c r="R66" t="n">
-        <v>7039933</v>
+        <v>7040007</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129809127</v>
+        <v>129809098</v>
       </c>
       <c r="B68" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7888,21 +7888,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495608</v>
+        <v>495709</v>
       </c>
       <c r="R68" t="n">
-        <v>7040209</v>
+        <v>7040119</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7948,11 +7948,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7979,10 +7974,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129809158</v>
+        <v>129809127</v>
       </c>
       <c r="B69" t="n">
-        <v>83065</v>
+        <v>57741</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7990,21 +7985,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8014,10 +8009,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>495531</v>
+        <v>495608</v>
       </c>
       <c r="R69" t="n">
-        <v>7040125</v>
+        <v>7040209</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8050,6 +8045,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809098</v>
+        <v>129809129</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495709</v>
+        <v>495522</v>
       </c>
       <c r="R70" t="n">
-        <v>7040119</v>
+        <v>7039794</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8147,6 +8147,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8173,32 +8178,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809129</v>
+        <v>129809090</v>
       </c>
       <c r="B71" t="n">
-        <v>57900</v>
+        <v>98831</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8208,10 +8213,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495522</v>
+        <v>495544</v>
       </c>
       <c r="R71" t="n">
-        <v>7039794</v>
+        <v>7040035</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8244,11 +8249,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8275,32 +8275,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129809090</v>
+        <v>129809158</v>
       </c>
       <c r="B72" t="n">
-        <v>98831</v>
+        <v>83065</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>495544</v>
+        <v>495531</v>
       </c>
       <c r="R72" t="n">
-        <v>7040035</v>
+        <v>7040125</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809579</v>
+        <v>129809568</v>
       </c>
       <c r="B73" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,28 +8383,29 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -8414,10 +8415,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495499</v>
+        <v>495618</v>
       </c>
       <c r="R73" t="n">
-        <v>7040089</v>
+        <v>7040130</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8454,7 +8455,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark av en levande sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8463,7 +8464,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809585</v>
+        <v>129809122</v>
       </c>
       <c r="B74" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8518,41 +8518,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495645</v>
+        <v>495433</v>
       </c>
       <c r="R74" t="n">
-        <v>7039861</v>
+        <v>7039995</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8587,60 +8580,39 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809601</v>
+        <v>129809585</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>91635</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8648,26 +8620,30 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8675,10 +8651,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495583</v>
+        <v>495645</v>
       </c>
       <c r="R75" t="n">
-        <v>7039969</v>
+        <v>7039861</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8740,12 +8716,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8763,7 +8739,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809607</v>
+        <v>129809601</v>
       </c>
       <c r="B76" t="n">
         <v>79095</v>
@@ -8793,11 +8769,7 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8805,10 +8777,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495591</v>
+        <v>495583</v>
       </c>
       <c r="R76" t="n">
-        <v>7040221</v>
+        <v>7039969</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8841,11 +8813,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Med apothecier på gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8898,7 +8865,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809600</v>
+        <v>129809607</v>
       </c>
       <c r="B77" t="n">
         <v>79095</v>
@@ -8928,7 +8895,11 @@
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8936,10 +8907,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495604</v>
+        <v>495591</v>
       </c>
       <c r="R77" t="n">
-        <v>7040032</v>
+        <v>7040221</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8976,7 +8947,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran i äldre  granskog.</t>
+          <t>Med apothecier på gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9029,10 +9000,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809104</v>
+        <v>129809600</v>
       </c>
       <c r="B78" t="n">
-        <v>83073</v>
+        <v>79095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9040,34 +9011,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495595</v>
+        <v>495604</v>
       </c>
       <c r="R78" t="n">
-        <v>7040220</v>
+        <v>7040032</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9102,34 +9076,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran i äldre  granskog.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129809101</v>
+        <v>129809579</v>
       </c>
       <c r="B79" t="n">
-        <v>83073</v>
+        <v>80200</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9137,34 +9142,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>495682</v>
+        <v>495499</v>
       </c>
       <c r="R79" t="n">
-        <v>7039933</v>
+        <v>7040089</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9199,34 +9211,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På bark av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809568</v>
+        <v>129809104</v>
       </c>
       <c r="B80" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9234,42 +9277,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495618</v>
+        <v>495595</v>
       </c>
       <c r="R80" t="n">
-        <v>7040130</v>
+        <v>7040220</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9304,11 +9339,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9317,51 +9347,26 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809122</v>
+        <v>129809101</v>
       </c>
       <c r="B81" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9369,21 +9374,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9393,10 +9398,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495433</v>
+        <v>495682</v>
       </c>
       <c r="R81" t="n">
-        <v>7039995</v>
+        <v>7039933</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9429,11 +9434,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9562,10 +9562,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129809106</v>
+        <v>129809574</v>
       </c>
       <c r="B83" t="n">
-        <v>91639</v>
+        <v>57738</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9573,34 +9573,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>495777</v>
+        <v>495509</v>
       </c>
       <c r="R83" t="n">
-        <v>7040083</v>
+        <v>7040092</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9635,6 +9643,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9643,69 +9656,86 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129809574</v>
+        <v>129809145</v>
       </c>
       <c r="B84" t="n">
-        <v>57738</v>
+        <v>80160</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>495509</v>
+        <v>495535</v>
       </c>
       <c r="R84" t="n">
-        <v>7040092</v>
+        <v>7040131</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9740,11 +9770,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en stående död gran med full längd och 43 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9753,51 +9778,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129809125</v>
+        <v>129809106</v>
       </c>
       <c r="B85" t="n">
-        <v>57741</v>
+        <v>91639</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9805,21 +9805,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>495461</v>
+        <v>495777</v>
       </c>
       <c r="R85" t="n">
-        <v>7040125</v>
+        <v>7040083</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9865,11 +9865,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9896,32 +9891,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129809145</v>
+        <v>129809125</v>
       </c>
       <c r="B86" t="n">
-        <v>80160</v>
+        <v>57741</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9931,10 +9926,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>495535</v>
+        <v>495461</v>
       </c>
       <c r="R86" t="n">
-        <v>7040131</v>
+        <v>7040125</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9967,6 +9962,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9993,10 +9993,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129809081</v>
+        <v>129809148</v>
       </c>
       <c r="B87" t="n">
-        <v>57741</v>
+        <v>91635</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>495568</v>
+        <v>495742</v>
       </c>
       <c r="R87" t="n">
-        <v>7040032</v>
+        <v>7040116</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10064,11 +10064,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10095,10 +10090,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129809148</v>
+        <v>129809081</v>
       </c>
       <c r="B88" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10106,21 +10101,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10130,10 +10125,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>495742</v>
+        <v>495568</v>
       </c>
       <c r="R88" t="n">
-        <v>7040116</v>
+        <v>7040032</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10166,6 +10161,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129809587</v>
+        <v>129809597</v>
       </c>
       <c r="B91" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10435,30 +10435,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10466,10 +10462,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>495597</v>
+        <v>495598</v>
       </c>
       <c r="R91" t="n">
-        <v>7040221</v>
+        <v>7039942</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10504,11 +10500,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>I en stående levande gran.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10536,12 +10527,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10782,10 +10773,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129809597</v>
+        <v>129809587</v>
       </c>
       <c r="B94" t="n">
-        <v>79095</v>
+        <v>91635</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10793,26 +10784,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10820,10 +10815,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>495598</v>
+        <v>495597</v>
       </c>
       <c r="R94" t="n">
-        <v>7039942</v>
+        <v>7040221</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10858,6 +10853,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>I en stående levande gran.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10885,12 +10885,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12039,52 +12039,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129809581</v>
+        <v>129809102</v>
       </c>
       <c r="B105" t="n">
-        <v>80236</v>
+        <v>83073</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>495749</v>
+        <v>495533</v>
       </c>
       <c r="R105" t="n">
-        <v>7040011</v>
+        <v>7039800</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12119,55 +12112,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På bark på en smal sälg.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12309,45 +12271,52 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809102</v>
+        <v>129809581</v>
       </c>
       <c r="B107" t="n">
-        <v>83073</v>
+        <v>80236</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495533</v>
+        <v>495749</v>
       </c>
       <c r="R107" t="n">
-        <v>7039800</v>
+        <v>7040011</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12382,24 +12351,55 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>På bark på en smal sälg.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129809151</v>
+        <v>129809566</v>
       </c>
       <c r="B110" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12654,30 +12654,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>495456</v>
+        <v>495633</v>
       </c>
       <c r="R110" t="n">
-        <v>7039928</v>
+        <v>7040044</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12712,6 +12724,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12720,68 +12737,82 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129809582</v>
+        <v>129809151</v>
       </c>
       <c r="B111" t="n">
-        <v>80236</v>
+        <v>91659</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>495698</v>
+        <v>495456</v>
       </c>
       <c r="R111" t="n">
-        <v>7040023</v>
+        <v>7039928</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12816,65 +12847,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129809085</v>
+        <v>129809582</v>
       </c>
       <c r="B112" t="n">
-        <v>80229</v>
+        <v>80236</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12882,34 +12882,41 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>495476</v>
+        <v>495698</v>
       </c>
       <c r="R112" t="n">
-        <v>7040074</v>
+        <v>7040023</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12944,77 +12951,100 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129809566</v>
+        <v>129809085</v>
       </c>
       <c r="B113" t="n">
-        <v>57741</v>
+        <v>80229</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>495633</v>
+        <v>495476</v>
       </c>
       <c r="R113" t="n">
-        <v>7040044</v>
+        <v>7040074</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13049,11 +13079,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13062,41 +13087,16 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809157</v>
+        <v>129809109</v>
       </c>
       <c r="B2" t="n">
-        <v>82939</v>
+        <v>57741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495620</v>
+        <v>495738</v>
       </c>
       <c r="R2" t="n">
-        <v>7040063</v>
+        <v>7040008</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +766,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,37 +797,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809595</v>
+        <v>129809611</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>101022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -810,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495548</v>
+        <v>495627</v>
       </c>
       <c r="R3" t="n">
-        <v>7039913</v>
+        <v>7039995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +878,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -861,26 +896,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,53 +913,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809611</v>
+        <v>129809157</v>
       </c>
       <c r="B4" t="n">
-        <v>101020</v>
+        <v>82939</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495627</v>
+        <v>495620</v>
       </c>
       <c r="R4" t="n">
-        <v>7039995</v>
+        <v>7040063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,42 +986,31 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809603</v>
+        <v>129809595</v>
       </c>
       <c r="B5" t="n">
         <v>79095</v>
@@ -1052,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495504</v>
+        <v>495548</v>
       </c>
       <c r="R5" t="n">
-        <v>7040017</v>
+        <v>7039913</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809578</v>
+        <v>129809603</v>
       </c>
       <c r="B6" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,30 +1147,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495701</v>
+        <v>495504</v>
       </c>
       <c r="R6" t="n">
-        <v>7040014</v>
+        <v>7040017</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1214,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,22 +1234,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1280,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809087</v>
+        <v>129809578</v>
       </c>
       <c r="B7" t="n">
         <v>80200</v>
@@ -1309,16 +1296,23 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495710</v>
+        <v>495701</v>
       </c>
       <c r="R7" t="n">
-        <v>7039992</v>
+        <v>7040014</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,31 +1347,62 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809089</v>
+        <v>129809087</v>
       </c>
       <c r="B8" t="n">
         <v>80200</v>
@@ -1412,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495476</v>
+        <v>495710</v>
       </c>
       <c r="R8" t="n">
-        <v>7040074</v>
+        <v>7039992</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129809109</v>
+        <v>129809089</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,54 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495738</v>
+        <v>495476</v>
       </c>
       <c r="R9" t="n">
-        <v>7040008</v>
+        <v>7040074</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,11 +1570,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökande hona i avverkningsanmäld skog med höga till mycket höga livsmiljövärden!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809146</v>
+        <v>129809107</v>
       </c>
       <c r="B10" t="n">
-        <v>91635</v>
+        <v>91641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495659</v>
+        <v>495592</v>
       </c>
       <c r="R10" t="n">
-        <v>7039854</v>
+        <v>7040205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129809107</v>
+        <v>129809146</v>
       </c>
       <c r="B11" t="n">
-        <v>91639</v>
+        <v>91637</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495592</v>
+        <v>495659</v>
       </c>
       <c r="R11" t="n">
-        <v>7040205</v>
+        <v>7039854</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809134</v>
+        <v>129809076</v>
       </c>
       <c r="B19" t="n">
-        <v>80229</v>
+        <v>91641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495561</v>
+        <v>495663</v>
       </c>
       <c r="R19" t="n">
-        <v>7039987</v>
+        <v>7040097</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809159</v>
+        <v>129809144</v>
       </c>
       <c r="B20" t="n">
-        <v>83065</v>
+        <v>78107</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495530</v>
+        <v>495584</v>
       </c>
       <c r="R20" t="n">
-        <v>7040111</v>
+        <v>7040207</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129809076</v>
+        <v>129809159</v>
       </c>
       <c r="B21" t="n">
-        <v>91639</v>
+        <v>83065</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495663</v>
+        <v>495530</v>
       </c>
       <c r="R21" t="n">
-        <v>7040097</v>
+        <v>7040111</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809602</v>
+        <v>129809152</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,37 +2922,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495479</v>
+        <v>495696</v>
       </c>
       <c r="R22" t="n">
-        <v>7039967</v>
+        <v>7040090</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2993,51 +2986,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809596</v>
+        <v>129809602</v>
       </c>
       <c r="B23" t="n">
         <v>79095</v>
@@ -3075,10 +3042,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495570</v>
+        <v>495479</v>
       </c>
       <c r="R23" t="n">
-        <v>7039935</v>
+        <v>7039967</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809152</v>
+        <v>129809596</v>
       </c>
       <c r="B24" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,30 +3141,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495696</v>
+        <v>495570</v>
       </c>
       <c r="R24" t="n">
-        <v>7040090</v>
+        <v>7039935</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,50 +3212,76 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129809114</v>
+        <v>129809134</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>80229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495559</v>
+        <v>495561</v>
       </c>
       <c r="R25" t="n">
-        <v>7039895</v>
+        <v>7039987</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3327,11 +3327,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3358,10 +3353,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129809144</v>
+        <v>129809114</v>
       </c>
       <c r="B26" t="n">
-        <v>78107</v>
+        <v>57741</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,21 +3364,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3393,10 +3388,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495584</v>
+        <v>495559</v>
       </c>
       <c r="R26" t="n">
-        <v>7040207</v>
+        <v>7039895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3429,6 +3424,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3557,10 +3557,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129809096</v>
+        <v>129809124</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3568,21 +3568,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495570</v>
+        <v>495478</v>
       </c>
       <c r="R28" t="n">
-        <v>7040065</v>
+        <v>7040087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3628,6 +3628,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,10 +3659,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129809124</v>
+        <v>129809147</v>
       </c>
       <c r="B29" t="n">
-        <v>57741</v>
+        <v>91637</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,21 +3670,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3689,10 +3694,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495478</v>
+        <v>495722</v>
       </c>
       <c r="R29" t="n">
-        <v>7040087</v>
+        <v>7040115</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3725,11 +3730,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129809147</v>
+        <v>129809096</v>
       </c>
       <c r="B30" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495722</v>
+        <v>495570</v>
       </c>
       <c r="R30" t="n">
-        <v>7040115</v>
+        <v>7040065</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3853,45 +3853,61 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129809105</v>
+        <v>129809137</v>
       </c>
       <c r="B31" t="n">
-        <v>91603</v>
+        <v>57738</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495461</v>
+        <v>495739</v>
       </c>
       <c r="R31" t="n">
-        <v>7039930</v>
+        <v>7040024</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3950,10 +3966,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129809094</v>
+        <v>129809567</v>
       </c>
       <c r="B32" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,30 +3977,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495459</v>
+        <v>495594</v>
       </c>
       <c r="R32" t="n">
-        <v>7039862</v>
+        <v>7039971</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,35 +4047,64 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129809137</v>
+        <v>129809126</v>
       </c>
       <c r="B33" t="n">
-        <v>57738</v>
+        <v>57741</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4055,16 +4112,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4072,33 +4129,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495739</v>
+        <v>495467</v>
       </c>
       <c r="R33" t="n">
-        <v>7040024</v>
+        <v>7040110</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,6 +4172,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,10 +4203,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129809572</v>
+        <v>129809105</v>
       </c>
       <c r="B34" t="n">
-        <v>80229</v>
+        <v>91605</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,41 +4214,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495579</v>
+        <v>495461</v>
       </c>
       <c r="R34" t="n">
-        <v>7039969</v>
+        <v>7039930</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,89 +4276,54 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På barken av en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129809141</v>
+        <v>129809094</v>
       </c>
       <c r="B35" t="n">
-        <v>80236</v>
+        <v>91661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4327,10 +4331,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495483</v>
+        <v>495459</v>
       </c>
       <c r="R35" t="n">
-        <v>7040081</v>
+        <v>7039862</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4371,6 +4375,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4389,40 +4394,39 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129809567</v>
+        <v>129809572</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>80229</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4432,10 +4436,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495594</v>
+        <v>495579</v>
       </c>
       <c r="R36" t="n">
-        <v>7039971</v>
+        <v>7039969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,7 +4476,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran som är snitslad för hänsyn till kulturminne.</t>
+          <t>På barken av en sälglåga.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4481,6 +4485,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4491,22 +4496,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4524,32 +4529,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129809126</v>
+        <v>129809141</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>80236</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4559,10 +4564,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495467</v>
+        <v>495483</v>
       </c>
       <c r="R37" t="n">
-        <v>7040110</v>
+        <v>7040081</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4595,11 +4600,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4629,7 +4629,7 @@
         <v>129809140</v>
       </c>
       <c r="B38" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4723,45 +4723,52 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129809084</v>
+        <v>129809561</v>
       </c>
       <c r="B39" t="n">
-        <v>80229</v>
+        <v>91641</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495651</v>
+        <v>495774</v>
       </c>
       <c r="R39" t="n">
-        <v>7039928</v>
+        <v>7040061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4796,34 +4803,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129809138</v>
+        <v>129809111</v>
       </c>
       <c r="B40" t="n">
-        <v>57738</v>
+        <v>57741</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,16 +4869,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4855,10 +4893,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495613</v>
+        <v>495558</v>
       </c>
       <c r="R40" t="n">
-        <v>7039922</v>
+        <v>7039811</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4891,6 +4929,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4917,32 +4960,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129809111</v>
+        <v>129809083</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>56931</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4952,10 +4995,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495558</v>
+        <v>495476</v>
       </c>
       <c r="R41" t="n">
-        <v>7039811</v>
+        <v>7040074</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4988,11 +5031,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,45 +5057,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129809083</v>
+        <v>129809604</v>
       </c>
       <c r="B42" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495476</v>
+        <v>495501</v>
       </c>
       <c r="R42" t="n">
-        <v>7040074</v>
+        <v>7040069</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5098,70 +5139,89 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129809561</v>
+        <v>129809084</v>
       </c>
       <c r="B43" t="n">
-        <v>91639</v>
+        <v>80229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495774</v>
+        <v>495651</v>
       </c>
       <c r="R43" t="n">
-        <v>7040061</v>
+        <v>7039928</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,65 +5256,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129809604</v>
+        <v>129809138</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5262,37 +5291,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495501</v>
+        <v>495613</v>
       </c>
       <c r="R44" t="n">
-        <v>7040069</v>
+        <v>7039922</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5333,44 +5359,18 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5380,7 +5380,7 @@
         <v>129809091</v>
       </c>
       <c r="B45" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6032,41 +6032,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129809584</v>
+        <v>129809606</v>
       </c>
       <c r="B51" t="n">
-        <v>80236</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6074,10 +6070,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495504</v>
+        <v>495603</v>
       </c>
       <c r="R51" t="n">
-        <v>7040027</v>
+        <v>7040220</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6112,11 +6108,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På barken av en smal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6134,22 +6125,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6167,52 +6158,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129809571</v>
+        <v>129809103</v>
       </c>
       <c r="B52" t="n">
-        <v>80229</v>
+        <v>83073</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495699</v>
+        <v>495680</v>
       </c>
       <c r="R52" t="n">
-        <v>7040018</v>
+        <v>7039973</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6247,100 +6231,76 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129809103</v>
+        <v>129809584</v>
       </c>
       <c r="B53" t="n">
-        <v>83073</v>
+        <v>80236</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495680</v>
+        <v>495504</v>
       </c>
       <c r="R53" t="n">
-        <v>7039973</v>
+        <v>7040027</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6375,61 +6335,96 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På barken av en smal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129809606</v>
+        <v>129809571</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6437,10 +6432,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495603</v>
+        <v>495699</v>
       </c>
       <c r="R54" t="n">
-        <v>7040220</v>
+        <v>7040018</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6475,6 +6470,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På barken av en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6492,22 +6492,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6926,7 +6926,7 @@
         <v>129809563</v>
       </c>
       <c r="B59" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7053,10 +7053,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129809562</v>
+        <v>129809153</v>
       </c>
       <c r="B60" t="n">
-        <v>91639</v>
+        <v>91661</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7064,41 +7064,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495606</v>
+        <v>495507</v>
       </c>
       <c r="R60" t="n">
-        <v>7040134</v>
+        <v>7040063</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,65 +7122,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>I en upplyft granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129809156</v>
+        <v>129809143</v>
       </c>
       <c r="B61" t="n">
-        <v>82939</v>
+        <v>78107</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,21 +7157,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7223,10 +7181,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495664</v>
+        <v>495700</v>
       </c>
       <c r="R61" t="n">
-        <v>7040037</v>
+        <v>7040007</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7285,10 +7243,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129809153</v>
+        <v>129809150</v>
       </c>
       <c r="B62" t="n">
-        <v>91659</v>
+        <v>91637</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7296,19 +7254,23 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7316,10 +7278,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495507</v>
+        <v>495465</v>
       </c>
       <c r="R62" t="n">
-        <v>7040063</v>
+        <v>7039933</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7378,45 +7340,52 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129809133</v>
+        <v>129809562</v>
       </c>
       <c r="B63" t="n">
-        <v>80229</v>
+        <v>91641</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495563</v>
+        <v>495606</v>
       </c>
       <c r="R63" t="n">
-        <v>7039894</v>
+        <v>7040134</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7451,34 +7420,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129809150</v>
+        <v>129809156</v>
       </c>
       <c r="B64" t="n">
-        <v>91635</v>
+        <v>82939</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7486,21 +7486,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495465</v>
+        <v>495664</v>
       </c>
       <c r="R64" t="n">
-        <v>7039933</v>
+        <v>7040037</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7572,10 +7572,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129809610</v>
+        <v>129809133</v>
       </c>
       <c r="B65" t="n">
-        <v>101020</v>
+        <v>80229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7583,42 +7583,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495622</v>
+        <v>495563</v>
       </c>
       <c r="R65" t="n">
-        <v>7039966</v>
+        <v>7039894</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7659,69 +7651,71 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129809143</v>
+        <v>129809610</v>
       </c>
       <c r="B66" t="n">
-        <v>78107</v>
+        <v>101022</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495700</v>
+        <v>495622</v>
       </c>
       <c r="R66" t="n">
-        <v>7040007</v>
+        <v>7039966</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7762,18 +7756,24 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129809129</v>
+        <v>129809158</v>
       </c>
       <c r="B70" t="n">
-        <v>57900</v>
+        <v>83065</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>495522</v>
+        <v>495531</v>
       </c>
       <c r="R70" t="n">
-        <v>7039794</v>
+        <v>7040125</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8147,11 +8147,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8178,32 +8173,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129809090</v>
+        <v>129809129</v>
       </c>
       <c r="B71" t="n">
-        <v>98831</v>
+        <v>57900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8213,10 +8208,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>495544</v>
+        <v>495522</v>
       </c>
       <c r="R71" t="n">
-        <v>7040035</v>
+        <v>7039794</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8249,6 +8244,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8275,32 +8275,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129809158</v>
+        <v>129809090</v>
       </c>
       <c r="B72" t="n">
-        <v>83065</v>
+        <v>98833</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>495531</v>
+        <v>495544</v>
       </c>
       <c r="R72" t="n">
-        <v>7040125</v>
+        <v>7040035</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129809568</v>
+        <v>129809585</v>
       </c>
       <c r="B73" t="n">
-        <v>57741</v>
+        <v>91637</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,29 +8383,28 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -8415,10 +8414,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>495618</v>
+        <v>495645</v>
       </c>
       <c r="R73" t="n">
-        <v>7040130</v>
+        <v>7039861</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8453,17 +8452,13 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8507,10 +8502,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129809122</v>
+        <v>129809601</v>
       </c>
       <c r="B74" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8518,34 +8513,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>495433</v>
+        <v>495583</v>
       </c>
       <c r="R74" t="n">
-        <v>7039995</v>
+        <v>7039969</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8580,39 +8578,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129809585</v>
+        <v>129809600</v>
       </c>
       <c r="B75" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8620,30 +8639,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8651,10 +8666,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>495645</v>
+        <v>495604</v>
       </c>
       <c r="R75" t="n">
-        <v>7039861</v>
+        <v>7040032</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8689,6 +8704,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran i äldre  granskog.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8716,12 +8736,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8739,7 +8759,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129809601</v>
+        <v>129809607</v>
       </c>
       <c r="B76" t="n">
         <v>79095</v>
@@ -8769,7 +8789,11 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8777,10 +8801,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>495583</v>
+        <v>495591</v>
       </c>
       <c r="R76" t="n">
-        <v>7039969</v>
+        <v>7040221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8813,6 +8837,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Med apothecier på gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8865,10 +8894,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129809607</v>
+        <v>129809104</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>83073</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8876,41 +8905,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>495591</v>
+        <v>495595</v>
       </c>
       <c r="R77" t="n">
-        <v>7040221</v>
+        <v>7040220</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8945,65 +8967,34 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Med apothecier på gran.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129809600</v>
+        <v>129809101</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>83073</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9011,37 +9002,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>495604</v>
+        <v>495682</v>
       </c>
       <c r="R78" t="n">
-        <v>7040032</v>
+        <v>7039933</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9076,55 +9064,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran i äldre  granskog.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9266,10 +9223,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129809104</v>
+        <v>129809130</v>
       </c>
       <c r="B80" t="n">
-        <v>83073</v>
+        <v>57900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9277,21 +9234,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9301,10 +9258,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>495595</v>
+        <v>495569</v>
       </c>
       <c r="R80" t="n">
-        <v>7040220</v>
+        <v>7039991</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9337,6 +9294,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9363,10 +9325,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129809101</v>
+        <v>129809568</v>
       </c>
       <c r="B81" t="n">
-        <v>83073</v>
+        <v>57741</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9374,34 +9336,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>495682</v>
+        <v>495618</v>
       </c>
       <c r="R81" t="n">
-        <v>7039933</v>
+        <v>7040130</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9436,6 +9406,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9444,26 +9419,51 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129809130</v>
+        <v>129809122</v>
       </c>
       <c r="B82" t="n">
-        <v>57900</v>
+        <v>57741</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9471,21 +9471,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>495569</v>
+        <v>495433</v>
       </c>
       <c r="R82" t="n">
-        <v>7039991</v>
+        <v>7039995</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9697,32 +9697,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129809145</v>
+        <v>129809106</v>
       </c>
       <c r="B84" t="n">
-        <v>80160</v>
+        <v>91641</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9732,10 +9732,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>495535</v>
+        <v>495777</v>
       </c>
       <c r="R84" t="n">
-        <v>7040131</v>
+        <v>7040083</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9794,32 +9794,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129809106</v>
+        <v>129809145</v>
       </c>
       <c r="B85" t="n">
-        <v>91639</v>
+        <v>80160</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>495777</v>
+        <v>495535</v>
       </c>
       <c r="R85" t="n">
-        <v>7040083</v>
+        <v>7040131</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9993,10 +9993,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129809148</v>
+        <v>129809081</v>
       </c>
       <c r="B87" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>495742</v>
+        <v>495568</v>
       </c>
       <c r="R87" t="n">
-        <v>7040116</v>
+        <v>7040032</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10064,6 +10064,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10090,32 +10095,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129809081</v>
+        <v>129809135</v>
       </c>
       <c r="B88" t="n">
-        <v>57741</v>
+        <v>80229</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10125,10 +10130,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>495568</v>
+        <v>495536</v>
       </c>
       <c r="R88" t="n">
-        <v>7040032</v>
+        <v>7040124</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10161,11 +10166,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10192,10 +10192,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129809580</v>
+        <v>129809148</v>
       </c>
       <c r="B89" t="n">
-        <v>80200</v>
+        <v>91637</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10203,41 +10203,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>495517</v>
+        <v>495742</v>
       </c>
       <c r="R89" t="n">
-        <v>7040108</v>
+        <v>7040116</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10272,100 +10265,76 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På barken av en upplyft död nedfallen sälg.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129809135</v>
+        <v>129809580</v>
       </c>
       <c r="B90" t="n">
-        <v>80229</v>
+        <v>80200</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>495536</v>
+        <v>495517</v>
       </c>
       <c r="R90" t="n">
-        <v>7040124</v>
+        <v>7040108</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10400,34 +10369,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På barken av en upplyft död nedfallen sälg.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129809597</v>
+        <v>129809587</v>
       </c>
       <c r="B91" t="n">
-        <v>79095</v>
+        <v>91637</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10435,26 +10435,30 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10462,10 +10466,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>495598</v>
+        <v>495597</v>
       </c>
       <c r="R91" t="n">
-        <v>7039942</v>
+        <v>7040221</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10500,6 +10504,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>I en stående levande gran.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10527,12 +10536,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10676,7 +10685,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129809095</v>
+        <v>129809597</v>
       </c>
       <c r="B93" t="n">
         <v>79095</v>
@@ -10705,16 +10714,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>495614</v>
+        <v>495598</v>
       </c>
       <c r="R93" t="n">
-        <v>7039909</v>
+        <v>7039942</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10755,28 +10767,54 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129809587</v>
+        <v>129809095</v>
       </c>
       <c r="B94" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10784,41 +10822,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>495597</v>
+        <v>495614</v>
       </c>
       <c r="R94" t="n">
-        <v>7040221</v>
+        <v>7039909</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10853,55 +10884,24 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>I en stående levande gran.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
         <v>129809093</v>
       </c>
       <c r="B97" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11253,10 +11253,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129809569</v>
+        <v>129809088</v>
       </c>
       <c r="B98" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11264,42 +11264,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>495637</v>
+        <v>495461</v>
       </c>
       <c r="R98" t="n">
-        <v>7040173</v>
+        <v>7039960</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11334,11 +11326,6 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs några meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11347,48 +11334,23 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129809088</v>
+        <v>129809086</v>
       </c>
       <c r="B99" t="n">
         <v>80200</v>
@@ -11423,10 +11385,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>495461</v>
+        <v>495579</v>
       </c>
       <c r="R99" t="n">
-        <v>7039960</v>
+        <v>7040079</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11485,10 +11447,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129809086</v>
+        <v>129809569</v>
       </c>
       <c r="B100" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11496,34 +11458,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>495579</v>
+        <v>495637</v>
       </c>
       <c r="R100" t="n">
-        <v>7040079</v>
+        <v>7040173</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11558,6 +11528,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs några meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11566,26 +11541,51 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129809594</v>
+        <v>129809116</v>
       </c>
       <c r="B101" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11593,37 +11593,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>495544</v>
+        <v>495435</v>
       </c>
       <c r="R101" t="n">
-        <v>7039898</v>
+        <v>7039823</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11660,7 +11657,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11669,44 +11666,18 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11811,7 +11782,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129809598</v>
+        <v>129809594</v>
       </c>
       <c r="B103" t="n">
         <v>79095</v>
@@ -11849,10 +11820,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495684</v>
+        <v>495544</v>
       </c>
       <c r="R103" t="n">
-        <v>7040002</v>
+        <v>7039898</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11885,6 +11856,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11937,10 +11913,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129809116</v>
+        <v>129809598</v>
       </c>
       <c r="B104" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11948,34 +11924,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>495435</v>
+        <v>495684</v>
       </c>
       <c r="R104" t="n">
-        <v>7039823</v>
+        <v>7040002</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12010,39 +11989,60 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129809102</v>
+        <v>129809113</v>
       </c>
       <c r="B105" t="n">
-        <v>83073</v>
+        <v>57741</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12050,21 +12050,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12074,10 +12074,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>495533</v>
+        <v>495541</v>
       </c>
       <c r="R105" t="n">
-        <v>7039800</v>
+        <v>7039874</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12110,6 +12110,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12136,10 +12141,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129809586</v>
+        <v>129809570</v>
       </c>
       <c r="B106" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12147,28 +12152,29 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -12178,10 +12184,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>495477</v>
+        <v>495618</v>
       </c>
       <c r="R106" t="n">
-        <v>7039974</v>
+        <v>7040246</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12218,7 +12224,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Växer i en stubbe av en knäckt gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12227,7 +12233,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -12248,12 +12253,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12271,39 +12276,39 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129809581</v>
+        <v>129809586</v>
       </c>
       <c r="B107" t="n">
-        <v>80236</v>
+        <v>91637</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -12313,10 +12318,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>495749</v>
+        <v>495477</v>
       </c>
       <c r="R107" t="n">
-        <v>7040011</v>
+        <v>7039974</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12353,7 +12358,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På bark på en smal sälg.</t>
+          <t>Växer i en stubbe av en knäckt gran.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12373,22 +12378,22 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12406,10 +12411,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129809113</v>
+        <v>129809102</v>
       </c>
       <c r="B108" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12417,21 +12422,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12441,10 +12446,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>495541</v>
+        <v>495533</v>
       </c>
       <c r="R108" t="n">
-        <v>7039874</v>
+        <v>7039800</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12477,11 +12482,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12508,40 +12508,39 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129809570</v>
+        <v>129809581</v>
       </c>
       <c r="B109" t="n">
-        <v>57741</v>
+        <v>80236</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -12551,10 +12550,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>495618</v>
+        <v>495749</v>
       </c>
       <c r="R109" t="n">
-        <v>7040246</v>
+        <v>7040011</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12591,7 +12590,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På bark på en smal sälg.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12600,6 +12599,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12610,22 +12610,22 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12643,40 +12643,39 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129809566</v>
+        <v>129809582</v>
       </c>
       <c r="B110" t="n">
-        <v>57741</v>
+        <v>80236</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -12686,10 +12685,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>495633</v>
+        <v>495698</v>
       </c>
       <c r="R110" t="n">
-        <v>7040044</v>
+        <v>7040023</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12726,7 +12725,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12735,6 +12734,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12745,22 +12745,22 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12778,30 +12778,34 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129809151</v>
+        <v>129809085</v>
       </c>
       <c r="B111" t="n">
-        <v>91659</v>
+        <v>80229</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12809,10 +12813,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>495456</v>
+        <v>495476</v>
       </c>
       <c r="R111" t="n">
-        <v>7039928</v>
+        <v>7040074</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12871,52 +12875,41 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129809582</v>
+        <v>129809151</v>
       </c>
       <c r="B112" t="n">
-        <v>80236</v>
+        <v>91661</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>495698</v>
+        <v>495456</v>
       </c>
       <c r="R112" t="n">
-        <v>7040023</v>
+        <v>7039928</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12951,100 +12944,77 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129809085</v>
+        <v>129809566</v>
       </c>
       <c r="B113" t="n">
-        <v>80229</v>
+        <v>57741</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>495476</v>
+        <v>495633</v>
       </c>
       <c r="R113" t="n">
-        <v>7040074</v>
+        <v>7040044</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13079,6 +13049,11 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en levande gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13087,16 +13062,41 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -13106,7 +13106,7 @@
         <v>129835891</v>
       </c>
       <c r="B114" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>129835888</v>
       </c>
       <c r="B115" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>129835887</v>
       </c>
       <c r="B116" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>129835890</v>
       </c>
       <c r="B117" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>129835889</v>
       </c>
       <c r="B118" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -13106,7 +13106,7 @@
         <v>129835891</v>
       </c>
       <c r="B114" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>129835888</v>
       </c>
       <c r="B115" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>129835887</v>
       </c>
       <c r="B116" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>129835890</v>
       </c>
       <c r="B117" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>129835889</v>
       </c>
       <c r="B118" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 48059-2025 artfynd.xlsx
+++ b/artfynd/A 48059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809158</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809091</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809092</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809146</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809147</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809148</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809150</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809585</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1713,6 +1763,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809586</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809587</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1945,6 +2005,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809076</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2042,6 +2107,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809077</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2139,6 +2209,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809106</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2236,6 +2311,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809107</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2371,6 +2451,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809561</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2506,6 +2591,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809562</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809140</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2701,6 +2796,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809100</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2798,6 +2898,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809156</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2895,6 +3000,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809157</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2992,6 +3102,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809139</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3122,6 +3237,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809563</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3219,6 +3339,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809105</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3316,6 +3441,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809095</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3413,6 +3543,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809096</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3510,6 +3645,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809098</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3607,6 +3747,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809099</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3704,6 +3849,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809154</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3801,6 +3951,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809155</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3927,6 +4082,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809590</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4053,6 +4213,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809591</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4184,6 +4349,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809592</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809593</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4441,6 +4616,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809594</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4567,6 +4747,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809595</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4693,6 +4878,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809596</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4819,6 +5009,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809597</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4945,6 +5140,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809598</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5076,6 +5276,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809599</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5207,6 +5412,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809600</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5333,6 +5543,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809601</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5459,6 +5674,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809602</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5590,6 +5810,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809603</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5716,6 +5941,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809604</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5842,6 +6072,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809605</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5968,6 +6203,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809606</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6103,6 +6343,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809607</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6229,6 +6474,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809608</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6326,6 +6576,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809101</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6423,6 +6678,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809102</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6520,6 +6780,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809103</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6617,6 +6882,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809104</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6714,6 +6984,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809086</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6811,6 +7086,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809087</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6908,6 +7188,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809088</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7005,6 +7290,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809089</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7140,6 +7430,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809578</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7275,6 +7570,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809579</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7410,6 +7710,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809580</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7507,6 +7812,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809084</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7604,6 +7914,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809085</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7701,6 +8016,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809133</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7798,6 +8118,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809134</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7895,6 +8220,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809135</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8030,6 +8360,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809571</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8165,6 +8500,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809572</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8300,6 +8640,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809573</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8397,6 +8742,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809141</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8532,6 +8882,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809581</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8667,6 +9022,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809582</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8802,6 +9162,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809583</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8937,6 +9302,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809584</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9050,6 +9420,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809137</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9147,6 +9522,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809138</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9282,6 +9662,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809574</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9384,6 +9769,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809078</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9486,6 +9876,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809079</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9588,6 +9983,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809080</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9690,6 +10090,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809081</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9792,6 +10197,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809082</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9914,6 +10324,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809109</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10016,6 +10431,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809110</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10118,6 +10538,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809111</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10220,6 +10645,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809113</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10322,6 +10752,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809114</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10424,6 +10859,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809115</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10526,6 +10966,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809116</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10628,6 +11073,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809122</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10730,6 +11180,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809124</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10832,6 +11287,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809125</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10934,6 +11394,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809126</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11036,6 +11501,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809127</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11171,6 +11641,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809566</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11306,6 +11781,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809567</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11441,6 +11921,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809568</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11576,6 +12061,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809569</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11711,6 +12201,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809570</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11813,6 +12308,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835887</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11915,6 +12415,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835888</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12025,6 +12530,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835889</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12135,6 +12645,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835890</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12245,6 +12760,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835891</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12342,6 +12862,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809083</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12444,6 +12969,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809129</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12546,6 +13076,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809130</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12648,6 +13183,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809131</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12776,6 +13316,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809575</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12873,6 +13418,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809090</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12984,6 +13534,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809610</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13100,6 +13655,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809611</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13197,6 +13757,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809142</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13294,6 +13859,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809143</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13391,6 +13961,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809144</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13488,8 +14063,130 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809145</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>